--- a/bancos/SISOR/BASE_QDD_FISCAL_FONTE_95.xlsx
+++ b/bancos/SISOR/BASE_QDD_FISCAL_FONTE_95.xlsx
@@ -7270,6 +7270,11 @@
       <c r="Y60" t="n">
         <v>0</v>
       </c>
+      <c r="Z60" t="inlineStr">
+        <is>
+          <t>PROTEÇÃO E CONSERVAÇÃO DA FAUNA SILVESTRE</t>
+        </is>
+      </c>
       <c r="AA60" t="inlineStr">
         <is>
           <t>PROTEÇÃO DAS ÁREAS AMBIENTALMENTE CONSERVADAS, DA FAUNA E DA BIODIVERSIDADE FLORESTAL</t>

--- a/bancos/SISOR/BASE_QDD_FISCAL_FONTE_95.xlsx
+++ b/bancos/SISOR/BASE_QDD_FISCAL_FONTE_95.xlsx
@@ -616,7 +616,7 @@
         <v>39</v>
       </c>
       <c r="L2" t="n">
-        <v>95</v>
+        <v>80</v>
       </c>
       <c r="M2" t="n">
         <v>1</v>
@@ -732,7 +732,7 @@
         <v>39</v>
       </c>
       <c r="L3" t="n">
-        <v>95</v>
+        <v>80</v>
       </c>
       <c r="M3" t="n">
         <v>1</v>
@@ -848,7 +848,7 @@
         <v>39</v>
       </c>
       <c r="L4" t="n">
-        <v>95</v>
+        <v>80</v>
       </c>
       <c r="M4" t="n">
         <v>1</v>
@@ -964,7 +964,7 @@
         <v>39</v>
       </c>
       <c r="L5" t="n">
-        <v>95</v>
+        <v>80</v>
       </c>
       <c r="M5" t="n">
         <v>1</v>
@@ -1080,7 +1080,7 @@
         <v>39</v>
       </c>
       <c r="L6" t="n">
-        <v>95</v>
+        <v>80</v>
       </c>
       <c r="M6" t="n">
         <v>1</v>
@@ -1196,7 +1196,7 @@
         <v>39</v>
       </c>
       <c r="L7" t="n">
-        <v>95</v>
+        <v>80</v>
       </c>
       <c r="M7" t="n">
         <v>1</v>
@@ -1312,7 +1312,7 @@
         <v>39</v>
       </c>
       <c r="L8" t="n">
-        <v>95</v>
+        <v>80</v>
       </c>
       <c r="M8" t="n">
         <v>1</v>
@@ -1428,7 +1428,7 @@
         <v>52</v>
       </c>
       <c r="L9" t="n">
-        <v>95</v>
+        <v>80</v>
       </c>
       <c r="M9" t="n">
         <v>1</v>
@@ -1544,7 +1544,7 @@
         <v>39</v>
       </c>
       <c r="L10" t="n">
-        <v>95</v>
+        <v>80</v>
       </c>
       <c r="M10" t="n">
         <v>1</v>
@@ -1660,7 +1660,7 @@
         <v>39</v>
       </c>
       <c r="L11" t="n">
-        <v>95</v>
+        <v>80</v>
       </c>
       <c r="M11" t="n">
         <v>1</v>
@@ -1890,7 +1890,7 @@
         <v>39</v>
       </c>
       <c r="L13" t="n">
-        <v>95</v>
+        <v>80</v>
       </c>
       <c r="M13" t="n">
         <v>1</v>
@@ -2462,7 +2462,7 @@
         <v>39</v>
       </c>
       <c r="L18" t="n">
-        <v>95</v>
+        <v>80</v>
       </c>
       <c r="M18" t="n">
         <v>1</v>
@@ -2578,7 +2578,7 @@
         <v>39</v>
       </c>
       <c r="L19" t="n">
-        <v>95</v>
+        <v>80</v>
       </c>
       <c r="M19" t="n">
         <v>1</v>
@@ -2694,7 +2694,7 @@
         <v>39</v>
       </c>
       <c r="L20" t="n">
-        <v>95</v>
+        <v>80</v>
       </c>
       <c r="M20" t="n">
         <v>1</v>
@@ -2810,7 +2810,7 @@
         <v>39</v>
       </c>
       <c r="L21" t="n">
-        <v>95</v>
+        <v>80</v>
       </c>
       <c r="M21" t="n">
         <v>1</v>
@@ -2926,7 +2926,7 @@
         <v>39</v>
       </c>
       <c r="L22" t="n">
-        <v>95</v>
+        <v>80</v>
       </c>
       <c r="M22" t="n">
         <v>1</v>
@@ -3042,7 +3042,7 @@
         <v>39</v>
       </c>
       <c r="L23" t="n">
-        <v>95</v>
+        <v>80</v>
       </c>
       <c r="M23" t="n">
         <v>1</v>
@@ -3158,7 +3158,7 @@
         <v>39</v>
       </c>
       <c r="L24" t="n">
-        <v>95</v>
+        <v>80</v>
       </c>
       <c r="M24" t="n">
         <v>1</v>
@@ -3274,7 +3274,7 @@
         <v>39</v>
       </c>
       <c r="L25" t="n">
-        <v>95</v>
+        <v>80</v>
       </c>
       <c r="M25" t="n">
         <v>1</v>
@@ -3390,7 +3390,7 @@
         <v>39</v>
       </c>
       <c r="L26" t="n">
-        <v>95</v>
+        <v>80</v>
       </c>
       <c r="M26" t="n">
         <v>1</v>
@@ -3506,7 +3506,7 @@
         <v>52</v>
       </c>
       <c r="L27" t="n">
-        <v>95</v>
+        <v>80</v>
       </c>
       <c r="M27" t="n">
         <v>1</v>
@@ -3622,7 +3622,7 @@
         <v>52</v>
       </c>
       <c r="L28" t="n">
-        <v>95</v>
+        <v>80</v>
       </c>
       <c r="M28" t="n">
         <v>1</v>
@@ -3738,7 +3738,7 @@
         <v>39</v>
       </c>
       <c r="L29" t="n">
-        <v>95</v>
+        <v>80</v>
       </c>
       <c r="M29" t="n">
         <v>1</v>
@@ -3854,7 +3854,7 @@
         <v>39</v>
       </c>
       <c r="L30" t="n">
-        <v>95</v>
+        <v>80</v>
       </c>
       <c r="M30" t="n">
         <v>1</v>
@@ -3970,7 +3970,7 @@
         <v>39</v>
       </c>
       <c r="L31" t="n">
-        <v>95</v>
+        <v>80</v>
       </c>
       <c r="M31" t="n">
         <v>1</v>
@@ -4086,7 +4086,7 @@
         <v>39</v>
       </c>
       <c r="L32" t="n">
-        <v>95</v>
+        <v>80</v>
       </c>
       <c r="M32" t="n">
         <v>1</v>
@@ -4202,7 +4202,7 @@
         <v>39</v>
       </c>
       <c r="L33" t="n">
-        <v>95</v>
+        <v>80</v>
       </c>
       <c r="M33" t="n">
         <v>1</v>
@@ -4318,7 +4318,7 @@
         <v>39</v>
       </c>
       <c r="L34" t="n">
-        <v>95</v>
+        <v>80</v>
       </c>
       <c r="M34" t="n">
         <v>1</v>
@@ -4548,7 +4548,7 @@
         <v>39</v>
       </c>
       <c r="L36" t="n">
-        <v>95</v>
+        <v>80</v>
       </c>
       <c r="M36" t="n">
         <v>1</v>
@@ -4664,7 +4664,7 @@
         <v>39</v>
       </c>
       <c r="L37" t="n">
-        <v>95</v>
+        <v>80</v>
       </c>
       <c r="M37" t="n">
         <v>1</v>
@@ -4780,7 +4780,7 @@
         <v>52</v>
       </c>
       <c r="L38" t="n">
-        <v>95</v>
+        <v>80</v>
       </c>
       <c r="M38" t="n">
         <v>1</v>
@@ -4896,7 +4896,7 @@
         <v>65</v>
       </c>
       <c r="L39" t="n">
-        <v>95</v>
+        <v>80</v>
       </c>
       <c r="M39" t="n">
         <v>1</v>

--- a/bancos/SISOR/BASE_QDD_FISCAL_FONTE_95.xlsx
+++ b/bancos/SISOR/BASE_QDD_FISCAL_FONTE_95.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AF39"/>
+  <dimension ref="A1:AF68"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -579,14 +579,14 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B2" t="n">
-        <v>1230</v>
+        <v>1070</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE AGRICULTURA, PECUÁRIA E ABASTECIMENTO - SEAPA</t>
+          <t>GABINETE MILITAR DO GOVERNADOR DO ESTADO DE MINAS GERAIS - GMG</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -596,24 +596,24 @@
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>1231</v>
+        <v>1071</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE AGRICULTURA, PECUÁRIA E ABASTECIMENTO - SEAPA</t>
+          <t>GABINETE MILITAR DO GOVERNADOR DO ESTADO DE MINAS GERAIS - GABINETE MILITAR</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J2" t="n">
         <v>90</v>
       </c>
       <c r="K2" t="n">
-        <v>39</v>
+        <v>52</v>
       </c>
       <c r="L2" t="n">
         <v>80</v>
@@ -622,87 +622,87 @@
         <v>1</v>
       </c>
       <c r="N2" t="n">
-        <v>10736</v>
+        <v>11232</v>
       </c>
       <c r="O2" t="n">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="P2" t="n">
-        <v>608</v>
+        <v>182</v>
       </c>
       <c r="Q2" t="n">
-        <v>114</v>
+        <v>101</v>
       </c>
       <c r="R2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="S2" t="n">
-        <v>396</v>
+        <v>8</v>
       </c>
       <c r="T2" t="n">
-        <v>4396</v>
+        <v>1008</v>
       </c>
       <c r="U2" t="n">
         <v>1</v>
       </c>
       <c r="V2" t="n">
-        <v>3000000</v>
+        <v>4950000</v>
       </c>
       <c r="W2" t="n">
-        <v>3000000</v>
+        <v>14800000</v>
       </c>
       <c r="X2" t="n">
-        <v>3000000</v>
+        <v>14800000</v>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>RECUPERAÇÃO INTEGRADA DA CAPACIDADE PRODUTIVA DAS BACIAS</t>
+          <t>PROJETO CONVIVÊNCIA COM A SECA E ESTIAGEM</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>INFRAESTRUTURA RURAL E AGRICULTURA SUSTENTÁVEL</t>
+          <t>PROGRAMA ENCONTRO DAS ÁGUAS</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>Acordo Repactuação Rio Doce</t>
+          <t>Acordo Judicial do Rio Doce</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Anexo a definir</t>
+          <t>ANEXO 12</t>
         </is>
       </c>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>Instrumento de entrada a cadastrar</t>
+          <t>A SER CRIADO</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>Atualização e realização de novos estudos de Zoneamento Ambiental Produtivo em sub-bacias hidrográficas da bacia do rio Doce</t>
+          <t>Disponibilização de acesso à água</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>Acordo Repactuação Rio Doce - Anexo a definir - Instrumento de entrada a cadastrar - Atualização e realização de novos estudos de Zoneamento Ambiental Produtivo em sub-bacias hidrográficas da bacia do rio Doce</t>
+          <t>Acordo Judicial do Rio Doce - ANEXO 12 - A SER CRIADO - Disponibilização de acesso à água</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B3" t="n">
-        <v>1230</v>
+        <v>1220</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE AGRICULTURA, PECUÁRIA E ABASTECIMENTO - SEAPA</t>
+          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO ECONÔMICO - SEDE</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -712,11 +712,11 @@
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>3041</v>
+        <v>1221</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>EMPRESA DE ASSISTÊNCIA TÉCNICA E EXTENSÃO RURAL DO ESTADO DE MINAS GERAIS - EMATER</t>
+          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO ECONÔMICO - SEDE</t>
         </is>
       </c>
       <c r="H3" t="n">
@@ -729,7 +729,7 @@
         <v>90</v>
       </c>
       <c r="K3" t="n">
-        <v>39</v>
+        <v>14</v>
       </c>
       <c r="L3" t="n">
         <v>80</v>
@@ -738,87 +738,85 @@
         <v>1</v>
       </c>
       <c r="N3" t="n">
-        <v>10517</v>
+        <v>10858</v>
       </c>
       <c r="O3" t="n">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="P3" t="n">
-        <v>606</v>
+        <v>127</v>
       </c>
       <c r="Q3" t="n">
-        <v>90</v>
+        <v>125</v>
       </c>
       <c r="R3" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="S3" t="n">
-        <v>235</v>
+        <v>82</v>
       </c>
       <c r="T3" t="n">
-        <v>4235</v>
+        <v>1082</v>
       </c>
       <c r="U3" t="n">
         <v>1</v>
       </c>
       <c r="V3" t="n">
-        <v>48432111</v>
+        <v>92880</v>
       </c>
       <c r="W3" t="n">
-        <v>48432111</v>
+        <v>92880</v>
       </c>
       <c r="X3" t="n">
-        <v>48432111</v>
+        <v>92880</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>ASSISTÊNCIA TÉCNICA E EXTENSÃO RURAL PARA AGRICULTORES FAMILIARES E DEMAIS PÚBLICOS</t>
+          <t>MINAS REURB SEDE</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>ASSISTÊNCIA TECNICA E EXTENSÃO RURAL PARA O ESTADO DE MINAS GERAIS</t>
+          <t>POLÍTICA DE REGULARIZAÇÃO FUNDIÁRIA E DE GESTÃO DE IMÓVEIS</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>Acordo Repactuação Rio Doce</t>
+          <t>Acordo Judicial do Rio Doce</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Anexo a definir</t>
-        </is>
-      </c>
-      <c r="AD3" t="inlineStr">
-        <is>
-          <t>Instrumento de entrada a cadastrar</t>
-        </is>
+          <t>ANEXO 12</t>
+        </is>
+      </c>
+      <c r="AD3" t="n">
+        <v>9473171</v>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>Ações de Reposta a Enchentes e de Recuperação Ambiental e Produtiva das Margens do rio Doce</t>
+          <t>Promoção de regularização fundiária</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>Acordo Repactuação Rio Doce - Anexo a definir - Instrumento de entrada a cadastrar - Ações de Reposta a Enchentes e de Recuperação Ambiental e Produtiva das Margens do rio Doce</t>
+          <t>Acordo Judicial do Rio Doce - ANEXO 12 - 9473171 - Promoção de regularização fundiária</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B4" t="n">
-        <v>1230</v>
+        <v>1220</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE AGRICULTURA, PECUÁRIA E ABASTECIMENTO - SEAPA</t>
+          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO ECONÔMICO - SEDE</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -828,11 +826,11 @@
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>3041</v>
+        <v>1221</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>EMPRESA DE ASSISTÊNCIA TÉCNICA E EXTENSÃO RURAL DO ESTADO DE MINAS GERAIS - EMATER</t>
+          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO ECONÔMICO - SEDE</t>
         </is>
       </c>
       <c r="H4" t="n">
@@ -845,7 +843,7 @@
         <v>90</v>
       </c>
       <c r="K4" t="n">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="L4" t="n">
         <v>80</v>
@@ -854,87 +852,85 @@
         <v>1</v>
       </c>
       <c r="N4" t="n">
-        <v>10517</v>
+        <v>10858</v>
       </c>
       <c r="O4" t="n">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="P4" t="n">
-        <v>606</v>
+        <v>127</v>
       </c>
       <c r="Q4" t="n">
-        <v>90</v>
+        <v>125</v>
       </c>
       <c r="R4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="S4" t="n">
-        <v>235</v>
+        <v>82</v>
       </c>
       <c r="T4" t="n">
-        <v>4235</v>
+        <v>1082</v>
       </c>
       <c r="U4" t="n">
         <v>1</v>
       </c>
       <c r="V4" t="n">
-        <v>5000000</v>
+        <v>39145000</v>
       </c>
       <c r="W4" t="n">
-        <v>5000000</v>
+        <v>39145000</v>
       </c>
       <c r="X4" t="n">
-        <v>5000000</v>
+        <v>39145000</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>ASSISTÊNCIA TÉCNICA E EXTENSÃO RURAL PARA AGRICULTORES FAMILIARES E DEMAIS PÚBLICOS</t>
+          <t>MINAS REURB SEDE</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>ASSISTÊNCIA TECNICA E EXTENSÃO RURAL PARA O ESTADO DE MINAS GERAIS</t>
+          <t>POLÍTICA DE REGULARIZAÇÃO FUNDIÁRIA E DE GESTÃO DE IMÓVEIS</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>Acordo Repactuação Rio Doce</t>
+          <t>Acordo Judicial do Rio Doce</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Anexo a definir</t>
-        </is>
-      </c>
-      <c r="AD4" t="inlineStr">
-        <is>
-          <t>Instrumento de entrada a cadastrar</t>
-        </is>
+          <t>ANEXO 12</t>
+        </is>
+      </c>
+      <c r="AD4" t="n">
+        <v>9473171</v>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>Realização de diagnóstico dos pescadores da região para guiar ações de capacitação para a atividade rural e instalação de unidades produtivas de criação de peixes em tanque e assistência técnica para sua utilização</t>
+          <t>Promoção de regularização fundiária</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>Acordo Repactuação Rio Doce - Anexo a definir - Instrumento de entrada a cadastrar - Realização de diagnóstico dos pescadores da região para guiar ações de capacitação para a atividade rural e instalação de unidades produtivas de criação de peixes em tanque e assistência técnica para sua utilização</t>
+          <t>Acordo Judicial do Rio Doce - ANEXO 12 - 9473171 - Promoção de regularização fundiária</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B5" t="n">
-        <v>1230</v>
+        <v>1220</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE AGRICULTURA, PECUÁRIA E ABASTECIMENTO - SEAPA</t>
+          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO ECONÔMICO - SEDE</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -944,11 +940,11 @@
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>3041</v>
+        <v>1221</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>EMPRESA DE ASSISTÊNCIA TÉCNICA E EXTENSÃO RURAL DO ESTADO DE MINAS GERAIS - EMATER</t>
+          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO ECONÔMICO - SEDE</t>
         </is>
       </c>
       <c r="H5" t="n">
@@ -961,7 +957,7 @@
         <v>90</v>
       </c>
       <c r="K5" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="L5" t="n">
         <v>80</v>
@@ -970,87 +966,85 @@
         <v>1</v>
       </c>
       <c r="N5" t="n">
-        <v>10517</v>
+        <v>10858</v>
       </c>
       <c r="O5" t="n">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="P5" t="n">
-        <v>606</v>
+        <v>127</v>
       </c>
       <c r="Q5" t="n">
-        <v>90</v>
+        <v>125</v>
       </c>
       <c r="R5" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="S5" t="n">
-        <v>235</v>
+        <v>82</v>
       </c>
       <c r="T5" t="n">
-        <v>4235</v>
+        <v>1082</v>
       </c>
       <c r="U5" t="n">
         <v>1</v>
       </c>
       <c r="V5" t="n">
-        <v>10064443</v>
+        <v>993696</v>
       </c>
       <c r="W5" t="n">
-        <v>10064443</v>
+        <v>993696</v>
       </c>
       <c r="X5" t="n">
-        <v>10064443</v>
+        <v>993696</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>ASSISTÊNCIA TÉCNICA E EXTENSÃO RURAL PARA AGRICULTORES FAMILIARES E DEMAIS PÚBLICOS</t>
+          <t>MINAS REURB SEDE</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>ASSISTÊNCIA TECNICA E EXTENSÃO RURAL PARA O ESTADO DE MINAS GERAIS</t>
+          <t>POLÍTICA DE REGULARIZAÇÃO FUNDIÁRIA E DE GESTÃO DE IMÓVEIS</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>Acordo Repactuação Rio Doce</t>
+          <t>Acordo Judicial do Rio Doce</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Anexo a definir</t>
-        </is>
-      </c>
-      <c r="AD5" t="inlineStr">
-        <is>
-          <t>Instrumento de entrada a cadastrar</t>
-        </is>
+          <t>ANEXO 12</t>
+        </is>
+      </c>
+      <c r="AD5" t="n">
+        <v>9473171</v>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>Oferta de serviços de assistência técnica e extensão rural (metodologia ISA/PASEA), visando à produção de alimentos e estímulo à comercialização e adequação socioeconômica e ambiental de propriedades rurais</t>
+          <t>Promoção de regularização fundiária</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>Acordo Repactuação Rio Doce - Anexo a definir - Instrumento de entrada a cadastrar - Oferta de serviços de assistência técnica e extensão rural (metodologia ISA/PASEA), visando à produção de alimentos e estímulo à comercialização e adequação socioeconômica e ambiental de propriedades rurais</t>
+          <t>Acordo Judicial do Rio Doce - ANEXO 12 - 9473171 - Promoção de regularização fundiária</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B6" t="n">
-        <v>1250</v>
+        <v>1220</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>POLÍCIA MILITAR DO ESTADO DE MINAS GERAIS - PMMG</t>
+          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO ECONÔMICO - SEDE</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -1060,18 +1054,18 @@
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>1251</v>
+        <v>1221</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>POLÍCIA MILITAR DO ESTADO DE MINAS GERAIS - PMMG</t>
+          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO ECONÔMICO - SEDE</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J6" t="n">
         <v>90</v>
@@ -1086,87 +1080,85 @@
         <v>1</v>
       </c>
       <c r="N6" t="n">
-        <v>10690</v>
+        <v>10858</v>
       </c>
       <c r="O6" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="P6" t="n">
-        <v>181</v>
+        <v>127</v>
       </c>
       <c r="Q6" t="n">
-        <v>137</v>
+        <v>125</v>
       </c>
       <c r="R6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="S6" t="n">
-        <v>365</v>
+        <v>82</v>
       </c>
       <c r="T6" t="n">
-        <v>4365</v>
+        <v>1082</v>
       </c>
       <c r="U6" t="n">
         <v>1</v>
       </c>
       <c r="V6" t="n">
-        <v>1214845</v>
+        <v>269632</v>
       </c>
       <c r="W6" t="n">
-        <v>1214845</v>
+        <v>269632</v>
       </c>
       <c r="X6" t="n">
-        <v>1214845</v>
+        <v>269632</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>POLICIAMENTO OSTENSIVO GERAL</t>
+          <t>MINAS REURB SEDE</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>POLÍCIA OSTENSIVA</t>
+          <t>POLÍTICA DE REGULARIZAÇÃO FUNDIÁRIA E DE GESTÃO DE IMÓVEIS</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>Acordo Repactuação Rio Doce</t>
+          <t>Acordo Judicial do Rio Doce</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Anexo a definir</t>
-        </is>
-      </c>
-      <c r="AD6" t="inlineStr">
-        <is>
-          <t>Instrumento de entrada a cadastrar</t>
-        </is>
+          <t>ANEXO 12</t>
+        </is>
+      </c>
+      <c r="AD6" t="n">
+        <v>9473171</v>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>Adequação e equipagem de Bases de Segurança Pública (PMMG, CBMMG e PCMG) no Município de Mariana/MG</t>
+          <t>Promoção de regularização fundiária</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>Acordo Repactuação Rio Doce - Anexo a definir - Instrumento de entrada a cadastrar - Adequação e equipagem de Bases de Segurança Pública (PMMG, CBMMG e PCMG) no Município de Mariana/MG</t>
+          <t>Acordo Judicial do Rio Doce - ANEXO 12 - 9473171 - Promoção de regularização fundiária</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B7" t="n">
-        <v>1250</v>
+        <v>1220</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>POLÍCIA MILITAR DO ESTADO DE MINAS GERAIS - PMMG</t>
+          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO ECONÔMICO - SEDE</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -1176,24 +1168,24 @@
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>1251</v>
+        <v>1221</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>POLÍCIA MILITAR DO ESTADO DE MINAS GERAIS - PMMG</t>
+          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO ECONÔMICO - SEDE</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J7" t="n">
         <v>90</v>
       </c>
       <c r="K7" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="L7" t="n">
         <v>80</v>
@@ -1202,87 +1194,85 @@
         <v>1</v>
       </c>
       <c r="N7" t="n">
-        <v>10690</v>
+        <v>10858</v>
       </c>
       <c r="O7" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="P7" t="n">
-        <v>181</v>
+        <v>127</v>
       </c>
       <c r="Q7" t="n">
-        <v>137</v>
+        <v>125</v>
       </c>
       <c r="R7" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="S7" t="n">
-        <v>365</v>
+        <v>82</v>
       </c>
       <c r="T7" t="n">
-        <v>4365</v>
+        <v>1082</v>
       </c>
       <c r="U7" t="n">
         <v>1</v>
       </c>
       <c r="V7" t="n">
-        <v>4796778</v>
+        <v>7000000</v>
       </c>
       <c r="W7" t="n">
-        <v>4796778</v>
+        <v>7000000</v>
       </c>
       <c r="X7" t="n">
-        <v>4796778</v>
+        <v>7000000</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>POLICIAMENTO OSTENSIVO GERAL</t>
+          <t>MINAS REURB SEDE</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>POLÍCIA OSTENSIVA</t>
+          <t>POLÍTICA DE REGULARIZAÇÃO FUNDIÁRIA E DE GESTÃO DE IMÓVEIS</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>Acordo Repactuação Rio Doce</t>
+          <t>Acordo Judicial do Rio Doce</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Anexo a definir</t>
-        </is>
-      </c>
-      <c r="AD7" t="inlineStr">
-        <is>
-          <t>Instrumento de entrada a cadastrar</t>
-        </is>
+          <t>ANEXO 12</t>
+        </is>
+      </c>
+      <c r="AD7" t="n">
+        <v>9473171</v>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>Adequação e equipagem de Bases de Segurança Pública (PMMG, CBMMG e PCMG) no Município de Mariana/MG</t>
+          <t>Promoção de regularização fundiária</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>Acordo Repactuação Rio Doce - Anexo a definir - Instrumento de entrada a cadastrar - Adequação e equipagem de Bases de Segurança Pública (PMMG, CBMMG e PCMG) no Município de Mariana/MG</t>
+          <t>Acordo Judicial do Rio Doce - ANEXO 12 - 9473171 - Promoção de regularização fundiária</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B8" t="n">
-        <v>1250</v>
+        <v>1220</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>POLÍCIA MILITAR DO ESTADO DE MINAS GERAIS - PMMG</t>
+          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO ECONÔMICO - SEDE</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -1292,24 +1282,24 @@
         <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>1251</v>
+        <v>1221</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>POLÍCIA MILITAR DO ESTADO DE MINAS GERAIS - PMMG</t>
+          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO ECONÔMICO - SEDE</t>
         </is>
       </c>
       <c r="H8" t="n">
         <v>4</v>
       </c>
       <c r="I8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J8" t="n">
         <v>90</v>
       </c>
       <c r="K8" t="n">
-        <v>39</v>
+        <v>66</v>
       </c>
       <c r="L8" t="n">
         <v>80</v>
@@ -1318,87 +1308,87 @@
         <v>1</v>
       </c>
       <c r="N8" t="n">
-        <v>10690</v>
+        <v>11264</v>
       </c>
       <c r="O8" t="n">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="P8" t="n">
-        <v>181</v>
+        <v>334</v>
       </c>
       <c r="Q8" t="n">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="R8" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="S8" t="n">
-        <v>365</v>
+        <v>57</v>
       </c>
       <c r="T8" t="n">
-        <v>4365</v>
+        <v>1057</v>
       </c>
       <c r="U8" t="n">
         <v>1</v>
       </c>
       <c r="V8" t="n">
-        <v>6488377</v>
+        <v>40200000</v>
       </c>
       <c r="W8" t="n">
-        <v>6488377</v>
+        <v>40200000</v>
       </c>
       <c r="X8" t="n">
-        <v>6488377</v>
+        <v>40200000</v>
       </c>
       <c r="Y8" t="n">
         <v>0</v>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>POLICIAMENTO OSTENSIVO GERAL</t>
+          <t>CRÉDITO A EMPRESAS DA BACIA DO RIO DOCE</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>POLÍCIA OSTENSIVA</t>
+          <t>MINAS EMPREENDEDORA: ESTADO MAIS SIMPLES E LIVRE PARA SE EMPREENDER</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>Acordo Repactuação Rio Doce</t>
+          <t>Acordo Judicial do Rio Doce</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Anexo a definir</t>
+          <t>ANEXO 12</t>
         </is>
       </c>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>Instrumento de entrada a cadastrar</t>
+          <t>A SER CRIADO</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fortalecimento da infraestrutura e logística das unidades das forças de segurança </t>
+          <t>Criação de fundo de disponibilização de crédito para recuperação econômica de pequenas, médias e grandes empresas dos municípios atingidos, além de fundo garantidor para facilitar o acesso a essa linha de crédito</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Acordo Repactuação Rio Doce - Anexo a definir - Instrumento de entrada a cadastrar - Fortalecimento da infraestrutura e logística das unidades das forças de segurança </t>
+          <t>Acordo Judicial do Rio Doce - ANEXO 12 - A SER CRIADO - Criação de fundo de disponibilização de crédito para recuperação econômica de pequenas, médias e grandes empresas dos municípios atingidos, além de fundo garantidor para facilitar o acesso a essa linha de crédito</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B9" t="n">
-        <v>1250</v>
+        <v>1220</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>POLÍCIA MILITAR DO ESTADO DE MINAS GERAIS - PMMG</t>
+          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO ECONÔMICO - SEDE</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -1408,24 +1398,24 @@
         <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>1251</v>
+        <v>1221</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>POLÍCIA MILITAR DO ESTADO DE MINAS GERAIS - PMMG</t>
+          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO ECONÔMICO - SEDE</t>
         </is>
       </c>
       <c r="H9" t="n">
         <v>4</v>
       </c>
       <c r="I9" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J9" t="n">
         <v>90</v>
       </c>
       <c r="K9" t="n">
-        <v>52</v>
+        <v>27</v>
       </c>
       <c r="L9" t="n">
         <v>80</v>
@@ -1434,87 +1424,87 @@
         <v>1</v>
       </c>
       <c r="N9" t="n">
-        <v>10690</v>
+        <v>11265</v>
       </c>
       <c r="O9" t="n">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="P9" t="n">
-        <v>181</v>
+        <v>334</v>
       </c>
       <c r="Q9" t="n">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="R9" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="S9" t="n">
-        <v>365</v>
+        <v>59</v>
       </c>
       <c r="T9" t="n">
-        <v>4365</v>
+        <v>1059</v>
       </c>
       <c r="U9" t="n">
         <v>1</v>
       </c>
       <c r="V9" t="n">
-        <v>16390738</v>
+        <v>30000000</v>
       </c>
       <c r="W9" t="n">
-        <v>16390738</v>
+        <v>30000000</v>
       </c>
       <c r="X9" t="n">
-        <v>16390738</v>
+        <v>30000000</v>
       </c>
       <c r="Y9" t="n">
         <v>0</v>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>POLICIAMENTO OSTENSIVO GERAL</t>
+          <t>GARANTIA DE CRÉDITOS A EMPRESAS DA BACIA DO RIO DOCE</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>POLÍCIA OSTENSIVA</t>
+          <t>MINAS EMPREENDEDORA: ESTADO MAIS SIMPLES E LIVRE PARA SE EMPREENDER</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>Acordo Repactuação Rio Doce</t>
+          <t>Acordo Judicial do Rio Doce</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Anexo a definir</t>
+          <t>ANEXO 12</t>
         </is>
       </c>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>Instrumento de entrada a cadastrar</t>
+          <t>A SER CRIADO</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fortalecimento da infraestrutura e logística das unidades das forças de segurança </t>
+          <t>Criação de fundo de disponibilização de crédito para recuperação econômica de pequenas, médias e grandes empresas dos municípios atingidos, além de fundo garantidor para facilitar o acesso a essa linha de crédito</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Acordo Repactuação Rio Doce - Anexo a definir - Instrumento de entrada a cadastrar - Fortalecimento da infraestrutura e logística das unidades das forças de segurança </t>
+          <t>Acordo Judicial do Rio Doce - ANEXO 12 - A SER CRIADO - Criação de fundo de disponibilização de crédito para recuperação econômica de pequenas, médias e grandes empresas dos municípios atingidos, além de fundo garantidor para facilitar o acesso a essa linha de crédito</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B10" t="n">
-        <v>1270</v>
+        <v>1220</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE CULTURA E TURISMO - SECULT</t>
+          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO ECONÔMICO - SEDE</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -1524,11 +1514,11 @@
         <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>1271</v>
+        <v>1221</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE CULTURA E TURISMO - SECULT</t>
+          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO ECONÔMICO - SEDE</t>
         </is>
       </c>
       <c r="H10" t="n">
@@ -1541,7 +1531,7 @@
         <v>90</v>
       </c>
       <c r="K10" t="n">
-        <v>39</v>
+        <v>14</v>
       </c>
       <c r="L10" t="n">
         <v>80</v>
@@ -1550,87 +1540,87 @@
         <v>1</v>
       </c>
       <c r="N10" t="n">
-        <v>10656</v>
+        <v>11250</v>
       </c>
       <c r="O10" t="n">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="P10" t="n">
-        <v>392</v>
+        <v>691</v>
       </c>
       <c r="Q10" t="n">
-        <v>102</v>
+        <v>132</v>
       </c>
       <c r="R10" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="S10" t="n">
-        <v>343</v>
+        <v>56</v>
       </c>
       <c r="T10" t="n">
-        <v>4343</v>
+        <v>1056</v>
       </c>
       <c r="U10" t="n">
         <v>1</v>
       </c>
       <c r="V10" t="n">
-        <v>5110039</v>
+        <v>272500</v>
       </c>
       <c r="W10" t="n">
-        <v>5110039</v>
+        <v>272500</v>
       </c>
       <c r="X10" t="n">
-        <v>5110039</v>
+        <v>272500</v>
       </c>
       <c r="Y10" t="n">
         <v>0</v>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>GESTÃO DO FOMENTO E MUNICIPALIZAÇÃO DA CULTURA</t>
+          <t>FOMENTO AO COOPERATIVISMO, ASSOCIATIVISMO E ÀS MICRO E PEQUENAS EMPRESAS DA BACIA DO RIO DOCE (COOPERA + RIO DOCE)</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>FOMENTO À ECONOMIA DA CRIATIVIDADE</t>
+          <t>MINAS EMPREENDEDORA: ESTADO MAIS SIMPLES E LIVRE PARA SE EMPREENDER</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>Acordo Repactuação Rio Doce</t>
+          <t>Acordo Judicial do Rio Doce</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Anexo a definir</t>
+          <t>ANEXO 12</t>
         </is>
       </c>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>Instrumento de entrada a cadastrar</t>
+          <t>A SER CRIADO</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>Fomento à cadeia produtiva da cultura e turismo</t>
+          <t>Fomento ao associativismo e ao cooperativismo a partir de assessoria às organizações, podendo incluir aprimoramento da gestão, qualificação de produtos e serviços, apoio na comunicação e marketing, mapeamento de necessidades de infraestrutura e fornecimento de equipamentos e insumos</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>Acordo Repactuação Rio Doce - Anexo a definir - Instrumento de entrada a cadastrar - Fomento à cadeia produtiva da cultura e turismo</t>
+          <t>Acordo Judicial do Rio Doce - ANEXO 12 - A SER CRIADO - Fomento ao associativismo e ao cooperativismo a partir de assessoria às organizações, podendo incluir aprimoramento da gestão, qualificação de produtos e serviços, apoio na comunicação e marketing, mapeamento de necessidades de infraestrutura e fornecimento de equipamentos e insumos</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B11" t="n">
-        <v>1270</v>
+        <v>1220</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE CULTURA E TURISMO - SECULT</t>
+          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO ECONÔMICO - SEDE</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -1640,11 +1630,11 @@
         <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>1271</v>
+        <v>1221</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE CULTURA E TURISMO - SECULT</t>
+          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO ECONÔMICO - SEDE</t>
         </is>
       </c>
       <c r="H11" t="n">
@@ -1657,7 +1647,7 @@
         <v>90</v>
       </c>
       <c r="K11" t="n">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="L11" t="n">
         <v>80</v>
@@ -1666,87 +1656,87 @@
         <v>1</v>
       </c>
       <c r="N11" t="n">
-        <v>10634</v>
+        <v>11250</v>
       </c>
       <c r="O11" t="n">
         <v>23</v>
       </c>
       <c r="P11" t="n">
-        <v>695</v>
+        <v>691</v>
       </c>
       <c r="Q11" t="n">
-        <v>100</v>
+        <v>132</v>
       </c>
       <c r="R11" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="S11" t="n">
-        <v>324</v>
+        <v>56</v>
       </c>
       <c r="T11" t="n">
-        <v>4324</v>
+        <v>1056</v>
       </c>
       <c r="U11" t="n">
         <v>1</v>
       </c>
       <c r="V11" t="n">
-        <v>6092000</v>
+        <v>322501</v>
       </c>
       <c r="W11" t="n">
-        <v>6092000</v>
+        <v>322501</v>
       </c>
       <c r="X11" t="n">
-        <v>6092000</v>
+        <v>322501</v>
       </c>
       <c r="Y11" t="n">
         <v>0</v>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>DIVULGAÇÃO TURÍSTICA DE MINAS GERAIS</t>
+          <t>FOMENTO AO COOPERATIVISMO, ASSOCIATIVISMO E ÀS MICRO E PEQUENAS EMPRESAS DA BACIA DO RIO DOCE (COOPERA + RIO DOCE)</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>MAIS TURISTAS</t>
+          <t>MINAS EMPREENDEDORA: ESTADO MAIS SIMPLES E LIVRE PARA SE EMPREENDER</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>Acordo Repactuação Rio Doce</t>
+          <t>Acordo Judicial do Rio Doce</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Anexo a definir</t>
+          <t>ANEXO 12</t>
         </is>
       </c>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>Instrumento de entrada a cadastrar</t>
+          <t>A SER CRIADO</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>Fomento à cadeia produtiva da cultura e turismo</t>
+          <t>Fomento ao associativismo e ao cooperativismo a partir de assessoria às organizações, podendo incluir aprimoramento da gestão, qualificação de produtos e serviços, apoio na comunicação e marketing, mapeamento de necessidades de infraestrutura e fornecimento de equipamentos e insumos</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>Acordo Repactuação Rio Doce - Anexo a definir - Instrumento de entrada a cadastrar - Fomento à cadeia produtiva da cultura e turismo</t>
+          <t>Acordo Judicial do Rio Doce - ANEXO 12 - A SER CRIADO - Fomento ao associativismo e ao cooperativismo a partir de assessoria às organizações, podendo incluir aprimoramento da gestão, qualificação de produtos e serviços, apoio na comunicação e marketing, mapeamento de necessidades de infraestrutura e fornecimento de equipamentos e insumos</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B12" t="n">
-        <v>1300</v>
+        <v>1220</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE INFRAESTRUTURA, MOBILIDADE E PARCERIA - SEINFRA</t>
+          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO ECONÔMICO - SEDE</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -1756,111 +1746,113 @@
         <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>1301</v>
+        <v>1221</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE INFRAESTRUTURA, MOBILIDADE E PARCERIAS - SEINFRA</t>
+          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO ECONÔMICO - SEDE</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I12" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J12" t="n">
         <v>90</v>
       </c>
       <c r="K12" t="n">
-        <v>61</v>
+        <v>35</v>
       </c>
       <c r="L12" t="n">
-        <v>95</v>
+        <v>80</v>
       </c>
       <c r="M12" t="n">
         <v>1</v>
       </c>
       <c r="N12" t="n">
-        <v>10659</v>
+        <v>11250</v>
       </c>
       <c r="O12" t="n">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="P12" t="n">
-        <v>130</v>
+        <v>691</v>
       </c>
       <c r="Q12" t="n">
-        <v>85</v>
+        <v>132</v>
       </c>
       <c r="R12" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="S12" t="n">
-        <v>345</v>
+        <v>56</v>
       </c>
       <c r="T12" t="n">
-        <v>4345</v>
+        <v>1056</v>
       </c>
       <c r="U12" t="n">
         <v>1</v>
       </c>
       <c r="V12" t="n">
-        <v>87053233</v>
+        <v>5678875</v>
       </c>
       <c r="W12" t="n">
-        <v>87053233</v>
+        <v>5678875</v>
       </c>
       <c r="X12" t="n">
-        <v>87053233</v>
+        <v>5678875</v>
       </c>
       <c r="Y12" t="n">
         <v>0</v>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>GESTÃO DO RODOANEL METROPOLITANO</t>
+          <t>FOMENTO AO COOPERATIVISMO, ASSOCIATIVISMO E ÀS MICRO E PEQUENAS EMPRESAS DA BACIA DO RIO DOCE (COOPERA + RIO DOCE)</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>PROMOÇÃO DE CONCESSÕES E PARCERIAS</t>
+          <t>MINAS EMPREENDEDORA: ESTADO MAIS SIMPLES E LIVRE PARA SE EMPREENDER</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>Acordo Judicial Vale</t>
+          <t>Acordo Judicial do Rio Doce</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Anexo III</t>
-        </is>
-      </c>
-      <c r="AD12" t="n">
-        <v>9288180</v>
+          <t>ANEXO 12</t>
+        </is>
+      </c>
+      <c r="AD12" t="inlineStr">
+        <is>
+          <t>A SER CRIADO</t>
+        </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>Implantação do Rodoanel da Região Metropolitana de Belo Horizonte</t>
+          <t>Fomento ao associativismo e ao cooperativismo a partir de assessoria às organizações, podendo incluir aprimoramento da gestão, qualificação de produtos e serviços, apoio na comunicação e marketing, mapeamento de necessidades de infraestrutura e fornecimento de equipamentos e insumos</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>Acordo Judicial Vale - Anexo III - 9288180 - Implantação do Rodoanel da Região Metropolitana de Belo Horizonte</t>
+          <t>Acordo Judicial do Rio Doce - ANEXO 12 - A SER CRIADO - Fomento ao associativismo e ao cooperativismo a partir de assessoria às organizações, podendo incluir aprimoramento da gestão, qualificação de produtos e serviços, apoio na comunicação e marketing, mapeamento de necessidades de infraestrutura e fornecimento de equipamentos e insumos</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B13" t="n">
-        <v>1300</v>
+        <v>1220</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE INFRAESTRUTURA, MOBILIDADE E PARCERIA - SEINFRA</t>
+          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO ECONÔMICO - SEDE</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -1870,24 +1862,24 @@
         <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>2301</v>
+        <v>1221</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>DEPARTAMENTO DE ESTRADAS DE RODAGEM DO ESTADO DE MINAS GERAIS - DER-MG</t>
+          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO ECONÔMICO - SEDE</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I13" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J13" t="n">
         <v>90</v>
       </c>
       <c r="K13" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="L13" t="n">
         <v>80</v>
@@ -1896,87 +1888,87 @@
         <v>1</v>
       </c>
       <c r="N13" t="n">
-        <v>10582</v>
+        <v>11250</v>
       </c>
       <c r="O13" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="P13" t="n">
-        <v>782</v>
+        <v>691</v>
       </c>
       <c r="Q13" t="n">
-        <v>81</v>
+        <v>132</v>
       </c>
       <c r="R13" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="S13" t="n">
-        <v>287</v>
+        <v>56</v>
       </c>
       <c r="T13" t="n">
-        <v>4287</v>
+        <v>1056</v>
       </c>
       <c r="U13" t="n">
         <v>1</v>
       </c>
       <c r="V13" t="n">
-        <v>200000000</v>
+        <v>470000</v>
       </c>
       <c r="W13" t="n">
-        <v>200000000</v>
+        <v>470000</v>
       </c>
       <c r="X13" t="n">
-        <v>200000000</v>
+        <v>470000</v>
       </c>
       <c r="Y13" t="n">
         <v>0</v>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>CONSTRUÇÃO E ADEQUAÇÃO DE RODOVIAS - RIO DOCE</t>
+          <t>FOMENTO AO COOPERATIVISMO, ASSOCIATIVISMO E ÀS MICRO E PEQUENAS EMPRESAS DA BACIA DO RIO DOCE (COOPERA + RIO DOCE)</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>DESENVOLVIMENTO SUSTENTÁVEL DA INFRAESTRUTURA RODOVIÁRIA</t>
+          <t>MINAS EMPREENDEDORA: ESTADO MAIS SIMPLES E LIVRE PARA SE EMPREENDER</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>Acordo Repactuação Rio Doce</t>
+          <t>Acordo Judicial do Rio Doce</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Anexo a definir</t>
+          <t>ANEXO 12</t>
         </is>
       </c>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>Instrumento de entrada a cadastrar</t>
+          <t>A SER CRIADO</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>Cooperação Interfederativa de Infraestrutura de Mobilidade</t>
+          <t>Fomento ao associativismo e ao cooperativismo a partir de assessoria às organizações, podendo incluir aprimoramento da gestão, qualificação de produtos e serviços, apoio na comunicação e marketing, mapeamento de necessidades de infraestrutura e fornecimento de equipamentos e insumos</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>Acordo Repactuação Rio Doce - Anexo a definir - Instrumento de entrada a cadastrar - Cooperação Interfederativa de Infraestrutura de Mobilidade</t>
+          <t>Acordo Judicial do Rio Doce - ANEXO 12 - A SER CRIADO - Fomento ao associativismo e ao cooperativismo a partir de assessoria às organizações, podendo incluir aprimoramento da gestão, qualificação de produtos e serviços, apoio na comunicação e marketing, mapeamento de necessidades de infraestrutura e fornecimento de equipamentos e insumos</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B14" t="n">
-        <v>1300</v>
+        <v>1220</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE INFRAESTRUTURA, MOBILIDADE E PARCERIA - SEINFRA</t>
+          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO ECONÔMICO - SEDE</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -1986,111 +1978,113 @@
         <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>2301</v>
+        <v>1221</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>DEPARTAMENTO DE ESTRADAS DE RODAGEM DO ESTADO DE MINAS GERAIS - DER-MG</t>
+          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO ECONÔMICO - SEDE</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I14" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J14" t="n">
         <v>90</v>
       </c>
       <c r="K14" t="n">
-        <v>51</v>
+        <v>39</v>
       </c>
       <c r="L14" t="n">
-        <v>95</v>
+        <v>80</v>
       </c>
       <c r="M14" t="n">
         <v>1</v>
       </c>
       <c r="N14" t="n">
-        <v>10582</v>
+        <v>11250</v>
       </c>
       <c r="O14" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="P14" t="n">
-        <v>782</v>
+        <v>691</v>
       </c>
       <c r="Q14" t="n">
-        <v>81</v>
+        <v>132</v>
       </c>
       <c r="R14" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="S14" t="n">
-        <v>287</v>
+        <v>56</v>
       </c>
       <c r="T14" t="n">
-        <v>4287</v>
+        <v>1056</v>
       </c>
       <c r="U14" t="n">
         <v>1</v>
       </c>
       <c r="V14" t="n">
-        <v>20400000</v>
+        <v>2960000</v>
       </c>
       <c r="W14" t="n">
-        <v>20400000</v>
+        <v>2960000</v>
       </c>
       <c r="X14" t="n">
-        <v>20400000</v>
+        <v>2960000</v>
       </c>
       <c r="Y14" t="n">
         <v>0</v>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>CONSTRUÇÃO E ADEQUAÇÃO DE RODOVIAS - RIO DOCE</t>
+          <t>FOMENTO AO COOPERATIVISMO, ASSOCIATIVISMO E ÀS MICRO E PEQUENAS EMPRESAS DA BACIA DO RIO DOCE (COOPERA + RIO DOCE)</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>DESENVOLVIMENTO SUSTENTÁVEL DA INFRAESTRUTURA RODOVIÁRIA</t>
+          <t>MINAS EMPREENDEDORA: ESTADO MAIS SIMPLES E LIVRE PARA SE EMPREENDER</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>Agenda Integrada - Renova</t>
+          <t>Acordo Judicial do Rio Doce</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Sem anexo</t>
-        </is>
-      </c>
-      <c r="AD14" t="n">
-        <v>9382040</v>
+          <t>ANEXO 12</t>
+        </is>
+      </c>
+      <c r="AD14" t="inlineStr">
+        <is>
+          <t>A SER CRIADO</t>
+        </is>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>Marliéria</t>
+          <t>Fomento ao associativismo e ao cooperativismo a partir de assessoria às organizações, podendo incluir aprimoramento da gestão, qualificação de produtos e serviços, apoio na comunicação e marketing, mapeamento de necessidades de infraestrutura e fornecimento de equipamentos e insumos</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>Agenda Integrada - Renova - Sem anexo - 9382040 - Marliéria</t>
+          <t>Acordo Judicial do Rio Doce - ANEXO 12 - A SER CRIADO - Fomento ao associativismo e ao cooperativismo a partir de assessoria às organizações, podendo incluir aprimoramento da gestão, qualificação de produtos e serviços, apoio na comunicação e marketing, mapeamento de necessidades de infraestrutura e fornecimento de equipamentos e insumos</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B15" t="n">
-        <v>1300</v>
+        <v>1220</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE INFRAESTRUTURA, MOBILIDADE E PARCERIA - SEINFRA</t>
+          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO ECONÔMICO - SEDE</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -2100,11 +2094,11 @@
         <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>2301</v>
+        <v>1221</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>DEPARTAMENTO DE ESTRADAS DE RODAGEM DO ESTADO DE MINAS GERAIS - DER-MG</t>
+          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO ECONÔMICO - SEDE</t>
         </is>
       </c>
       <c r="H15" t="n">
@@ -2117,94 +2111,96 @@
         <v>90</v>
       </c>
       <c r="K15" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="L15" t="n">
-        <v>95</v>
+        <v>80</v>
       </c>
       <c r="M15" t="n">
         <v>1</v>
       </c>
       <c r="N15" t="n">
-        <v>10583</v>
+        <v>11250</v>
       </c>
       <c r="O15" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="P15" t="n">
-        <v>782</v>
+        <v>691</v>
       </c>
       <c r="Q15" t="n">
-        <v>81</v>
+        <v>132</v>
       </c>
       <c r="R15" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="S15" t="n">
-        <v>288</v>
+        <v>56</v>
       </c>
       <c r="T15" t="n">
-        <v>4288</v>
+        <v>1056</v>
       </c>
       <c r="U15" t="n">
         <v>1</v>
       </c>
       <c r="V15" t="n">
-        <v>5000000</v>
+        <v>4000000</v>
       </c>
       <c r="W15" t="n">
-        <v>5000000</v>
+        <v>4000000</v>
       </c>
       <c r="X15" t="n">
-        <v>5000000</v>
+        <v>4000000</v>
       </c>
       <c r="Y15" t="n">
         <v>0</v>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>RECUPERAÇÃO E MANUTENÇÃO DA MALHA VIÁRIA - RECUPERAÇÃO BRUMADINHO</t>
+          <t>FOMENTO AO COOPERATIVISMO, ASSOCIATIVISMO E ÀS MICRO E PEQUENAS EMPRESAS DA BACIA DO RIO DOCE (COOPERA + RIO DOCE)</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>DESENVOLVIMENTO SUSTENTÁVEL DA INFRAESTRUTURA RODOVIÁRIA</t>
+          <t>MINAS EMPREENDEDORA: ESTADO MAIS SIMPLES E LIVRE PARA SE EMPREENDER</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>Acordo Judicial Vale</t>
+          <t>Acordo Judicial do Rio Doce</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Anexo III</t>
-        </is>
-      </c>
-      <c r="AD15" t="n">
-        <v>9288133</v>
+          <t>ANEXO 12</t>
+        </is>
+      </c>
+      <c r="AD15" t="inlineStr">
+        <is>
+          <t>A SER CRIADO</t>
+        </is>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>Recuperação de rodovias pavimentadas em pior estado, conforme avaliação técnica do DER-MG/conclusão de corredor logístico estruturante, conforme critérios técnicos da SEINFRA</t>
+          <t>Fomento ao associativismo e ao cooperativismo a partir de assessoria às organizações, podendo incluir aprimoramento da gestão, qualificação de produtos e serviços, apoio na comunicação e marketing, mapeamento de necessidades de infraestrutura e fornecimento de equipamentos e insumos</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>Acordo Judicial Vale - Anexo III - 9288133 - Recuperação de rodovias pavimentadas em pior estado, conforme avaliação técnica do DER-MG/conclusão de corredor logístico estruturante, conforme critérios técnicos da SEINFRA</t>
+          <t>Acordo Judicial do Rio Doce - ANEXO 12 - A SER CRIADO - Fomento ao associativismo e ao cooperativismo a partir de assessoria às organizações, podendo incluir aprimoramento da gestão, qualificação de produtos e serviços, apoio na comunicação e marketing, mapeamento de necessidades de infraestrutura e fornecimento de equipamentos e insumos</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B16" t="n">
-        <v>1300</v>
+        <v>1230</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE INFRAESTRUTURA, MOBILIDADE E PARCERIA - SEINFRA</t>
+          <t>SECRETARIA DE ESTADO DE AGRICULTURA, PECUÁRIA E ABASTECIMENTO - SEAPA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -2214,111 +2210,113 @@
         <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>2301</v>
+        <v>1231</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>DEPARTAMENTO DE ESTRADAS DE RODAGEM DO ESTADO DE MINAS GERAIS - DER-MG</t>
+          <t>SECRETARIA DE ESTADO DE AGRICULTURA, PECUÁRIA E ABASTECIMENTO - SEAPA</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I16" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J16" t="n">
         <v>90</v>
       </c>
       <c r="K16" t="n">
-        <v>51</v>
+        <v>37</v>
       </c>
       <c r="L16" t="n">
-        <v>95</v>
+        <v>80</v>
       </c>
       <c r="M16" t="n">
         <v>1</v>
       </c>
       <c r="N16" t="n">
-        <v>10584</v>
+        <v>9559</v>
       </c>
       <c r="O16" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="P16" t="n">
-        <v>782</v>
+        <v>122</v>
       </c>
       <c r="Q16" t="n">
-        <v>81</v>
+        <v>705</v>
       </c>
       <c r="R16" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="S16" t="n">
-        <v>289</v>
+        <v>500</v>
       </c>
       <c r="T16" t="n">
-        <v>4289</v>
+        <v>2500</v>
       </c>
       <c r="U16" t="n">
         <v>1</v>
       </c>
       <c r="V16" t="n">
-        <v>186139750</v>
+        <v>440000</v>
       </c>
       <c r="W16" t="n">
-        <v>186139750</v>
+        <v>440000</v>
       </c>
       <c r="X16" t="n">
-        <v>186139750</v>
+        <v>440000</v>
       </c>
       <c r="Y16" t="n">
         <v>0</v>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>CONSTRUÇÃO E ADEQUAÇÃO DE RODOVIAS - RECUPERAÇÃO BRUMADINHO</t>
+          <t>ASSESSORAMENTO E GERENCIAMENTO DE POLÍTICAS PÚBLICAS</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>DESENVOLVIMENTO SUSTENTÁVEL DA INFRAESTRUTURA RODOVIÁRIA</t>
+          <t>APOIO ÀS POLÍTICAS PÚBLICAS</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>Acordo Judicial Vale</t>
+          <t>Acordo Judicial do Rio Doce</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Anexo III</t>
-        </is>
-      </c>
-      <c r="AD16" t="n">
-        <v>9288132</v>
+          <t>ANEXO 10</t>
+        </is>
+      </c>
+      <c r="AD16" t="inlineStr">
+        <is>
+          <t>A SER CRIADO</t>
+        </is>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>Construção de pontes em São Francisco, Manga e São Romão sobre o Rio São Francisco</t>
+          <t>A SER CRIADA</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>Acordo Judicial Vale - Anexo III - 9288132 - Construção de pontes em São Francisco, Manga e São Romão sobre o Rio São Francisco</t>
+          <t>Acordo Judicial do Rio Doce - ANEXO 10 - A SER CRIADO - A SER CRIADA</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B17" t="n">
-        <v>1300</v>
+        <v>1230</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE INFRAESTRUTURA, MOBILIDADE E PARCERIA - SEINFRA</t>
+          <t>SECRETARIA DE ESTADO DE AGRICULTURA, PECUÁRIA E ABASTECIMENTO - SEAPA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -2328,111 +2326,113 @@
         <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>4631</v>
+        <v>1231</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>FUNDO DE PAGAMENTO DE PARCERIAS PÚBLICO - PRIVADAS DE MINAS GERAIS - FPP - MG</t>
+          <t>SECRETARIA DE ESTADO DE AGRICULTURA, PECUÁRIA E ABASTECIMENTO - SEAPA</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I17" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J17" t="n">
-        <v>67</v>
+        <v>90</v>
       </c>
       <c r="K17" t="n">
-        <v>83</v>
+        <v>32</v>
       </c>
       <c r="L17" t="n">
-        <v>95</v>
+        <v>80</v>
       </c>
       <c r="M17" t="n">
         <v>1</v>
       </c>
       <c r="N17" t="n">
-        <v>10500</v>
+        <v>10674</v>
       </c>
       <c r="O17" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="P17" t="n">
-        <v>130</v>
+        <v>608</v>
       </c>
       <c r="Q17" t="n">
-        <v>85</v>
+        <v>108</v>
       </c>
       <c r="R17" t="n">
         <v>4</v>
       </c>
       <c r="S17" t="n">
-        <v>220</v>
+        <v>358</v>
       </c>
       <c r="T17" t="n">
-        <v>4220</v>
+        <v>4358</v>
       </c>
       <c r="U17" t="n">
         <v>1</v>
       </c>
       <c r="V17" t="n">
-        <v>737946767</v>
+        <v>2132231</v>
       </c>
       <c r="W17" t="n">
-        <v>737946767</v>
+        <v>2132231</v>
       </c>
       <c r="X17" t="n">
-        <v>737946767</v>
+        <v>2132231</v>
       </c>
       <c r="Y17" t="n">
         <v>0</v>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>RODOANEL METROPOLITANO DE BELO HORIZONTE</t>
+          <t>CIRCUITOS DE COMERCIALIZAÇÃO E MERCADOS INSTITUCIONAIS</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>PROMOÇÃO DE CONCESSÕES E PARCERIAS</t>
+          <t>ACESSO A MERCADOS</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>Acordo Judicial Vale</t>
+          <t>Acordo Judicial do Rio Doce</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Anexo III</t>
-        </is>
-      </c>
-      <c r="AD17" t="n">
-        <v>9288180</v>
+          <t>ANEXO 10</t>
+        </is>
+      </c>
+      <c r="AD17" t="inlineStr">
+        <is>
+          <t>A SER CRIADO</t>
+        </is>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>Implantação do Rodoanel da Região Metropolitana de Belo Horizonte</t>
+          <t>A SER CRIADA</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>Acordo Judicial Vale - Anexo III - 9288180 - Implantação do Rodoanel da Região Metropolitana de Belo Horizonte</t>
+          <t>Acordo Judicial do Rio Doce - ANEXO 10 - A SER CRIADO - A SER CRIADA</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B18" t="n">
-        <v>1320</v>
+        <v>1230</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE SAÚDE - SES</t>
+          <t>SECRETARIA DE ESTADO DE AGRICULTURA, PECUÁRIA E ABASTECIMENTO - SEAPA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -2442,24 +2442,24 @@
         <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>4291</v>
+        <v>1231</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>FUNDO ESTADUAL DE SAÚDE - FES</t>
+          <t>SECRETARIA DE ESTADO DE AGRICULTURA, PECUÁRIA E ABASTECIMENTO - SEAPA</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I18" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J18" t="n">
-        <v>90</v>
+        <v>50</v>
       </c>
       <c r="K18" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="L18" t="n">
         <v>80</v>
@@ -2468,87 +2468,85 @@
         <v>1</v>
       </c>
       <c r="N18" t="n">
-        <v>10384</v>
+        <v>10720</v>
       </c>
       <c r="O18" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="P18" t="n">
-        <v>301</v>
+        <v>608</v>
       </c>
       <c r="Q18" t="n">
-        <v>60</v>
+        <v>111</v>
       </c>
       <c r="R18" t="n">
         <v>4</v>
       </c>
       <c r="S18" t="n">
-        <v>125</v>
+        <v>383</v>
       </c>
       <c r="T18" t="n">
-        <v>4125</v>
+        <v>4383</v>
       </c>
       <c r="U18" t="n">
         <v>1</v>
       </c>
       <c r="V18" t="n">
-        <v>105000000</v>
+        <v>1634900</v>
       </c>
       <c r="W18" t="n">
-        <v>105000000</v>
+        <v>1634900</v>
       </c>
       <c r="X18" t="n">
-        <v>105000000</v>
+        <v>1634900</v>
       </c>
       <c r="Y18" t="n">
         <v>0</v>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>FORTALECIMENTO DA ATENÇÃO PRIMÁRIA À SAÚDE</t>
+          <t>DESENVOLVIMENTO RURAL SUSTENTÁVEL E AGRICULTURA FAMILIAR</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>ATENÇÃO PRIMÁRIA À SAÚDE</t>
+          <t>DESENVOLVIMENTO DAS CADEIAS PRODUTIVAS DA AGROPECUÁRIA</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>Acordo Repactuação Rio Doce</t>
+          <t>Acordo Judicial do Rio Doce</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Anexo a definir</t>
-        </is>
-      </c>
-      <c r="AD18" t="inlineStr">
-        <is>
-          <t>Instrumento de entrada a cadastrar</t>
-        </is>
+          <t>ANEXO 12</t>
+        </is>
+      </c>
+      <c r="AD18" t="n">
+        <v>9456616</v>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>Fortalecimento da Atenção Primária à Saúde</t>
+          <t>Atualização e realização de novos estudos de Zoneamento Ambiental Produtivo em sub-bacias hidrográficas da Bacia Hidrográfica do rio Doce</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>Acordo Repactuação Rio Doce - Anexo a definir - Instrumento de entrada a cadastrar - Fortalecimento da Atenção Primária à Saúde</t>
+          <t>Acordo Judicial do Rio Doce - ANEXO 12 - 9456616 - Atualização e realização de novos estudos de Zoneamento Ambiental Produtivo em sub-bacias hidrográficas da Bacia Hidrográfica do rio Doce</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B19" t="n">
-        <v>1320</v>
+        <v>1230</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE SAÚDE - SES</t>
+          <t>SECRETARIA DE ESTADO DE AGRICULTURA, PECUÁRIA E ABASTECIMENTO - SEAPA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -2558,24 +2556,24 @@
         <v>0</v>
       </c>
       <c r="F19" t="n">
-        <v>4291</v>
+        <v>1231</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>FUNDO ESTADUAL DE SAÚDE - FES</t>
+          <t>SECRETARIA DE ESTADO DE AGRICULTURA, PECUÁRIA E ABASTECIMENTO - SEAPA</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I19" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J19" t="n">
         <v>90</v>
       </c>
       <c r="K19" t="n">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="L19" t="n">
         <v>80</v>
@@ -2584,87 +2582,87 @@
         <v>1</v>
       </c>
       <c r="N19" t="n">
-        <v>10384</v>
+        <v>10720</v>
       </c>
       <c r="O19" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="P19" t="n">
-        <v>301</v>
+        <v>608</v>
       </c>
       <c r="Q19" t="n">
-        <v>60</v>
+        <v>111</v>
       </c>
       <c r="R19" t="n">
         <v>4</v>
       </c>
       <c r="S19" t="n">
-        <v>125</v>
+        <v>383</v>
       </c>
       <c r="T19" t="n">
-        <v>4125</v>
+        <v>4383</v>
       </c>
       <c r="U19" t="n">
         <v>1</v>
       </c>
       <c r="V19" t="n">
-        <v>5000000</v>
+        <v>407776</v>
       </c>
       <c r="W19" t="n">
-        <v>5000000</v>
+        <v>407776</v>
       </c>
       <c r="X19" t="n">
-        <v>5000000</v>
+        <v>407776</v>
       </c>
       <c r="Y19" t="n">
         <v>0</v>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>FORTALECIMENTO DA ATENÇÃO PRIMÁRIA À SAÚDE</t>
+          <t>DESENVOLVIMENTO RURAL SUSTENTÁVEL E AGRICULTURA FAMILIAR</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>ATENÇÃO PRIMÁRIA À SAÚDE</t>
+          <t>DESENVOLVIMENTO DAS CADEIAS PRODUTIVAS DA AGROPECUÁRIA</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>Acordo Repactuação Rio Doce</t>
+          <t>Acordo Judicial do Rio Doce</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Anexo a definir</t>
+          <t>ANEXO 10</t>
         </is>
       </c>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>Instrumento de entrada a cadastrar</t>
+          <t>A SER CRIADO</t>
         </is>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>Fortalecimento da Rede de Atenção Psicossocial</t>
+          <t>A SER CRIADA</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>Acordo Repactuação Rio Doce - Anexo a definir - Instrumento de entrada a cadastrar - Fortalecimento da Rede de Atenção Psicossocial</t>
+          <t>Acordo Judicial do Rio Doce - ANEXO 10 - A SER CRIADO - A SER CRIADA</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B20" t="n">
-        <v>1370</v>
+        <v>1230</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE MEIO AMBIENTE E DESENVOLVIMENTO SUSTENTÁVEL - SEMAD</t>
+          <t>SECRETARIA DE ESTADO DE AGRICULTURA, PECUÁRIA E ABASTECIMENTO - SEAPA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -2674,24 +2672,24 @@
         <v>0</v>
       </c>
       <c r="F20" t="n">
-        <v>1371</v>
+        <v>1231</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE MEIO AMBIENTE E DESENVOLVIMENTO SUSTENTÁVEL - SEMAD</t>
+          <t>SECRETARIA DE ESTADO DE AGRICULTURA, PECUÁRIA E ABASTECIMENTO - SEAPA</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I20" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J20" t="n">
         <v>90</v>
       </c>
       <c r="K20" t="n">
-        <v>39</v>
+        <v>52</v>
       </c>
       <c r="L20" t="n">
         <v>80</v>
@@ -2700,87 +2698,85 @@
         <v>1</v>
       </c>
       <c r="N20" t="n">
-        <v>10263</v>
+        <v>10764</v>
       </c>
       <c r="O20" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="P20" t="n">
-        <v>541</v>
+        <v>608</v>
       </c>
       <c r="Q20" t="n">
-        <v>27</v>
+        <v>111</v>
       </c>
       <c r="R20" t="n">
         <v>4</v>
       </c>
       <c r="S20" t="n">
-        <v>46</v>
+        <v>420</v>
       </c>
       <c r="T20" t="n">
-        <v>4046</v>
+        <v>4420</v>
       </c>
       <c r="U20" t="n">
         <v>1</v>
       </c>
       <c r="V20" t="n">
-        <v>2500000</v>
+        <v>30000000</v>
       </c>
       <c r="W20" t="n">
-        <v>2500000</v>
+        <v>30000000</v>
       </c>
       <c r="X20" t="n">
-        <v>2500000</v>
+        <v>30000000</v>
       </c>
       <c r="Y20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>MUDANÇAS CLIMÁTICAS E QUALIDADE AMBIENTAL</t>
+          <t>MECANIZAÇÃO NO CAMPO</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>GESTÃO AMBIENTAL.</t>
+          <t>DESENVOLVIMENTO DAS CADEIAS PRODUTIVAS DA AGROPECUÁRIA</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>Acordo Repactuação Rio Doce</t>
+          <t>Acordo Judicial do Rio Doce</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Anexo a definir</t>
-        </is>
-      </c>
-      <c r="AD20" t="inlineStr">
-        <is>
-          <t>Instrumento de entrada a cadastrar</t>
-        </is>
+          <t>ANEXO 12</t>
+        </is>
+      </c>
+      <c r="AD20" t="n">
+        <v>9474703</v>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>Planejamento e execução de estratégias para adequação dos municípios mineiros às mudanças climáticas, visando à redução de riscos potenciais</t>
+          <t>Adequação de infraestrutura em áreas rurais</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>Acordo Repactuação Rio Doce - Anexo a definir - Instrumento de entrada a cadastrar - Planejamento e execução de estratégias para adequação dos municípios mineiros às mudanças climáticas, visando à redução de riscos potenciais</t>
+          <t>Acordo Judicial do Rio Doce - ANEXO 12 - 9474703 - Adequação de infraestrutura em áreas rurais</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B21" t="n">
-        <v>1370</v>
+        <v>1230</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE MEIO AMBIENTE E DESENVOLVIMENTO SUSTENTÁVEL - SEMAD</t>
+          <t>SECRETARIA DE ESTADO DE AGRICULTURA, PECUÁRIA E ABASTECIMENTO - SEAPA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -2790,11 +2786,11 @@
         <v>0</v>
       </c>
       <c r="F21" t="n">
-        <v>2101</v>
+        <v>1231</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>INSTITUTO ESTADUAL DE FLORESTAS - IEF</t>
+          <t>SECRETARIA DE ESTADO DE AGRICULTURA, PECUÁRIA E ABASTECIMENTO - SEAPA</t>
         </is>
       </c>
       <c r="H21" t="n">
@@ -2807,7 +2803,7 @@
         <v>90</v>
       </c>
       <c r="K21" t="n">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="L21" t="n">
         <v>80</v>
@@ -2816,87 +2812,87 @@
         <v>1</v>
       </c>
       <c r="N21" t="n">
-        <v>10276</v>
+        <v>10744</v>
       </c>
       <c r="O21" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="P21" t="n">
-        <v>541</v>
+        <v>608</v>
       </c>
       <c r="Q21" t="n">
-        <v>31</v>
+        <v>112</v>
       </c>
       <c r="R21" t="n">
         <v>4</v>
       </c>
       <c r="S21" t="n">
-        <v>59</v>
+        <v>403</v>
       </c>
       <c r="T21" t="n">
-        <v>4059</v>
+        <v>4403</v>
       </c>
       <c r="U21" t="n">
         <v>1</v>
       </c>
       <c r="V21" t="n">
-        <v>28156764</v>
+        <v>5641567</v>
       </c>
       <c r="W21" t="n">
-        <v>28156764</v>
+        <v>5641567</v>
       </c>
       <c r="X21" t="n">
-        <v>28156764</v>
+        <v>5641567</v>
       </c>
       <c r="Y21" t="n">
         <v>0</v>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>GESTÃO DE UNIDADES E CONSERVAÇÃO</t>
+          <t>MINAS AGROINDÚSTRIA</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>PROTEÇÃO DAS ÁREAS AMBIENTALMENTE CONSERVADAS, DA FAUNA E DA BIODIVERSIDADE FLORESTAL</t>
+          <t>CERTIFICAÇÕES E HABILITAÇÕES DE PRODUTOS AGROPECUÁRIOS E AGROINDUSTRIAIS</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>Acordo Repactuação Rio Doce</t>
+          <t>Acordo Judicial do Rio Doce</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Anexo a definir</t>
+          <t>ANEXO 10</t>
         </is>
       </c>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>Instrumento de entrada a cadastrar</t>
+          <t>A SER CRIADO</t>
         </is>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>Revitalização aquática da bacia hidrográfica do rio Doce, a partir do mapeamento de áreas estratégicas para revitalização e conservação da fauna e flora aquáticas, em especial áreas de cabeceiras, tributários e rotas de piracema, e execução de ações como zoneamento pesqueiro; desassoreamento; reconformação de calhas de rios; renaturalização de leitos de rios; reintrodução de espécies aquáticas ameaçadas; educação ambiental, dentre outras ações baseadas na natureza para a revitalização intracalha do rio Doce e seus tributários</t>
+          <t>A SER CRIADA</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>Acordo Repactuação Rio Doce - Anexo a definir - Instrumento de entrada a cadastrar - Revitalização aquática da bacia hidrográfica do rio Doce, a partir do mapeamento de áreas estratégicas para revitalização e conservação da fauna e flora aquáticas, em especial áreas de cabeceiras, tributários e rotas de piracema, e execução de ações como zoneamento pesqueiro; desassoreamento; reconformação de calhas de rios; renaturalização de leitos de rios; reintrodução de espécies aquáticas ameaçadas; educação ambiental, dentre outras ações baseadas na natureza para a revitalização intracalha do rio Doce e seus tributários</t>
+          <t>Acordo Judicial do Rio Doce - ANEXO 10 - A SER CRIADO - A SER CRIADA</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B22" t="n">
-        <v>1370</v>
+        <v>1230</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE MEIO AMBIENTE E DESENVOLVIMENTO SUSTENTÁVEL - SEMAD</t>
+          <t>SECRETARIA DE ESTADO DE AGRICULTURA, PECUÁRIA E ABASTECIMENTO - SEAPA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -2906,11 +2902,11 @@
         <v>0</v>
       </c>
       <c r="F22" t="n">
-        <v>2101</v>
+        <v>2371</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>INSTITUTO ESTADUAL DE FLORESTAS - IEF</t>
+          <t>INSTITUTO MINEIRO DE AGROPECUÁRIA - IMA</t>
         </is>
       </c>
       <c r="H22" t="n">
@@ -2932,87 +2928,87 @@
         <v>1</v>
       </c>
       <c r="N22" t="n">
-        <v>10276</v>
+        <v>10521</v>
       </c>
       <c r="O22" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="P22" t="n">
-        <v>541</v>
+        <v>609</v>
       </c>
       <c r="Q22" t="n">
-        <v>31</v>
+        <v>78</v>
       </c>
       <c r="R22" t="n">
         <v>4</v>
       </c>
       <c r="S22" t="n">
-        <v>59</v>
+        <v>238</v>
       </c>
       <c r="T22" t="n">
-        <v>4059</v>
+        <v>4238</v>
       </c>
       <c r="U22" t="n">
         <v>1</v>
       </c>
       <c r="V22" t="n">
-        <v>81197000</v>
+        <v>6874243</v>
       </c>
       <c r="W22" t="n">
-        <v>81197000</v>
+        <v>6874243</v>
       </c>
       <c r="X22" t="n">
-        <v>81197000</v>
+        <v>6874243</v>
       </c>
       <c r="Y22" t="n">
         <v>0</v>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>GESTÃO DE UNIDADES E CONSERVAÇÃO</t>
+          <t>REESTRUTURAÇÃO DO LABORATÓRIO DE QUÍMICA AGROPECUÁRIA DO INSTITUTO MINEIRO DE AGROPECUÁRIA.</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>PROTEÇÃO DAS ÁREAS AMBIENTALMENTE CONSERVADAS, DA FAUNA E DA BIODIVERSIDADE FLORESTAL</t>
+          <t>DEFESA SANITÁRIA</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>Acordo Repactuação Rio Doce</t>
+          <t>Acordo Judicial do Rio Doce</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Anexo a definir</t>
+          <t>ANEXO 10</t>
         </is>
       </c>
       <c r="AD22" t="inlineStr">
         <is>
-          <t>Instrumento de entrada a cadastrar</t>
+          <t>A SER CRIADO</t>
         </is>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>Recuperação da vegetação nativa na bacia hidrográfica do rio Doce, com prioridade às áreas de mata ripária, por meio de projetos de reflorestamento, pagamento de serviços ambientais, mapeamento do uso de solo e investimento tecnológico para monitoramento da vegetação nativa e sua recuperação</t>
+          <t>A SER CRIADA</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>Acordo Repactuação Rio Doce - Anexo a definir - Instrumento de entrada a cadastrar - Recuperação da vegetação nativa na bacia hidrográfica do rio Doce, com prioridade às áreas de mata ripária, por meio de projetos de reflorestamento, pagamento de serviços ambientais, mapeamento do uso de solo e investimento tecnológico para monitoramento da vegetação nativa e sua recuperação</t>
+          <t>Acordo Judicial do Rio Doce - ANEXO 10 - A SER CRIADO - A SER CRIADA</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B23" t="n">
-        <v>1370</v>
+        <v>1230</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE MEIO AMBIENTE E DESENVOLVIMENTO SUSTENTÁVEL - SEMAD</t>
+          <t>SECRETARIA DE ESTADO DE AGRICULTURA, PECUÁRIA E ABASTECIMENTO - SEAPA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -3022,11 +3018,11 @@
         <v>0</v>
       </c>
       <c r="F23" t="n">
-        <v>2101</v>
+        <v>3041</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>INSTITUTO ESTADUAL DE FLORESTAS - IEF</t>
+          <t>EMPRESA DE ASSISTÊNCIA TÉCNICA E EXTENSÃO RURAL DO ESTADO DE MINAS GERAIS - EMATER</t>
         </is>
       </c>
       <c r="H23" t="n">
@@ -3039,7 +3035,7 @@
         <v>90</v>
       </c>
       <c r="K23" t="n">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="L23" t="n">
         <v>80</v>
@@ -3048,87 +3044,87 @@
         <v>1</v>
       </c>
       <c r="N23" t="n">
-        <v>10276</v>
+        <v>10518</v>
       </c>
       <c r="O23" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="P23" t="n">
-        <v>541</v>
+        <v>608</v>
       </c>
       <c r="Q23" t="n">
-        <v>31</v>
+        <v>97</v>
       </c>
       <c r="R23" t="n">
         <v>4</v>
       </c>
       <c r="S23" t="n">
-        <v>59</v>
+        <v>236</v>
       </c>
       <c r="T23" t="n">
-        <v>4059</v>
+        <v>4236</v>
       </c>
       <c r="U23" t="n">
         <v>1</v>
       </c>
       <c r="V23" t="n">
-        <v>69722564</v>
+        <v>16000000</v>
       </c>
       <c r="W23" t="n">
-        <v>69722564</v>
+        <v>16000000</v>
       </c>
       <c r="X23" t="n">
-        <v>69722564</v>
+        <v>16000000</v>
       </c>
       <c r="Y23" t="n">
         <v>0</v>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>GESTÃO DE UNIDADES E CONSERVAÇÃO</t>
+          <t>FOMENTO PARA O DESENVOLVIMENTO DO SETOR AGROPECUÁRIO</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>PROTEÇÃO DAS ÁREAS AMBIENTALMENTE CONSERVADAS, DA FAUNA E DA BIODIVERSIDADE FLORESTAL</t>
+          <t>MINAS SEM FOME</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>Acordo Repactuação Rio Doce</t>
+          <t>Acordo Judicial do Rio Doce</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Anexo a definir</t>
+          <t>ANEXO 12</t>
         </is>
       </c>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>Instrumento de entrada a cadastrar</t>
+          <t>A SER CRIADO</t>
         </is>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>Consolidação de unidades de conservação estaduais na bacia hidrográfica do rio Doce, a partir do investimento e custeio de suas estruturas e serviços prestados, de acordo com seus objetivos de criação; criação, se necessário, de nova(s) unidade(s) de conservação na bacia hidrográfica do rio Doce de acordo com mapeamento de áreas prioritárias para conservação; realização de atividades de prevenção e combate a incêndios e regularização fundiária das unidades de conservação</t>
+          <t>Oferta de serviços de assistência técnica e extensão rural (metodologia ISA/PASEA), visando à produção de alimentos e estímulo à comercialização e adequação socioeconômica e ambiental de propriedades rurais</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
         <is>
-          <t>Acordo Repactuação Rio Doce - Anexo a definir - Instrumento de entrada a cadastrar - Consolidação de unidades de conservação estaduais na bacia hidrográfica do rio Doce, a partir do investimento e custeio de suas estruturas e serviços prestados, de acordo com seus objetivos de criação; criação, se necessário, de nova(s) unidade(s) de conservação na bacia hidrográfica do rio Doce de acordo com mapeamento de áreas prioritárias para conservação; realização de atividades de prevenção e combate a incêndios e regularização fundiária das unidades de conservação</t>
+          <t>Acordo Judicial do Rio Doce - ANEXO 12 - A SER CRIADO - Oferta de serviços de assistência técnica e extensão rural (metodologia ISA/PASEA), visando à produção de alimentos e estímulo à comercialização e adequação socioeconômica e ambiental de propriedades rurais</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B24" t="n">
-        <v>1370</v>
+        <v>1230</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE MEIO AMBIENTE E DESENVOLVIMENTO SUSTENTÁVEL - SEMAD</t>
+          <t>SECRETARIA DE ESTADO DE AGRICULTURA, PECUÁRIA E ABASTECIMENTO - SEAPA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -3138,11 +3134,11 @@
         <v>0</v>
       </c>
       <c r="F24" t="n">
-        <v>2101</v>
+        <v>3041</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>INSTITUTO ESTADUAL DE FLORESTAS - IEF</t>
+          <t>EMPRESA DE ASSISTÊNCIA TÉCNICA E EXTENSÃO RURAL DO ESTADO DE MINAS GERAIS - EMATER</t>
         </is>
       </c>
       <c r="H24" t="n">
@@ -3164,87 +3160,87 @@
         <v>1</v>
       </c>
       <c r="N24" t="n">
-        <v>10276</v>
+        <v>10518</v>
       </c>
       <c r="O24" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="P24" t="n">
-        <v>541</v>
+        <v>608</v>
       </c>
       <c r="Q24" t="n">
-        <v>31</v>
+        <v>97</v>
       </c>
       <c r="R24" t="n">
         <v>4</v>
       </c>
       <c r="S24" t="n">
-        <v>59</v>
+        <v>236</v>
       </c>
       <c r="T24" t="n">
-        <v>4059</v>
+        <v>4236</v>
       </c>
       <c r="U24" t="n">
         <v>1</v>
       </c>
       <c r="V24" t="n">
-        <v>7657500</v>
+        <v>24000000</v>
       </c>
       <c r="W24" t="n">
-        <v>7657500</v>
+        <v>24000000</v>
       </c>
       <c r="X24" t="n">
-        <v>7657500</v>
+        <v>24000000</v>
       </c>
       <c r="Y24" t="n">
         <v>0</v>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>GESTÃO DE UNIDADES E CONSERVAÇÃO</t>
+          <t>FOMENTO PARA O DESENVOLVIMENTO DO SETOR AGROPECUÁRIO</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>PROTEÇÃO DAS ÁREAS AMBIENTALMENTE CONSERVADAS, DA FAUNA E DA BIODIVERSIDADE FLORESTAL</t>
+          <t>MINAS SEM FOME</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>Acordo Repactuação Rio Doce</t>
+          <t>Acordo Judicial do Rio Doce</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Anexo a definir</t>
+          <t>ANEXO 12</t>
         </is>
       </c>
       <c r="AD24" t="inlineStr">
         <is>
-          <t>Instrumento de entrada a cadastrar</t>
+          <t>A SER CRIADO</t>
         </is>
       </c>
       <c r="AE24" t="inlineStr">
         <is>
-          <t>Fortalecimento da política pública de gestão do manejo da fauna silvestre, de acordo com mapeamento de necessidades a ser detalhado, a partir de ações como da estruturação e custeio dos serviços prestados pelos Cetras que atendam à bacia hidrográfica do rio Doce; contratação de serviços veterinários especializados; construção de viveiros em áreas de parceiros para a reabilitação e conservação da fauna</t>
+          <t>Oferta de serviços de assistência técnica e extensão rural (metodologia ISA/PASEA), visando à produção de alimentos e estímulo à comercialização e adequação socioeconômica e ambiental de propriedades rurais</t>
         </is>
       </c>
       <c r="AF24" t="inlineStr">
         <is>
-          <t>Acordo Repactuação Rio Doce - Anexo a definir - Instrumento de entrada a cadastrar - Fortalecimento da política pública de gestão do manejo da fauna silvestre, de acordo com mapeamento de necessidades a ser detalhado, a partir de ações como da estruturação e custeio dos serviços prestados pelos Cetras que atendam à bacia hidrográfica do rio Doce; contratação de serviços veterinários especializados; construção de viveiros em áreas de parceiros para a reabilitação e conservação da fauna</t>
+          <t>Acordo Judicial do Rio Doce - ANEXO 12 - A SER CRIADO - Oferta de serviços de assistência técnica e extensão rural (metodologia ISA/PASEA), visando à produção de alimentos e estímulo à comercialização e adequação socioeconômica e ambiental de propriedades rurais</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B25" t="n">
-        <v>1370</v>
+        <v>1300</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE MEIO AMBIENTE E DESENVOLVIMENTO SUSTENTÁVEL - SEMAD</t>
+          <t>SECRETARIA DE ESTADO DE INFRAESTRUTURA, MOBILIDADE E PARCERIA - SEINFRA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -3254,113 +3250,111 @@
         <v>0</v>
       </c>
       <c r="F25" t="n">
-        <v>2101</v>
+        <v>1301</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>INSTITUTO ESTADUAL DE FLORESTAS - IEF</t>
+          <t>SECRETARIA DE ESTADO DE INFRAESTRUTURA, MOBILIDADE E PARCERIAS - SEINFRA</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I25" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J25" t="n">
         <v>90</v>
       </c>
       <c r="K25" t="n">
-        <v>39</v>
+        <v>61</v>
       </c>
       <c r="L25" t="n">
-        <v>80</v>
+        <v>95</v>
       </c>
       <c r="M25" t="n">
         <v>1</v>
       </c>
       <c r="N25" t="n">
-        <v>10276</v>
+        <v>10659</v>
       </c>
       <c r="O25" t="n">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="P25" t="n">
-        <v>541</v>
+        <v>130</v>
       </c>
       <c r="Q25" t="n">
-        <v>31</v>
+        <v>85</v>
       </c>
       <c r="R25" t="n">
         <v>4</v>
       </c>
       <c r="S25" t="n">
-        <v>59</v>
+        <v>345</v>
       </c>
       <c r="T25" t="n">
-        <v>4059</v>
+        <v>4345</v>
       </c>
       <c r="U25" t="n">
         <v>1</v>
       </c>
       <c r="V25" t="n">
-        <v>13415406</v>
+        <v>324155748</v>
       </c>
       <c r="W25" t="n">
-        <v>13415406</v>
+        <v>324155748</v>
       </c>
       <c r="X25" t="n">
-        <v>13415406</v>
+        <v>324155748</v>
       </c>
       <c r="Y25" t="n">
         <v>0</v>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>GESTÃO DE UNIDADES E CONSERVAÇÃO</t>
+          <t>GESTÃO DO RODOANEL METROPOLITANO</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>PROTEÇÃO DAS ÁREAS AMBIENTALMENTE CONSERVADAS, DA FAUNA E DA BIODIVERSIDADE FLORESTAL</t>
+          <t>PROMOÇÃO DE CONCESSÕES E PARCERIAS</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>Acordo Repactuação Rio Doce</t>
+          <t>Acordo Judicial Vale</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Anexo a definir</t>
-        </is>
-      </c>
-      <c r="AD25" t="inlineStr">
-        <is>
-          <t>Instrumento de entrada a cadastrar</t>
-        </is>
+          <t>III</t>
+        </is>
+      </c>
+      <c r="AD25" t="n">
+        <v>9288180</v>
       </c>
       <c r="AE25" t="inlineStr">
         <is>
-          <t>Aquisição de materiais, equipamentos e capacitações para modernização da fiscalização ambiental e viabilização da implantação de serviços de inteligência em fiscalização no Sistema Estadual do Meio Ambiente de Minas Gerais</t>
+          <t>Implantação do Rodoanel da Região Metropolitana de Belo Horizonte</t>
         </is>
       </c>
       <c r="AF25" t="inlineStr">
         <is>
-          <t>Acordo Repactuação Rio Doce - Anexo a definir - Instrumento de entrada a cadastrar - Aquisição de materiais, equipamentos e capacitações para modernização da fiscalização ambiental e viabilização da implantação de serviços de inteligência em fiscalização no Sistema Estadual do Meio Ambiente de Minas Gerais</t>
+          <t>Acordo Judicial Vale - III - 9288180 - Implantação do Rodoanel da Região Metropolitana de Belo Horizonte</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B26" t="n">
-        <v>1400</v>
+        <v>1300</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>CORPO DE BOMBEIROS MILITAR DO ESTADO DE MINAS GERAIS - CBMMG</t>
+          <t>SECRETARIA DE ESTADO DE INFRAESTRUTURA, MOBILIDADE E PARCERIA - SEINFRA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -3370,11 +3364,11 @@
         <v>0</v>
       </c>
       <c r="F26" t="n">
-        <v>1401</v>
+        <v>1301</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>CORPO DE BOMBEIROS MILITAR DO ESTADO DE MINAS GERAIS - CBMMG</t>
+          <t>SECRETARIA DE ESTADO DE INFRAESTRUTURA, MOBILIDADE E PARCERIAS - SEINFRA</t>
         </is>
       </c>
       <c r="H26" t="n">
@@ -3390,93 +3384,91 @@
         <v>39</v>
       </c>
       <c r="L26" t="n">
-        <v>80</v>
+        <v>95</v>
       </c>
       <c r="M26" t="n">
         <v>1</v>
       </c>
       <c r="N26" t="n">
-        <v>10377</v>
+        <v>10552</v>
       </c>
       <c r="O26" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="P26" t="n">
-        <v>182</v>
+        <v>451</v>
       </c>
       <c r="Q26" t="n">
-        <v>52</v>
+        <v>99</v>
       </c>
       <c r="R26" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="S26" t="n">
-        <v>120</v>
+        <v>40</v>
       </c>
       <c r="T26" t="n">
-        <v>4120</v>
+        <v>1040</v>
       </c>
       <c r="U26" t="n">
         <v>1</v>
       </c>
       <c r="V26" t="n">
-        <v>6250000</v>
+        <v>1000</v>
       </c>
       <c r="W26" t="n">
-        <v>6250000</v>
+        <v>1000</v>
       </c>
       <c r="X26" t="n">
-        <v>6250000</v>
+        <v>1000</v>
       </c>
       <c r="Y26" t="n">
         <v>0</v>
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>MODERNIZAÇÃO E ESTRUTURAÇÃO DO CORPO DE BOMBEIROS MILITAR DE MINAS GERAIS</t>
+          <t>REQUALIFICAÇÃO URBANA E AMBIENTAL E CONTROLE DE CHEIAS DO CÓRREGO FERRUGEM - PAC FERRUGEM (VALE)</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>PROMOÇÃO DE DEFESA CIVIL</t>
+          <t>DESENVOLVIMENTO DA INFRAESTRUTURA ESTADUAL, MUNICIPAL E REGIONAL</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>Acordo Repactuação Rio Doce</t>
+          <t>Acordo Judicial Vale</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Anexo a definir</t>
-        </is>
-      </c>
-      <c r="AD26" t="inlineStr">
-        <is>
-          <t>Instrumento de entrada a cadastrar</t>
-        </is>
+          <t>IV</t>
+        </is>
+      </c>
+      <c r="AD26" t="n">
+        <v>9288178</v>
       </c>
       <c r="AE26" t="inlineStr">
         <is>
-          <t>Adequação e equipagem de Bases de Segurança Pública (PMMG, CBMMG e PCMG) no Município de Mariana/MG</t>
+          <t>Prevenção de Enchentes - Construção de Bacias de Contenção no Córrego Ferrugem</t>
         </is>
       </c>
       <c r="AF26" t="inlineStr">
         <is>
-          <t>Acordo Repactuação Rio Doce - Anexo a definir - Instrumento de entrada a cadastrar - Adequação e equipagem de Bases de Segurança Pública (PMMG, CBMMG e PCMG) no Município de Mariana/MG</t>
+          <t>Acordo Judicial Vale - IV - 9288178 - Prevenção de Enchentes - Construção de Bacias de Contenção no Córrego Ferrugem</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B27" t="n">
-        <v>1400</v>
+        <v>1300</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>CORPO DE BOMBEIROS MILITAR DO ESTADO DE MINAS GERAIS - CBMMG</t>
+          <t>SECRETARIA DE ESTADO DE INFRAESTRUTURA, MOBILIDADE E PARCERIA - SEINFRA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -3486,11 +3478,11 @@
         <v>0</v>
       </c>
       <c r="F27" t="n">
-        <v>1401</v>
+        <v>1301</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>CORPO DE BOMBEIROS MILITAR DO ESTADO DE MINAS GERAIS - CBMMG</t>
+          <t>SECRETARIA DE ESTADO DE INFRAESTRUTURA, MOBILIDADE E PARCERIAS - SEINFRA</t>
         </is>
       </c>
       <c r="H27" t="n">
@@ -3503,96 +3495,94 @@
         <v>90</v>
       </c>
       <c r="K27" t="n">
-        <v>52</v>
+        <v>39</v>
       </c>
       <c r="L27" t="n">
-        <v>80</v>
+        <v>95</v>
       </c>
       <c r="M27" t="n">
         <v>1</v>
       </c>
       <c r="N27" t="n">
-        <v>10377</v>
+        <v>10554</v>
       </c>
       <c r="O27" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="P27" t="n">
-        <v>182</v>
+        <v>451</v>
       </c>
       <c r="Q27" t="n">
-        <v>52</v>
+        <v>99</v>
       </c>
       <c r="R27" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="S27" t="n">
-        <v>120</v>
+        <v>42</v>
       </c>
       <c r="T27" t="n">
-        <v>4120</v>
+        <v>1042</v>
       </c>
       <c r="U27" t="n">
         <v>1</v>
       </c>
       <c r="V27" t="n">
-        <v>4621003</v>
+        <v>1000</v>
       </c>
       <c r="W27" t="n">
-        <v>4621003</v>
+        <v>1000</v>
       </c>
       <c r="X27" t="n">
-        <v>4621003</v>
+        <v>1000</v>
       </c>
       <c r="Y27" t="n">
         <v>0</v>
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>MODERNIZAÇÃO E ESTRUTURAÇÃO DO CORPO DE BOMBEIROS MILITAR DE MINAS GERAIS</t>
+          <t>REQUALIFICAÇÃO URBANA E AMBIENTAL E DE CONTROLE DE CHEIAS DO CÓRREGO RIACHO DAS PEDRAS (VALE)</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>PROMOÇÃO DE DEFESA CIVIL</t>
+          <t>DESENVOLVIMENTO DA INFRAESTRUTURA ESTADUAL, MUNICIPAL E REGIONAL</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>Acordo Repactuação Rio Doce</t>
+          <t>Acordo Judicial Vale</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Anexo a definir</t>
-        </is>
-      </c>
-      <c r="AD27" t="inlineStr">
-        <is>
-          <t>Instrumento de entrada a cadastrar</t>
-        </is>
+          <t>IV</t>
+        </is>
+      </c>
+      <c r="AD27" t="n">
+        <v>9288179</v>
       </c>
       <c r="AE27" t="inlineStr">
         <is>
-          <t>Adequação e equipagem de Bases de Segurança Pública (PMMG, CBMMG e PCMG) no Município de Mariana/MG</t>
+          <t>Prevenção de Enchentes - Desapropriação para construção de bacias de contenção no Córrego Riacho das Pedras</t>
         </is>
       </c>
       <c r="AF27" t="inlineStr">
         <is>
-          <t>Acordo Repactuação Rio Doce - Anexo a definir - Instrumento de entrada a cadastrar - Adequação e equipagem de Bases de Segurança Pública (PMMG, CBMMG e PCMG) no Município de Mariana/MG</t>
+          <t>Acordo Judicial Vale - IV - 9288179 - Prevenção de Enchentes - Desapropriação para construção de bacias de contenção no Córrego Riacho das Pedras</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B28" t="n">
-        <v>1400</v>
+        <v>1300</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>CORPO DE BOMBEIROS MILITAR DO ESTADO DE MINAS GERAIS - CBMMG</t>
+          <t>SECRETARIA DE ESTADO DE INFRAESTRUTURA, MOBILIDADE E PARCERIA - SEINFRA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -3602,11 +3592,11 @@
         <v>0</v>
       </c>
       <c r="F28" t="n">
-        <v>1401</v>
+        <v>2301</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>CORPO DE BOMBEIROS MILITAR DO ESTADO DE MINAS GERAIS - CBMMG</t>
+          <t>DEPARTAMENTO DE ESTRADAS DE RODAGEM DO ESTADO DE MINAS GERAIS - DER-MG</t>
         </is>
       </c>
       <c r="H28" t="n">
@@ -3619,7 +3609,7 @@
         <v>90</v>
       </c>
       <c r="K28" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="L28" t="n">
         <v>80</v>
@@ -3628,87 +3618,85 @@
         <v>1</v>
       </c>
       <c r="N28" t="n">
-        <v>10377</v>
+        <v>10559</v>
       </c>
       <c r="O28" t="n">
-        <v>6</v>
+        <v>26</v>
       </c>
       <c r="P28" t="n">
-        <v>182</v>
+        <v>782</v>
       </c>
       <c r="Q28" t="n">
-        <v>52</v>
+        <v>81</v>
       </c>
       <c r="R28" t="n">
         <v>4</v>
       </c>
       <c r="S28" t="n">
-        <v>120</v>
+        <v>268</v>
       </c>
       <c r="T28" t="n">
-        <v>4120</v>
+        <v>4268</v>
       </c>
       <c r="U28" t="n">
         <v>1</v>
       </c>
       <c r="V28" t="n">
-        <v>3574366</v>
+        <v>41300000</v>
       </c>
       <c r="W28" t="n">
-        <v>3574366</v>
+        <v>41300000</v>
       </c>
       <c r="X28" t="n">
-        <v>3574366</v>
+        <v>41300000</v>
       </c>
       <c r="Y28" t="n">
         <v>0</v>
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>MODERNIZAÇÃO E ESTRUTURAÇÃO DO CORPO DE BOMBEIROS MILITAR DE MINAS GERAIS</t>
+          <t>AMPLIAÇÃO DE CAPACIDADE DA MALHA E RESTAURAÇÃO DO PAVIMENTO</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>PROMOÇÃO DE DEFESA CIVIL</t>
+          <t>DESENVOLVIMENTO SUSTENTÁVEL DA INFRAESTRUTURA RODOVIÁRIA</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>Acordo Repactuação Rio Doce</t>
+          <t>Acordo Judicial do Rio Doce</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Anexo a definir</t>
-        </is>
-      </c>
-      <c r="AD28" t="inlineStr">
-        <is>
-          <t>Instrumento de entrada a cadastrar</t>
-        </is>
+          <t>ANEXO 12</t>
+        </is>
+      </c>
+      <c r="AD28" t="n">
+        <v>9452379</v>
       </c>
       <c r="AE28" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fortalecimento da infraestrutura e logística das unidades das forças de segurança </t>
+          <t>Ampliação e melhoria na pavimentação, manutenção e recuperação funcional da infraestrutura viária</t>
         </is>
       </c>
       <c r="AF28" t="inlineStr">
         <is>
-          <t xml:space="preserve">Acordo Repactuação Rio Doce - Anexo a definir - Instrumento de entrada a cadastrar - Fortalecimento da infraestrutura e logística das unidades das forças de segurança </t>
+          <t>Acordo Judicial do Rio Doce - ANEXO 12 - 9452379 - Ampliação e melhoria na pavimentação, manutenção e recuperação funcional da infraestrutura viária</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B29" t="n">
-        <v>1480</v>
+        <v>1300</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO SOCIAL - SEDESE</t>
+          <t>SECRETARIA DE ESTADO DE INFRAESTRUTURA, MOBILIDADE E PARCERIA - SEINFRA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -3718,24 +3706,24 @@
         <v>0</v>
       </c>
       <c r="F29" t="n">
-        <v>1481</v>
+        <v>2301</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO SOCIAL - SEDESE</t>
+          <t>DEPARTAMENTO DE ESTRADAS DE RODAGEM DO ESTADO DE MINAS GERAIS - DER-MG</t>
         </is>
       </c>
       <c r="H29" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I29" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J29" t="n">
         <v>90</v>
       </c>
       <c r="K29" t="n">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="L29" t="n">
         <v>80</v>
@@ -3744,87 +3732,85 @@
         <v>1</v>
       </c>
       <c r="N29" t="n">
-        <v>10803</v>
+        <v>10568</v>
       </c>
       <c r="O29" t="n">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="P29" t="n">
-        <v>122</v>
+        <v>782</v>
       </c>
       <c r="Q29" t="n">
-        <v>148</v>
+        <v>81</v>
       </c>
       <c r="R29" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="S29" t="n">
-        <v>79</v>
+        <v>275</v>
       </c>
       <c r="T29" t="n">
-        <v>2079</v>
+        <v>4275</v>
       </c>
       <c r="U29" t="n">
         <v>1</v>
       </c>
       <c r="V29" t="n">
-        <v>5000000</v>
+        <v>115000000</v>
       </c>
       <c r="W29" t="n">
-        <v>5000000</v>
+        <v>115000000</v>
       </c>
       <c r="X29" t="n">
-        <v>5000000</v>
+        <v>115000000</v>
       </c>
       <c r="Y29" t="n">
         <v>0</v>
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>APOIO FINANCEIRO E MATERIAL ÀS INSTITUIÇÕES NA PROMOÇÃO DO DESENVOLVIMENTO SOCIAL</t>
+          <t>IMPLANTAÇÃO/PAVIMENTAÇÃO DA MALHA</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>APOIO ÀS POLÍTICAS DE DESENVOLVIMENTO SOCIAL</t>
+          <t>DESENVOLVIMENTO SUSTENTÁVEL DA INFRAESTRUTURA RODOVIÁRIA</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>Acordo Repactuação Rio Doce</t>
+          <t>Acordo Judicial do Rio Doce</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Anexo a definir</t>
-        </is>
-      </c>
-      <c r="AD29" t="inlineStr">
-        <is>
-          <t>Instrumento de entrada a cadastrar</t>
-        </is>
+          <t>ANEXO 12</t>
+        </is>
+      </c>
+      <c r="AD29" t="n">
+        <v>9452379</v>
       </c>
       <c r="AE29" t="inlineStr">
         <is>
-          <t>Promoção, defesa e garantia dos direitos das mulheres e fomento da política de prevenção à violência doméstica e atenção à mulher</t>
+          <t>Ampliação e melhoria na pavimentação, manutenção e recuperação funcional da infraestrutura viária</t>
         </is>
       </c>
       <c r="AF29" t="inlineStr">
         <is>
-          <t>Acordo Repactuação Rio Doce - Anexo a definir - Instrumento de entrada a cadastrar - Promoção, defesa e garantia dos direitos das mulheres e fomento da política de prevenção à violência doméstica e atenção à mulher</t>
+          <t>Acordo Judicial do Rio Doce - ANEXO 12 - 9452379 - Ampliação e melhoria na pavimentação, manutenção e recuperação funcional da infraestrutura viária</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B30" t="n">
-        <v>1480</v>
+        <v>1300</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO SOCIAL - SEDESE</t>
+          <t>SECRETARIA DE ESTADO DE INFRAESTRUTURA, MOBILIDADE E PARCERIA - SEINFRA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -3834,113 +3820,111 @@
         <v>0</v>
       </c>
       <c r="F30" t="n">
-        <v>1481</v>
+        <v>2301</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO SOCIAL - SEDESE</t>
+          <t>DEPARTAMENTO DE ESTRADAS DE RODAGEM DO ESTADO DE MINAS GERAIS - DER-MG</t>
         </is>
       </c>
       <c r="H30" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I30" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J30" t="n">
         <v>90</v>
       </c>
       <c r="K30" t="n">
-        <v>39</v>
+        <v>93</v>
       </c>
       <c r="L30" t="n">
-        <v>80</v>
+        <v>95</v>
       </c>
       <c r="M30" t="n">
         <v>1</v>
       </c>
       <c r="N30" t="n">
-        <v>10803</v>
+        <v>10582</v>
       </c>
       <c r="O30" t="n">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="P30" t="n">
-        <v>122</v>
+        <v>782</v>
       </c>
       <c r="Q30" t="n">
-        <v>148</v>
+        <v>81</v>
       </c>
       <c r="R30" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="S30" t="n">
-        <v>79</v>
+        <v>287</v>
       </c>
       <c r="T30" t="n">
-        <v>2079</v>
+        <v>4287</v>
       </c>
       <c r="U30" t="n">
         <v>1</v>
       </c>
       <c r="V30" t="n">
-        <v>14032546</v>
+        <v>1000</v>
       </c>
       <c r="W30" t="n">
-        <v>14032546</v>
+        <v>1000</v>
       </c>
       <c r="X30" t="n">
-        <v>14032546</v>
+        <v>1000</v>
       </c>
       <c r="Y30" t="n">
         <v>0</v>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>APOIO FINANCEIRO E MATERIAL ÀS INSTITUIÇÕES NA PROMOÇÃO DO DESENVOLVIMENTO SOCIAL</t>
+          <t>CONSTRUÇÃO E ADEQUAÇÃO DE RODOVIAS - RIO DOCE</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>APOIO ÀS POLÍTICAS DE DESENVOLVIMENTO SOCIAL</t>
+          <t>DESENVOLVIMENTO SUSTENTÁVEL DA INFRAESTRUTURA RODOVIÁRIA</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>Acordo Repactuação Rio Doce</t>
+          <t>Agenda Integrada - Renova</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Anexo a definir</t>
-        </is>
-      </c>
-      <c r="AD30" t="inlineStr">
-        <is>
-          <t>Instrumento de entrada a cadastrar</t>
-        </is>
+          <t>Sem anexo</t>
+        </is>
+      </c>
+      <c r="AD30" t="n">
+        <v>9382040</v>
       </c>
       <c r="AE30" t="inlineStr">
         <is>
-          <t>Fortalecimento do atendimento da rede socioassistencial com execução de um plano de melhorias, que inclua, preferencialmente, construção e reforma de unidades do CRAS e CREAS, contratação de equipe técnica e aquisição de material de consumo de acordo com detalhamento a ser construído prioritariamente</t>
+          <t>Marliéria</t>
         </is>
       </c>
       <c r="AF30" t="inlineStr">
         <is>
-          <t>Acordo Repactuação Rio Doce - Anexo a definir - Instrumento de entrada a cadastrar - Fortalecimento do atendimento da rede socioassistencial com execução de um plano de melhorias, que inclua, preferencialmente, construção e reforma de unidades do CRAS e CREAS, contratação de equipe técnica e aquisição de material de consumo de acordo com detalhamento a ser construído prioritariamente</t>
+          <t>Agenda Integrada - Renova - Sem anexo - 9382040 - Marliéria</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B31" t="n">
-        <v>1480</v>
+        <v>1300</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO SOCIAL - SEDESE</t>
+          <t>SECRETARIA DE ESTADO DE INFRAESTRUTURA, MOBILIDADE E PARCERIA - SEINFRA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -3950,113 +3934,111 @@
         <v>0</v>
       </c>
       <c r="F31" t="n">
-        <v>1481</v>
+        <v>2301</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO SOCIAL - SEDESE</t>
+          <t>DEPARTAMENTO DE ESTRADAS DE RODAGEM DO ESTADO DE MINAS GERAIS - DER-MG</t>
         </is>
       </c>
       <c r="H31" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I31" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J31" t="n">
         <v>90</v>
       </c>
       <c r="K31" t="n">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="L31" t="n">
-        <v>80</v>
+        <v>95</v>
       </c>
       <c r="M31" t="n">
         <v>1</v>
       </c>
       <c r="N31" t="n">
-        <v>10803</v>
+        <v>10584</v>
       </c>
       <c r="O31" t="n">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="P31" t="n">
-        <v>122</v>
+        <v>782</v>
       </c>
       <c r="Q31" t="n">
-        <v>148</v>
+        <v>81</v>
       </c>
       <c r="R31" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="S31" t="n">
-        <v>79</v>
+        <v>289</v>
       </c>
       <c r="T31" t="n">
-        <v>2079</v>
+        <v>4289</v>
       </c>
       <c r="U31" t="n">
         <v>1</v>
       </c>
       <c r="V31" t="n">
-        <v>15470409</v>
+        <v>99517258</v>
       </c>
       <c r="W31" t="n">
-        <v>15470409</v>
+        <v>99517258</v>
       </c>
       <c r="X31" t="n">
-        <v>15470409</v>
+        <v>99517258</v>
       </c>
       <c r="Y31" t="n">
         <v>0</v>
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>APOIO FINANCEIRO E MATERIAL ÀS INSTITUIÇÕES NA PROMOÇÃO DO DESENVOLVIMENTO SOCIAL</t>
+          <t>CONSTRUÇÃO E ADEQUAÇÃO DE RODOVIAS - RECUPERAÇÃO BRUMADINHO</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>APOIO ÀS POLÍTICAS DE DESENVOLVIMENTO SOCIAL</t>
+          <t>DESENVOLVIMENTO SUSTENTÁVEL DA INFRAESTRUTURA RODOVIÁRIA</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>Acordo Repactuação Rio Doce</t>
+          <t>Acordo Judicial Vale</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Anexo a definir</t>
-        </is>
-      </c>
-      <c r="AD31" t="inlineStr">
-        <is>
-          <t>Instrumento de entrada a cadastrar</t>
-        </is>
+          <t>III</t>
+        </is>
+      </c>
+      <c r="AD31" t="n">
+        <v>9288132</v>
       </c>
       <c r="AE31" t="inlineStr">
         <is>
-          <t>Fortalecimento do atendimento da rede socioassistencial com execução de um plano de melhorias, que inclua, preferencialmente, construção e reforma de unidades do CRAS e CREAS, contratação de equipe técnica e aquisição de material de consumo de acordo com detalhamento a ser construído prioritariamente</t>
+          <t>Construção de pontes em São Francisco, Manga e São Romão sobre o Rio São Francisco</t>
         </is>
       </c>
       <c r="AF31" t="inlineStr">
         <is>
-          <t>Acordo Repactuação Rio Doce - Anexo a definir - Instrumento de entrada a cadastrar - Fortalecimento do atendimento da rede socioassistencial com execução de um plano de melhorias, que inclua, preferencialmente, construção e reforma de unidades do CRAS e CREAS, contratação de equipe técnica e aquisição de material de consumo de acordo com detalhamento a ser construído prioritariamente</t>
+          <t>Acordo Judicial Vale - III - 9288132 - Construção de pontes em São Francisco, Manga e São Romão sobre o Rio São Francisco</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B32" t="n">
-        <v>1480</v>
+        <v>1300</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO SOCIAL - SEDESE</t>
+          <t>SECRETARIA DE ESTADO DE INFRAESTRUTURA, MOBILIDADE E PARCERIA - SEINFRA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -4066,113 +4048,111 @@
         <v>0</v>
       </c>
       <c r="F32" t="n">
-        <v>1481</v>
+        <v>2301</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO SOCIAL - SEDESE</t>
+          <t>DEPARTAMENTO DE ESTRADAS DE RODAGEM DO ESTADO DE MINAS GERAIS - DER-MG</t>
         </is>
       </c>
       <c r="H32" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I32" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J32" t="n">
         <v>90</v>
       </c>
       <c r="K32" t="n">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="L32" t="n">
-        <v>80</v>
+        <v>95</v>
       </c>
       <c r="M32" t="n">
         <v>1</v>
       </c>
       <c r="N32" t="n">
-        <v>10803</v>
+        <v>10584</v>
       </c>
       <c r="O32" t="n">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="P32" t="n">
-        <v>122</v>
+        <v>782</v>
       </c>
       <c r="Q32" t="n">
-        <v>148</v>
+        <v>81</v>
       </c>
       <c r="R32" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="S32" t="n">
-        <v>79</v>
+        <v>289</v>
       </c>
       <c r="T32" t="n">
-        <v>2079</v>
+        <v>4289</v>
       </c>
       <c r="U32" t="n">
         <v>1</v>
       </c>
       <c r="V32" t="n">
-        <v>6441250</v>
+        <v>158250000</v>
       </c>
       <c r="W32" t="n">
-        <v>6441250</v>
+        <v>158250000</v>
       </c>
       <c r="X32" t="n">
-        <v>6441250</v>
+        <v>158250000</v>
       </c>
       <c r="Y32" t="n">
         <v>0</v>
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>APOIO FINANCEIRO E MATERIAL ÀS INSTITUIÇÕES NA PROMOÇÃO DO DESENVOLVIMENTO SOCIAL</t>
+          <t>CONSTRUÇÃO E ADEQUAÇÃO DE RODOVIAS - RECUPERAÇÃO BRUMADINHO</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>APOIO ÀS POLÍTICAS DE DESENVOLVIMENTO SOCIAL</t>
+          <t>DESENVOLVIMENTO SUSTENTÁVEL DA INFRAESTRUTURA RODOVIÁRIA</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>Acordo Repactuação Rio Doce</t>
+          <t>Acordo Judicial Vale</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Anexo a definir</t>
-        </is>
-      </c>
-      <c r="AD32" t="inlineStr">
-        <is>
-          <t>Instrumento de entrada a cadastrar</t>
-        </is>
+          <t>III</t>
+        </is>
+      </c>
+      <c r="AD32" t="n">
+        <v>9288133</v>
       </c>
       <c r="AE32" t="inlineStr">
         <is>
-          <t>Oferta de capacitações continuadas em gestão para os profissionais do SUAS, além do apoio na elaboração e execução do Plano Municipal de Assistência Social</t>
+          <t>Recuperação de rodovias pavimentadas em pior estado, conforme avaliação técnica do DER-MG/conclusão de corredor logístico estruturante, conforme critérios técnicos da SEINFRA</t>
         </is>
       </c>
       <c r="AF32" t="inlineStr">
         <is>
-          <t>Acordo Repactuação Rio Doce - Anexo a definir - Instrumento de entrada a cadastrar - Oferta de capacitações continuadas em gestão para os profissionais do SUAS, além do apoio na elaboração e execução do Plano Municipal de Assistência Social</t>
+          <t>Acordo Judicial Vale - III - 9288133 - Recuperação de rodovias pavimentadas em pior estado, conforme avaliação técnica do DER-MG/conclusão de corredor logístico estruturante, conforme critérios técnicos da SEINFRA</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B33" t="n">
-        <v>1480</v>
+        <v>1300</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO SOCIAL - SEDESE</t>
+          <t>SECRETARIA DE ESTADO DE INFRAESTRUTURA, MOBILIDADE E PARCERIA - SEINFRA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -4182,24 +4162,24 @@
         <v>0</v>
       </c>
       <c r="F33" t="n">
-        <v>1481</v>
+        <v>2301</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO SOCIAL - SEDESE</t>
+          <t>DEPARTAMENTO DE ESTRADAS DE RODAGEM DO ESTADO DE MINAS GERAIS - DER-MG</t>
         </is>
       </c>
       <c r="H33" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I33" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J33" t="n">
         <v>90</v>
       </c>
       <c r="K33" t="n">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="L33" t="n">
         <v>80</v>
@@ -4208,87 +4188,85 @@
         <v>1</v>
       </c>
       <c r="N33" t="n">
-        <v>10419</v>
+        <v>10589</v>
       </c>
       <c r="O33" t="n">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="P33" t="n">
-        <v>334</v>
+        <v>782</v>
       </c>
       <c r="Q33" t="n">
-        <v>66</v>
+        <v>81</v>
       </c>
       <c r="R33" t="n">
         <v>4</v>
       </c>
       <c r="S33" t="n">
-        <v>154</v>
+        <v>293</v>
       </c>
       <c r="T33" t="n">
-        <v>4154</v>
+        <v>4293</v>
       </c>
       <c r="U33" t="n">
         <v>1</v>
       </c>
       <c r="V33" t="n">
-        <v>10000000</v>
+        <v>53897833</v>
       </c>
       <c r="W33" t="n">
-        <v>10000000</v>
+        <v>53897833</v>
       </c>
       <c r="X33" t="n">
-        <v>10000000</v>
+        <v>53897833</v>
       </c>
       <c r="Y33" t="n">
         <v>0</v>
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>FOMENTO PARA ECONOMIA POPULAR SOLIDÁRIA E PROMOÇÃO DA INCLUSÃO PRODUTIVA</t>
+          <t>CONSERVAÇÃO ROTINEIRA DA MALHA VIÁRIA</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>POLÍTICAS DE TRABALHO E EMPREGO</t>
+          <t>DESENVOLVIMENTO SUSTENTÁVEL DA INFRAESTRUTURA RODOVIÁRIA</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>Acordo Repactuação Rio Doce</t>
+          <t>Acordo Judicial do Rio Doce</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Anexo a definir</t>
-        </is>
-      </c>
-      <c r="AD33" t="inlineStr">
-        <is>
-          <t>Instrumento de entrada a cadastrar</t>
-        </is>
+          <t>ANEXO 12</t>
+        </is>
+      </c>
+      <c r="AD33" t="n">
+        <v>9452379</v>
       </c>
       <c r="AE33" t="inlineStr">
         <is>
-          <t>Disponibilização de microcrédito para financiamento de atividades produtivas, podendo ter o apoio de agentes de crédito facilitadores</t>
+          <t>Ampliação e melhoria na pavimentação, manutenção e recuperação funcional da infraestrutura viária</t>
         </is>
       </c>
       <c r="AF33" t="inlineStr">
         <is>
-          <t>Acordo Repactuação Rio Doce - Anexo a definir - Instrumento de entrada a cadastrar - Disponibilização de microcrédito para financiamento de atividades produtivas, podendo ter o apoio de agentes de crédito facilitadores</t>
+          <t>Acordo Judicial do Rio Doce - ANEXO 12 - 9452379 - Ampliação e melhoria na pavimentação, manutenção e recuperação funcional da infraestrutura viária</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B34" t="n">
-        <v>1480</v>
+        <v>1300</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO SOCIAL - SEDESE</t>
+          <t>SECRETARIA DE ESTADO DE INFRAESTRUTURA, MOBILIDADE E PARCERIA - SEINFRA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -4298,24 +4276,24 @@
         <v>0</v>
       </c>
       <c r="F34" t="n">
-        <v>1481</v>
+        <v>2301</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO SOCIAL - SEDESE</t>
+          <t>DEPARTAMENTO DE ESTRADAS DE RODAGEM DO ESTADO DE MINAS GERAIS - DER-MG</t>
         </is>
       </c>
       <c r="H34" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I34" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J34" t="n">
         <v>90</v>
       </c>
       <c r="K34" t="n">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="L34" t="n">
         <v>80</v>
@@ -4324,87 +4302,85 @@
         <v>1</v>
       </c>
       <c r="N34" t="n">
-        <v>10423</v>
+        <v>10722</v>
       </c>
       <c r="O34" t="n">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="P34" t="n">
-        <v>363</v>
+        <v>782</v>
       </c>
       <c r="Q34" t="n">
-        <v>67</v>
+        <v>81</v>
       </c>
       <c r="R34" t="n">
         <v>4</v>
       </c>
       <c r="S34" t="n">
-        <v>158</v>
+        <v>385</v>
       </c>
       <c r="T34" t="n">
-        <v>4158</v>
+        <v>4385</v>
       </c>
       <c r="U34" t="n">
         <v>1</v>
       </c>
       <c r="V34" t="n">
-        <v>452871</v>
+        <v>54435022</v>
       </c>
       <c r="W34" t="n">
-        <v>452871</v>
+        <v>54435022</v>
       </c>
       <c r="X34" t="n">
-        <v>452871</v>
+        <v>54435022</v>
       </c>
       <c r="Y34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>QUALIFICAÇÃO PROFISSIONAL</t>
+          <t>REABILITAÇÃO DA MALHA VIÁRIA</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>REDE DE DESENVOLVIMENTO DA EDUCAÇÃO PROFISSIONAL</t>
+          <t>DESENVOLVIMENTO SUSTENTÁVEL DA INFRAESTRUTURA RODOVIÁRIA</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>Acordo Repactuação Rio Doce</t>
+          <t>Acordo Judicial do Rio Doce</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Anexo a definir</t>
-        </is>
-      </c>
-      <c r="AD34" t="inlineStr">
-        <is>
-          <t>Instrumento de entrada a cadastrar</t>
-        </is>
+          <t>ANEXO 12</t>
+        </is>
+      </c>
+      <c r="AD34" t="n">
+        <v>9452379</v>
       </c>
       <c r="AE34" t="inlineStr">
         <is>
-          <t>Oferta de cursos de qualificação profissional a partir de estudo de demandas do mercado de trabalho</t>
+          <t>Ampliação e melhoria na pavimentação, manutenção e recuperação funcional da infraestrutura viária</t>
         </is>
       </c>
       <c r="AF34" t="inlineStr">
         <is>
-          <t>Acordo Repactuação Rio Doce - Anexo a definir - Instrumento de entrada a cadastrar - Oferta de cursos de qualificação profissional a partir de estudo de demandas do mercado de trabalho</t>
+          <t>Acordo Judicial do Rio Doce - ANEXO 12 - 9452379 - Ampliação e melhoria na pavimentação, manutenção e recuperação funcional da infraestrutura viária</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B35" t="n">
-        <v>1500</v>
+        <v>1300</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE PLANEJAMENTO E GESTÃO - SEPLAG</t>
+          <t>SECRETARIA DE ESTADO DE INFRAESTRUTURA, MOBILIDADE E PARCERIA - SEINFRA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -4414,111 +4390,111 @@
         <v>0</v>
       </c>
       <c r="F35" t="n">
-        <v>1501</v>
+        <v>4631</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE PLANEJAMENTO E GESTÃO - SEPLAG</t>
+          <t>FUNDO DE PAGAMENTO DE PARCERIAS PÚBLICO - PRIVADAS DE MINAS GERAIS - FPP - MG</t>
         </is>
       </c>
       <c r="H35" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I35" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J35" t="n">
-        <v>90</v>
+        <v>67</v>
       </c>
       <c r="K35" t="n">
-        <v>39</v>
+        <v>82</v>
       </c>
       <c r="L35" t="n">
-        <v>95</v>
+        <v>80</v>
       </c>
       <c r="M35" t="n">
         <v>1</v>
       </c>
       <c r="N35" t="n">
-        <v>10821</v>
+        <v>11043</v>
       </c>
       <c r="O35" t="n">
         <v>4</v>
       </c>
       <c r="P35" t="n">
-        <v>122</v>
+        <v>130</v>
       </c>
       <c r="Q35" t="n">
-        <v>155</v>
+        <v>85</v>
       </c>
       <c r="R35" t="n">
         <v>4</v>
       </c>
       <c r="S35" t="n">
-        <v>462</v>
+        <v>128</v>
       </c>
       <c r="T35" t="n">
-        <v>4462</v>
+        <v>4128</v>
       </c>
       <c r="U35" t="n">
         <v>1</v>
       </c>
       <c r="V35" t="n">
-        <v>2000</v>
+        <v>345000000</v>
       </c>
       <c r="W35" t="n">
-        <v>2000</v>
+        <v>345000000</v>
       </c>
       <c r="X35" t="n">
-        <v>2000</v>
+        <v>345000000</v>
       </c>
       <c r="Y35" t="n">
         <v>0</v>
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>RECUPERAÇÃO E COMPENSAÇÃO DOS DANOS EM FUNÇÃO DO DESASTRE MINERÁRIO DA VALE S.A EM BRUMADINHO</t>
+          <t>LOTE OURO PRETO</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>REPARAÇÃO DOS DANOS DOS ROMPIMENTOS EM BRUMADINHO E MARIANA</t>
+          <t>PROMOÇÃO DE CONCESSÕES E PARCERIAS</t>
         </is>
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>Acordo Judicial Vale</t>
+          <t>Acordo Judicial do Rio Doce</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Item 4.4.10: Ressarcimentos e contratações temporárias</t>
+          <t>ANEXO 13</t>
         </is>
       </c>
       <c r="AD35" t="n">
-        <v>9288191</v>
+        <v>9445763</v>
       </c>
       <c r="AE35" t="inlineStr">
         <is>
-          <t>Ressarcimentos de despesas públicas</t>
+          <t>Obras e serviços para construção e implantação de melhorias rodoviárias, operação e manutenção das rodovias do lote Ouro Preto – Mariana, com priorização de duplicação da BR-356, do entroncamento com a BR-040 até o entroncamento com a Rodovia MG-129 (Mariana/MG)</t>
         </is>
       </c>
       <c r="AF35" t="inlineStr">
         <is>
-          <t>Acordo Judicial Vale - Item 4.4.10: Ressarcimentos e contratações temporárias - 9288191 - Ressarcimentos de despesas públicas</t>
+          <t>Acordo Judicial do Rio Doce - ANEXO 13 - 9445763 - Obras e serviços para construção e implantação de melhorias rodoviárias, operação e manutenção das rodovias do lote Ouro Preto – Mariana, com priorização de duplicação da BR-356, do entroncamento com a BR-040 até o entroncamento com a Rodovia MG-129 (Mariana/MG)</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B36" t="n">
-        <v>1510</v>
+        <v>1300</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>POLÍCIA CIVIL DO ESTADO DE MINAS GERAIS - PCMG</t>
+          <t>SECRETARIA DE ESTADO DE INFRAESTRUTURA, MOBILIDADE E PARCERIA - SEINFRA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -4528,113 +4504,111 @@
         <v>0</v>
       </c>
       <c r="F36" t="n">
-        <v>1511</v>
+        <v>4631</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>POLÍCIA CIVIL DO ESTADO DE MINAS GERAIS - PCMG</t>
+          <t>FUNDO DE PAGAMENTO DE PARCERIAS PÚBLICO - PRIVADAS DE MINAS GERAIS - FPP - MG</t>
         </is>
       </c>
       <c r="H36" t="n">
         <v>4</v>
       </c>
       <c r="I36" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J36" t="n">
-        <v>90</v>
+        <v>67</v>
       </c>
       <c r="K36" t="n">
-        <v>39</v>
+        <v>83</v>
       </c>
       <c r="L36" t="n">
-        <v>80</v>
+        <v>95</v>
       </c>
       <c r="M36" t="n">
         <v>1</v>
       </c>
       <c r="N36" t="n">
-        <v>10279</v>
+        <v>10500</v>
       </c>
       <c r="O36" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="P36" t="n">
-        <v>181</v>
+        <v>130</v>
       </c>
       <c r="Q36" t="n">
-        <v>32</v>
+        <v>85</v>
       </c>
       <c r="R36" t="n">
         <v>4</v>
       </c>
       <c r="S36" t="n">
-        <v>60</v>
+        <v>220</v>
       </c>
       <c r="T36" t="n">
-        <v>4060</v>
+        <v>4220</v>
       </c>
       <c r="U36" t="n">
         <v>1</v>
       </c>
       <c r="V36" t="n">
-        <v>3162316</v>
+        <v>500842252</v>
       </c>
       <c r="W36" t="n">
-        <v>3162316</v>
+        <v>500842252</v>
       </c>
       <c r="X36" t="n">
-        <v>3162316</v>
+        <v>500842252</v>
       </c>
       <c r="Y36" t="n">
         <v>0</v>
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>GESTÃO DAS UNIDADES POLICIAIS</t>
+          <t>RODOANEL METROPOLITANO DE BELO HORIZONTE</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>INVESTIGAÇÃO</t>
+          <t>PROMOÇÃO DE CONCESSÕES E PARCERIAS</t>
         </is>
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>Acordo Repactuação Rio Doce</t>
+          <t>Acordo Judicial Vale</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Anexo a definir</t>
-        </is>
-      </c>
-      <c r="AD36" t="inlineStr">
-        <is>
-          <t>Instrumento de entrada a cadastrar</t>
-        </is>
+          <t>III</t>
+        </is>
+      </c>
+      <c r="AD36" t="n">
+        <v>9288180</v>
       </c>
       <c r="AE36" t="inlineStr">
         <is>
-          <t>Adequação e equipagem de Bases de Segurança Pública (PMMG, CBMMG e PCMG) no Município de Mariana/MG</t>
+          <t>Implantação do Rodoanel da Região Metropolitana de Belo Horizonte</t>
         </is>
       </c>
       <c r="AF36" t="inlineStr">
         <is>
-          <t>Acordo Repactuação Rio Doce - Anexo a definir - Instrumento de entrada a cadastrar - Adequação e equipagem de Bases de Segurança Pública (PMMG, CBMMG e PCMG) no Município de Mariana/MG</t>
+          <t>Acordo Judicial Vale - III - 9288180 - Implantação do Rodoanel da Região Metropolitana de Belo Horizonte</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B37" t="n">
-        <v>1510</v>
+        <v>1320</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>POLÍCIA CIVIL DO ESTADO DE MINAS GERAIS - PCMG</t>
+          <t>SECRETARIA DE ESTADO DE SAÚDE - SES</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -4644,11 +4618,11 @@
         <v>0</v>
       </c>
       <c r="F37" t="n">
-        <v>1511</v>
+        <v>4291</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>POLÍCIA CIVIL DO ESTADO DE MINAS GERAIS - PCMG</t>
+          <t>FUNDO ESTADUAL DE SAÚDE - FES</t>
         </is>
       </c>
       <c r="H37" t="n">
@@ -4658,10 +4632,10 @@
         <v>4</v>
       </c>
       <c r="J37" t="n">
-        <v>90</v>
+        <v>41</v>
       </c>
       <c r="K37" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="L37" t="n">
         <v>80</v>
@@ -4670,87 +4644,85 @@
         <v>1</v>
       </c>
       <c r="N37" t="n">
-        <v>10279</v>
+        <v>10380</v>
       </c>
       <c r="O37" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="P37" t="n">
-        <v>181</v>
+        <v>302</v>
       </c>
       <c r="Q37" t="n">
-        <v>32</v>
+        <v>58</v>
       </c>
       <c r="R37" t="n">
         <v>4</v>
       </c>
       <c r="S37" t="n">
-        <v>60</v>
+        <v>123</v>
       </c>
       <c r="T37" t="n">
-        <v>4060</v>
+        <v>4123</v>
       </c>
       <c r="U37" t="n">
         <v>1</v>
       </c>
       <c r="V37" t="n">
-        <v>3087684</v>
+        <v>76757500</v>
       </c>
       <c r="W37" t="n">
-        <v>3087684</v>
+        <v>76757500</v>
       </c>
       <c r="X37" t="n">
-        <v>3087684</v>
+        <v>76757500</v>
       </c>
       <c r="Y37" t="n">
         <v>0</v>
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>GESTÃO DAS UNIDADES POLICIAIS</t>
+          <t>ESTRUTURAÇÃO DA ATENÇÃO HOSPITALAR E DE URGÊNCIA E EMERGÊNCIA</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>INVESTIGAÇÃO</t>
+          <t>POLÍTICAS DE ATENÇÃO HOSPITALAR</t>
         </is>
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>Acordo Repactuação Rio Doce</t>
+          <t>Acordo Judicial do Rio Doce</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Anexo a definir</t>
-        </is>
-      </c>
-      <c r="AD37" t="inlineStr">
-        <is>
-          <t>Instrumento de entrada a cadastrar</t>
-        </is>
+          <t>ANEXO 08</t>
+        </is>
+      </c>
+      <c r="AD37" t="n">
+        <v>9445683</v>
       </c>
       <c r="AE37" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fortalecimento da infraestrutura e logística das unidades das forças de segurança </t>
+          <t>Políticas e ações de competência e execução direta do ESTADO DE MINAS GERAIS para aplicação em saúde nos municípios  (pendente criação de inciativas)</t>
         </is>
       </c>
       <c r="AF37" t="inlineStr">
         <is>
-          <t xml:space="preserve">Acordo Repactuação Rio Doce - Anexo a definir - Instrumento de entrada a cadastrar - Fortalecimento da infraestrutura e logística das unidades das forças de segurança </t>
+          <t>Acordo Judicial do Rio Doce - ANEXO 08 - 9445683 - Políticas e ações de competência e execução direta do ESTADO DE MINAS GERAIS para aplicação em saúde nos municípios  (pendente criação de inciativas)</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B38" t="n">
-        <v>1510</v>
+        <v>1370</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>POLÍCIA CIVIL DO ESTADO DE MINAS GERAIS - PCMG</t>
+          <t>SECRETARIA DE ESTADO DE MEIO AMBIENTE E DESENVOLVIMENTO SUSTENTÁVEL - SEMAD</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -4760,24 +4732,24 @@
         <v>0</v>
       </c>
       <c r="F38" t="n">
-        <v>1511</v>
+        <v>1371</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>POLÍCIA CIVIL DO ESTADO DE MINAS GERAIS - PCMG</t>
+          <t>SECRETARIA DE ESTADO DE MEIO AMBIENTE E DESENVOLVIMENTO SUSTENTÁVEL - SEMAD</t>
         </is>
       </c>
       <c r="H38" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I38" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J38" t="n">
         <v>90</v>
       </c>
       <c r="K38" t="n">
-        <v>52</v>
+        <v>37</v>
       </c>
       <c r="L38" t="n">
         <v>80</v>
@@ -4786,87 +4758,87 @@
         <v>1</v>
       </c>
       <c r="N38" t="n">
-        <v>10279</v>
+        <v>9706</v>
       </c>
       <c r="O38" t="n">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="P38" t="n">
-        <v>181</v>
+        <v>122</v>
       </c>
       <c r="Q38" t="n">
-        <v>32</v>
+        <v>705</v>
       </c>
       <c r="R38" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="S38" t="n">
-        <v>60</v>
+        <v>500</v>
       </c>
       <c r="T38" t="n">
-        <v>4060</v>
+        <v>2500</v>
       </c>
       <c r="U38" t="n">
         <v>1</v>
       </c>
       <c r="V38" t="n">
-        <v>8195369</v>
+        <v>14656357</v>
       </c>
       <c r="W38" t="n">
-        <v>8195369</v>
+        <v>14656357</v>
       </c>
       <c r="X38" t="n">
-        <v>8195369</v>
+        <v>14656357</v>
       </c>
       <c r="Y38" t="n">
         <v>0</v>
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>GESTÃO DAS UNIDADES POLICIAIS</t>
+          <t>ASSESSORAMENTO E GERENCIAMENTO DE POLÍTICAS PÚBLICAS</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>INVESTIGAÇÃO</t>
+          <t>APOIO ÀS POLÍTICAS PÚBLICAS</t>
         </is>
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>Acordo Repactuação Rio Doce</t>
+          <t>Acordo Judicial do Rio Doce</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Anexo a definir</t>
+          <t>ANEXO 12</t>
         </is>
       </c>
       <c r="AD38" t="inlineStr">
         <is>
-          <t>Instrumento de entrada a cadastrar</t>
+          <t>A SER CRIADO</t>
         </is>
       </c>
       <c r="AE38" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fortalecimento da infraestrutura e logística das unidades das forças de segurança </t>
+          <t>Suporte gerencial, administrativo, tecnológico e de comunicação social à implementação das iniciativas ambientais</t>
         </is>
       </c>
       <c r="AF38" t="inlineStr">
         <is>
-          <t xml:space="preserve">Acordo Repactuação Rio Doce - Anexo a definir - Instrumento de entrada a cadastrar - Fortalecimento da infraestrutura e logística das unidades das forças de segurança </t>
+          <t>Acordo Judicial do Rio Doce - ANEXO 12 - A SER CRIADO - Suporte gerencial, administrativo, tecnológico e de comunicação social à implementação das iniciativas ambientais</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B39" t="n">
-        <v>1910</v>
+        <v>1370</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>ENCARGOS GERAIS DO ESTADO - SECRETARIA DE ESTADO DE FAZENDA - EGE SEF</t>
+          <t>SECRETARIA DE ESTADO DE MEIO AMBIENTE E DESENVOLVIMENTO SUSTENTÁVEL - SEMAD</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -4876,24 +4848,24 @@
         <v>0</v>
       </c>
       <c r="F39" t="n">
-        <v>1915</v>
+        <v>1371</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>PARTICIPAÇÃO NO AUMENTO DO CAPITAL SOCIAL DE EMPRESAS - PARTICIPAÇÃO EMPRESAS</t>
+          <t>SECRETARIA DE ESTADO DE MEIO AMBIENTE E DESENVOLVIMENTO SUSTENTÁVEL - SEMAD</t>
         </is>
       </c>
       <c r="H39" t="n">
         <v>4</v>
       </c>
       <c r="I39" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J39" t="n">
         <v>90</v>
       </c>
       <c r="K39" t="n">
-        <v>65</v>
+        <v>52</v>
       </c>
       <c r="L39" t="n">
         <v>80</v>
@@ -4902,74 +4874,3392 @@
         <v>1</v>
       </c>
       <c r="N39" t="n">
-        <v>2503</v>
+        <v>10255</v>
       </c>
       <c r="O39" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="P39" t="n">
-        <v>694</v>
+        <v>542</v>
       </c>
       <c r="Q39" t="n">
-        <v>705</v>
+        <v>25</v>
       </c>
       <c r="R39" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="S39" t="n">
-        <v>752</v>
+        <v>38</v>
       </c>
       <c r="T39" t="n">
-        <v>7752</v>
+        <v>4038</v>
       </c>
       <c r="U39" t="n">
         <v>1</v>
       </c>
       <c r="V39" t="n">
-        <v>110000000</v>
+        <v>3160000</v>
       </c>
       <c r="W39" t="n">
-        <v>110000000</v>
+        <v>3160000</v>
       </c>
       <c r="X39" t="n">
-        <v>110000000</v>
+        <v>3160000</v>
       </c>
       <c r="Y39" t="n">
         <v>0</v>
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>PROGRAMAÇÃO A CARGO DO ESTADO PARA O BANCO DE DESENVOLVIMENTO DE MINAS GERAIS - BDMG</t>
+          <t>FISCALIZAÇÃO AMBIENTAL</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>APOIO ÀS POLÍTICAS PÚBLICAS</t>
+          <t>MONITORAMENTO, CONTROLE E FISCALIZAÇÃO AMBIENTAL</t>
         </is>
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>Acordo Repactuação Rio Doce</t>
+          <t>Acordo Judicial do Rio Doce</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Anexo a definir</t>
+          <t>ANEXO 12</t>
         </is>
       </c>
       <c r="AD39" t="inlineStr">
         <is>
-          <t>Instrumento de entrada a cadastrar</t>
+          <t>A SER CRIADO</t>
         </is>
       </c>
       <c r="AE39" t="inlineStr">
         <is>
-          <t>Criação de fundo de disponibilização de crédito para recuperação econômica de pequenas, médias e grandes empresas dos municípios atingidos, além de fundo garantidor para facilitar o acesso a essa linha de crédito</t>
+          <t>Melhoria na capacidade estadual fiscalizatória de barragens nas estruturas localizadas na extensão territorial da Bacia Hidrográfica do Rio Doce: aquisição de equipamentos físicos e tecnológicos, contratação de serviços de consultoria</t>
         </is>
       </c>
       <c r="AF39" t="inlineStr">
         <is>
-          <t>Acordo Repactuação Rio Doce - Anexo a definir - Instrumento de entrada a cadastrar - Criação de fundo de disponibilização de crédito para recuperação econômica de pequenas, médias e grandes empresas dos municípios atingidos, além de fundo garantidor para facilitar o acesso a essa linha de crédito</t>
+          <t>Acordo Judicial do Rio Doce - ANEXO 12 - A SER CRIADO - Melhoria na capacidade estadual fiscalizatória de barragens nas estruturas localizadas na extensão territorial da Bacia Hidrográfica do Rio Doce: aquisição de equipamentos físicos e tecnológicos, contratação de serviços de consultoria</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B40" t="n">
+        <v>1370</v>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>SECRETARIA DE ESTADO DE MEIO AMBIENTE E DESENVOLVIMENTO SUSTENTÁVEL - SEMAD</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>3</v>
+      </c>
+      <c r="E40" t="n">
+        <v>0</v>
+      </c>
+      <c r="F40" t="n">
+        <v>2101</v>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>INSTITUTO ESTADUAL DE FLORESTAS - IEF</t>
+        </is>
+      </c>
+      <c r="H40" t="n">
+        <v>3</v>
+      </c>
+      <c r="I40" t="n">
+        <v>3</v>
+      </c>
+      <c r="J40" t="n">
+        <v>90</v>
+      </c>
+      <c r="K40" t="n">
+        <v>36</v>
+      </c>
+      <c r="L40" t="n">
+        <v>80</v>
+      </c>
+      <c r="M40" t="n">
+        <v>1</v>
+      </c>
+      <c r="N40" t="n">
+        <v>10271</v>
+      </c>
+      <c r="O40" t="n">
+        <v>18</v>
+      </c>
+      <c r="P40" t="n">
+        <v>541</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>31</v>
+      </c>
+      <c r="R40" t="n">
+        <v>4</v>
+      </c>
+      <c r="S40" t="n">
+        <v>54</v>
+      </c>
+      <c r="T40" t="n">
+        <v>4054</v>
+      </c>
+      <c r="U40" t="n">
+        <v>1</v>
+      </c>
+      <c r="V40" t="n">
+        <v>7853980</v>
+      </c>
+      <c r="W40" t="n">
+        <v>7853980</v>
+      </c>
+      <c r="X40" t="n">
+        <v>7853980</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>PREVENÇÃO E COMBATE A INCÊNDIOS FLORESTAIS</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>PROTEÇÃO DAS ÁREAS AMBIENTALMENTE CONSERVADAS, DA FAUNA E DA BIODIVERSIDADE FLORESTAL</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>Acordo Judicial do Rio Doce</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>ANEXO 12</t>
+        </is>
+      </c>
+      <c r="AD40" t="n">
+        <v>9456606</v>
+      </c>
+      <c r="AE40" t="inlineStr">
+        <is>
+          <t>Consolidação de unidades de conservação estaduais na Bacia Hidrográfica do Rio Doce, a partir do investimento e custeio de suas estruturas e serviços prestados, de acordo com seus objetivos de criação; criação, se necessário, de nova(s) unidade(s) de conservação na Bacia Hidrográfica do Rio Doce de acordo com mapeamento de áreas prioritárias para conservação; realização de atividades de prevenção e combate a incêndios e regularização fundiária das unidades de conservação.</t>
+        </is>
+      </c>
+      <c r="AF40" t="inlineStr">
+        <is>
+          <t>Acordo Judicial do Rio Doce - ANEXO 12 - 9456606 - Consolidação de unidades de conservação estaduais na Bacia Hidrográfica do Rio Doce, a partir do investimento e custeio de suas estruturas e serviços prestados, de acordo com seus objetivos de criação; criação, se necessário, de nova(s) unidade(s) de conservação na Bacia Hidrográfica do Rio Doce de acordo com mapeamento de áreas prioritárias para conservação; realização de atividades de prevenção e combate a incêndios e regularização fundiária das unidades de conservação.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B41" t="n">
+        <v>1370</v>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>SECRETARIA DE ESTADO DE MEIO AMBIENTE E DESENVOLVIMENTO SUSTENTÁVEL - SEMAD</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>3</v>
+      </c>
+      <c r="E41" t="n">
+        <v>0</v>
+      </c>
+      <c r="F41" t="n">
+        <v>2101</v>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>INSTITUTO ESTADUAL DE FLORESTAS - IEF</t>
+        </is>
+      </c>
+      <c r="H41" t="n">
+        <v>3</v>
+      </c>
+      <c r="I41" t="n">
+        <v>3</v>
+      </c>
+      <c r="J41" t="n">
+        <v>90</v>
+      </c>
+      <c r="K41" t="n">
+        <v>39</v>
+      </c>
+      <c r="L41" t="n">
+        <v>80</v>
+      </c>
+      <c r="M41" t="n">
+        <v>1</v>
+      </c>
+      <c r="N41" t="n">
+        <v>10271</v>
+      </c>
+      <c r="O41" t="n">
+        <v>18</v>
+      </c>
+      <c r="P41" t="n">
+        <v>541</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>31</v>
+      </c>
+      <c r="R41" t="n">
+        <v>4</v>
+      </c>
+      <c r="S41" t="n">
+        <v>54</v>
+      </c>
+      <c r="T41" t="n">
+        <v>4054</v>
+      </c>
+      <c r="U41" t="n">
+        <v>1</v>
+      </c>
+      <c r="V41" t="n">
+        <v>1566500</v>
+      </c>
+      <c r="W41" t="n">
+        <v>1566500</v>
+      </c>
+      <c r="X41" t="n">
+        <v>1566500</v>
+      </c>
+      <c r="Y41" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>PREVENÇÃO E COMBATE A INCÊNDIOS FLORESTAIS</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>PROTEÇÃO DAS ÁREAS AMBIENTALMENTE CONSERVADAS, DA FAUNA E DA BIODIVERSIDADE FLORESTAL</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>Acordo Judicial do Rio Doce</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>ANEXO 12</t>
+        </is>
+      </c>
+      <c r="AD41" t="n">
+        <v>9456606</v>
+      </c>
+      <c r="AE41" t="inlineStr">
+        <is>
+          <t>Consolidação de unidades de conservação estaduais na Bacia Hidrográfica do Rio Doce, a partir do investimento e custeio de suas estruturas e serviços prestados, de acordo com seus objetivos de criação; criação, se necessário, de nova(s) unidade(s) de conservação na Bacia Hidrográfica do Rio Doce de acordo com mapeamento de áreas prioritárias para conservação; realização de atividades de prevenção e combate a incêndios e regularização fundiária das unidades de conservação.</t>
+        </is>
+      </c>
+      <c r="AF41" t="inlineStr">
+        <is>
+          <t>Acordo Judicial do Rio Doce - ANEXO 12 - 9456606 - Consolidação de unidades de conservação estaduais na Bacia Hidrográfica do Rio Doce, a partir do investimento e custeio de suas estruturas e serviços prestados, de acordo com seus objetivos de criação; criação, se necessário, de nova(s) unidade(s) de conservação na Bacia Hidrográfica do Rio Doce de acordo com mapeamento de áreas prioritárias para conservação; realização de atividades de prevenção e combate a incêndios e regularização fundiária das unidades de conservação.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B42" t="n">
+        <v>1370</v>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>SECRETARIA DE ESTADO DE MEIO AMBIENTE E DESENVOLVIMENTO SUSTENTÁVEL - SEMAD</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>3</v>
+      </c>
+      <c r="E42" t="n">
+        <v>0</v>
+      </c>
+      <c r="F42" t="n">
+        <v>2101</v>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>INSTITUTO ESTADUAL DE FLORESTAS - IEF</t>
+        </is>
+      </c>
+      <c r="H42" t="n">
+        <v>3</v>
+      </c>
+      <c r="I42" t="n">
+        <v>3</v>
+      </c>
+      <c r="J42" t="n">
+        <v>50</v>
+      </c>
+      <c r="K42" t="n">
+        <v>39</v>
+      </c>
+      <c r="L42" t="n">
+        <v>80</v>
+      </c>
+      <c r="M42" t="n">
+        <v>1</v>
+      </c>
+      <c r="N42" t="n">
+        <v>10275</v>
+      </c>
+      <c r="O42" t="n">
+        <v>18</v>
+      </c>
+      <c r="P42" t="n">
+        <v>541</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>31</v>
+      </c>
+      <c r="R42" t="n">
+        <v>4</v>
+      </c>
+      <c r="S42" t="n">
+        <v>58</v>
+      </c>
+      <c r="T42" t="n">
+        <v>4058</v>
+      </c>
+      <c r="U42" t="n">
+        <v>1</v>
+      </c>
+      <c r="V42" t="n">
+        <v>10024937.95</v>
+      </c>
+      <c r="W42" t="n">
+        <v>10024937.95</v>
+      </c>
+      <c r="X42" t="n">
+        <v>10024937.95</v>
+      </c>
+      <c r="Y42" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>PROTEÇÃO E CONSERVAÇÃO DA FAUNA SILVESTRE</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>PROTEÇÃO DAS ÁREAS AMBIENTALMENTE CONSERVADAS, DA FAUNA E DA BIODIVERSIDADE FLORESTAL</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>Acordo Judicial do Rio Doce</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>ANEXO 10</t>
+        </is>
+      </c>
+      <c r="AD42" t="inlineStr">
+        <is>
+          <t>A CRIAR</t>
+        </is>
+      </c>
+      <c r="AE42" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Elaboração e/ou atualização do ordenamento pesqueiro, na forma da Lei n. 11.959, de 29 de junho de 2009. III. Recomposição da biota, dos recursos e dos estoques pesqueiros do ecossistema como um todo na Bacia Hidrográfica do rio Doce, em sua foz e região costeira e marinha.</t>
+        </is>
+      </c>
+      <c r="AF42" t="inlineStr">
+        <is>
+          <t>Acordo Judicial do Rio Doce - ANEXO 10 - A CRIAR -  Elaboração e/ou atualização do ordenamento pesqueiro, na forma da Lei n. 11.959, de 29 de junho de 2009. III. Recomposição da biota, dos recursos e dos estoques pesqueiros do ecossistema como um todo na Bacia Hidrográfica do rio Doce, em sua foz e região costeira e marinha.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B43" t="n">
+        <v>1370</v>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>SECRETARIA DE ESTADO DE MEIO AMBIENTE E DESENVOLVIMENTO SUSTENTÁVEL - SEMAD</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>3</v>
+      </c>
+      <c r="E43" t="n">
+        <v>0</v>
+      </c>
+      <c r="F43" t="n">
+        <v>2101</v>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>INSTITUTO ESTADUAL DE FLORESTAS - IEF</t>
+        </is>
+      </c>
+      <c r="H43" t="n">
+        <v>3</v>
+      </c>
+      <c r="I43" t="n">
+        <v>3</v>
+      </c>
+      <c r="J43" t="n">
+        <v>50</v>
+      </c>
+      <c r="K43" t="n">
+        <v>39</v>
+      </c>
+      <c r="L43" t="n">
+        <v>80</v>
+      </c>
+      <c r="M43" t="n">
+        <v>1</v>
+      </c>
+      <c r="N43" t="n">
+        <v>10275</v>
+      </c>
+      <c r="O43" t="n">
+        <v>18</v>
+      </c>
+      <c r="P43" t="n">
+        <v>541</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>31</v>
+      </c>
+      <c r="R43" t="n">
+        <v>4</v>
+      </c>
+      <c r="S43" t="n">
+        <v>58</v>
+      </c>
+      <c r="T43" t="n">
+        <v>4058</v>
+      </c>
+      <c r="U43" t="n">
+        <v>1</v>
+      </c>
+      <c r="V43" t="n">
+        <v>3392647.75</v>
+      </c>
+      <c r="W43" t="n">
+        <v>3392647.75</v>
+      </c>
+      <c r="X43" t="n">
+        <v>3392647.75</v>
+      </c>
+      <c r="Y43" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>PROTEÇÃO E CONSERVAÇÃO DA FAUNA SILVESTRE</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>PROTEÇÃO DAS ÁREAS AMBIENTALMENTE CONSERVADAS, DA FAUNA E DA BIODIVERSIDADE FLORESTAL</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>Acordo Judicial do Rio Doce</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>ANEXO 12</t>
+        </is>
+      </c>
+      <c r="AD43" t="n">
+        <v>9456605</v>
+      </c>
+      <c r="AE43" t="inlineStr">
+        <is>
+          <t>Fortalecimento da política pública de gestão do manejo da fauna silvestre, de acordo com mapeamento de necessidades a ser detalhado, a partir de ações como da estruturação e custeio dos serviços prestados pelos Cetras que atendam à bacia hidrográfica do rio Doce; contratação de serviços veterinários especializados; construção de viveiros em áreas de parceiros para a reabilitação e conservação da fauna</t>
+        </is>
+      </c>
+      <c r="AF43" t="inlineStr">
+        <is>
+          <t>Acordo Judicial do Rio Doce - ANEXO 12 - 9456605 - Fortalecimento da política pública de gestão do manejo da fauna silvestre, de acordo com mapeamento de necessidades a ser detalhado, a partir de ações como da estruturação e custeio dos serviços prestados pelos Cetras que atendam à bacia hidrográfica do rio Doce; contratação de serviços veterinários especializados; construção de viveiros em áreas de parceiros para a reabilitação e conservação da fauna</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B44" t="n">
+        <v>1370</v>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>SECRETARIA DE ESTADO DE MEIO AMBIENTE E DESENVOLVIMENTO SUSTENTÁVEL - SEMAD</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>3</v>
+      </c>
+      <c r="E44" t="n">
+        <v>0</v>
+      </c>
+      <c r="F44" t="n">
+        <v>2101</v>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>INSTITUTO ESTADUAL DE FLORESTAS - IEF</t>
+        </is>
+      </c>
+      <c r="H44" t="n">
+        <v>3</v>
+      </c>
+      <c r="I44" t="n">
+        <v>3</v>
+      </c>
+      <c r="J44" t="n">
+        <v>50</v>
+      </c>
+      <c r="K44" t="n">
+        <v>39</v>
+      </c>
+      <c r="L44" t="n">
+        <v>80</v>
+      </c>
+      <c r="M44" t="n">
+        <v>1</v>
+      </c>
+      <c r="N44" t="n">
+        <v>10275</v>
+      </c>
+      <c r="O44" t="n">
+        <v>18</v>
+      </c>
+      <c r="P44" t="n">
+        <v>541</v>
+      </c>
+      <c r="Q44" t="n">
+        <v>31</v>
+      </c>
+      <c r="R44" t="n">
+        <v>4</v>
+      </c>
+      <c r="S44" t="n">
+        <v>58</v>
+      </c>
+      <c r="T44" t="n">
+        <v>4058</v>
+      </c>
+      <c r="U44" t="n">
+        <v>1</v>
+      </c>
+      <c r="V44" t="n">
+        <v>10542586.43</v>
+      </c>
+      <c r="W44" t="n">
+        <v>10542586.43</v>
+      </c>
+      <c r="X44" t="n">
+        <v>10542586.43</v>
+      </c>
+      <c r="Y44" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>PROTEÇÃO E CONSERVAÇÃO DA FAUNA SILVESTRE</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>PROTEÇÃO DAS ÁREAS AMBIENTALMENTE CONSERVADAS, DA FAUNA E DA BIODIVERSIDADE FLORESTAL</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>Acordo Judicial do Rio Doce</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>ANEXO 12</t>
+        </is>
+      </c>
+      <c r="AD44" t="n">
+        <v>9456612</v>
+      </c>
+      <c r="AE44" t="inlineStr">
+        <is>
+          <t>Revitalização aquática da Bacia Hidrográfica do rio Doce, a partir do mapeamento de áreas estratégicas para revitalização e conservação da fauna e flora aquáticas, em especial áreas de cabeceiras, tributários e rotas de piracema, e execução de ações como zoneamento pesqueiro; desassoreamento; reconformação de calhas de rios; renaturalização de leitos de rios; reintrodução de espécies aquáticas ameaçadas; educação ambiental, dentre outras ações baseadas na natureza para a revitalização intracalha do rio Doce e seus tributários</t>
+        </is>
+      </c>
+      <c r="AF44" t="inlineStr">
+        <is>
+          <t>Acordo Judicial do Rio Doce - ANEXO 12 - 9456612 - Revitalização aquática da Bacia Hidrográfica do rio Doce, a partir do mapeamento de áreas estratégicas para revitalização e conservação da fauna e flora aquáticas, em especial áreas de cabeceiras, tributários e rotas de piracema, e execução de ações como zoneamento pesqueiro; desassoreamento; reconformação de calhas de rios; renaturalização de leitos de rios; reintrodução de espécies aquáticas ameaçadas; educação ambiental, dentre outras ações baseadas na natureza para a revitalização intracalha do rio Doce e seus tributários</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B45" t="n">
+        <v>1370</v>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>SECRETARIA DE ESTADO DE MEIO AMBIENTE E DESENVOLVIMENTO SUSTENTÁVEL - SEMAD</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>3</v>
+      </c>
+      <c r="E45" t="n">
+        <v>0</v>
+      </c>
+      <c r="F45" t="n">
+        <v>2101</v>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>INSTITUTO ESTADUAL DE FLORESTAS - IEF</t>
+        </is>
+      </c>
+      <c r="H45" t="n">
+        <v>3</v>
+      </c>
+      <c r="I45" t="n">
+        <v>3</v>
+      </c>
+      <c r="J45" t="n">
+        <v>90</v>
+      </c>
+      <c r="K45" t="n">
+        <v>36</v>
+      </c>
+      <c r="L45" t="n">
+        <v>80</v>
+      </c>
+      <c r="M45" t="n">
+        <v>1</v>
+      </c>
+      <c r="N45" t="n">
+        <v>10275</v>
+      </c>
+      <c r="O45" t="n">
+        <v>18</v>
+      </c>
+      <c r="P45" t="n">
+        <v>541</v>
+      </c>
+      <c r="Q45" t="n">
+        <v>31</v>
+      </c>
+      <c r="R45" t="n">
+        <v>4</v>
+      </c>
+      <c r="S45" t="n">
+        <v>58</v>
+      </c>
+      <c r="T45" t="n">
+        <v>4058</v>
+      </c>
+      <c r="U45" t="n">
+        <v>1</v>
+      </c>
+      <c r="V45" t="n">
+        <v>726819.2</v>
+      </c>
+      <c r="W45" t="n">
+        <v>726819.2</v>
+      </c>
+      <c r="X45" t="n">
+        <v>726819.2</v>
+      </c>
+      <c r="Y45" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>PROTEÇÃO E CONSERVAÇÃO DA FAUNA SILVESTRE</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>PROTEÇÃO DAS ÁREAS AMBIENTALMENTE CONSERVADAS, DA FAUNA E DA BIODIVERSIDADE FLORESTAL</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>Acordo Judicial do Rio Doce</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>ANEXO 12</t>
+        </is>
+      </c>
+      <c r="AD45" t="n">
+        <v>9456605</v>
+      </c>
+      <c r="AE45" t="inlineStr">
+        <is>
+          <t>Fortalecimento da política pública de gestão do manejo da fauna silvestre, de acordo com mapeamento de necessidades a ser detalhado, a partir de ações como da estruturação e custeio dos serviços prestados porelos Cetras que atendam à bacia hidrográfica do rio Doce; contratação de serviços veterinários especializados; construção de viveiros em áreas de parceiros para a reabilitação e conservação da faun</t>
+        </is>
+      </c>
+      <c r="AF45" t="inlineStr">
+        <is>
+          <t>Acordo Judicial do Rio Doce - ANEXO 12 - 9456605 - Fortalecimento da política pública de gestão do manejo da fauna silvestre, de acordo com mapeamento de necessidades a ser detalhado, a partir de ações como da estruturação e custeio dos serviços prestados porelos Cetras que atendam à bacia hidrográfica do rio Doce; contratação de serviços veterinários especializados; construção de viveiros em áreas de parceiros para a reabilitação e conservação da faun</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B46" t="n">
+        <v>1370</v>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>SECRETARIA DE ESTADO DE MEIO AMBIENTE E DESENVOLVIMENTO SUSTENTÁVEL - SEMAD</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>3</v>
+      </c>
+      <c r="E46" t="n">
+        <v>0</v>
+      </c>
+      <c r="F46" t="n">
+        <v>2101</v>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>INSTITUTO ESTADUAL DE FLORESTAS - IEF</t>
+        </is>
+      </c>
+      <c r="H46" t="n">
+        <v>3</v>
+      </c>
+      <c r="I46" t="n">
+        <v>3</v>
+      </c>
+      <c r="J46" t="n">
+        <v>90</v>
+      </c>
+      <c r="K46" t="n">
+        <v>36</v>
+      </c>
+      <c r="L46" t="n">
+        <v>80</v>
+      </c>
+      <c r="M46" t="n">
+        <v>1</v>
+      </c>
+      <c r="N46" t="n">
+        <v>10275</v>
+      </c>
+      <c r="O46" t="n">
+        <v>18</v>
+      </c>
+      <c r="P46" t="n">
+        <v>541</v>
+      </c>
+      <c r="Q46" t="n">
+        <v>31</v>
+      </c>
+      <c r="R46" t="n">
+        <v>4</v>
+      </c>
+      <c r="S46" t="n">
+        <v>58</v>
+      </c>
+      <c r="T46" t="n">
+        <v>4058</v>
+      </c>
+      <c r="U46" t="n">
+        <v>1</v>
+      </c>
+      <c r="V46" t="n">
+        <v>85000</v>
+      </c>
+      <c r="W46" t="n">
+        <v>85000</v>
+      </c>
+      <c r="X46" t="n">
+        <v>85000</v>
+      </c>
+      <c r="Y46" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>PROTEÇÃO E CONSERVAÇÃO DA FAUNA SILVESTRE</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>PROTEÇÃO DAS ÁREAS AMBIENTALMENTE CONSERVADAS, DA FAUNA E DA BIODIVERSIDADE FLORESTAL</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>Acordo Judicial do Rio Doce</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>ANEXO 12</t>
+        </is>
+      </c>
+      <c r="AD46" t="n">
+        <v>9456612</v>
+      </c>
+      <c r="AE46" t="inlineStr">
+        <is>
+          <t>Revitalização aquática da Bacia Hidrográfica do rio Doce, a partir do mapeamento de áreas estratégicas para revitalização e conservação da fauna e flora aquáticas, em especial áreas de cabeceiras, tributários e rotas de piracema, e execução de ações como zoneamento pesqueiro; desassoreamento; reconformação de calhas de rios; renaturalização de leitos de rios; reintrodução de espécies aquáticas ameaçadas; educação ambiental, dentre outras ações baseadas na natureza para a revitalização intracalha do rio Doce e seus tributários</t>
+        </is>
+      </c>
+      <c r="AF46" t="inlineStr">
+        <is>
+          <t>Acordo Judicial do Rio Doce - ANEXO 12 - 9456612 - Revitalização aquática da Bacia Hidrográfica do rio Doce, a partir do mapeamento de áreas estratégicas para revitalização e conservação da fauna e flora aquáticas, em especial áreas de cabeceiras, tributários e rotas de piracema, e execução de ações como zoneamento pesqueiro; desassoreamento; reconformação de calhas de rios; renaturalização de leitos de rios; reintrodução de espécies aquáticas ameaçadas; educação ambiental, dentre outras ações baseadas na natureza para a revitalização intracalha do rio Doce e seus tributários</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B47" t="n">
+        <v>1370</v>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>SECRETARIA DE ESTADO DE MEIO AMBIENTE E DESENVOLVIMENTO SUSTENTÁVEL - SEMAD</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>3</v>
+      </c>
+      <c r="E47" t="n">
+        <v>0</v>
+      </c>
+      <c r="F47" t="n">
+        <v>2101</v>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>INSTITUTO ESTADUAL DE FLORESTAS - IEF</t>
+        </is>
+      </c>
+      <c r="H47" t="n">
+        <v>3</v>
+      </c>
+      <c r="I47" t="n">
+        <v>3</v>
+      </c>
+      <c r="J47" t="n">
+        <v>50</v>
+      </c>
+      <c r="K47" t="n">
+        <v>39</v>
+      </c>
+      <c r="L47" t="n">
+        <v>80</v>
+      </c>
+      <c r="M47" t="n">
+        <v>1</v>
+      </c>
+      <c r="N47" t="n">
+        <v>10276</v>
+      </c>
+      <c r="O47" t="n">
+        <v>18</v>
+      </c>
+      <c r="P47" t="n">
+        <v>541</v>
+      </c>
+      <c r="Q47" t="n">
+        <v>31</v>
+      </c>
+      <c r="R47" t="n">
+        <v>4</v>
+      </c>
+      <c r="S47" t="n">
+        <v>59</v>
+      </c>
+      <c r="T47" t="n">
+        <v>4059</v>
+      </c>
+      <c r="U47" t="n">
+        <v>1</v>
+      </c>
+      <c r="V47" t="n">
+        <v>14093425</v>
+      </c>
+      <c r="W47" t="n">
+        <v>14093425</v>
+      </c>
+      <c r="X47" t="n">
+        <v>14093425</v>
+      </c>
+      <c r="Y47" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>GESTÃO DE UNIDADES E CONSERVAÇÃO</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>PROTEÇÃO DAS ÁREAS AMBIENTALMENTE CONSERVADAS, DA FAUNA E DA BIODIVERSIDADE FLORESTAL</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>Acordo Judicial do Rio Doce</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>ANEXO 12</t>
+        </is>
+      </c>
+      <c r="AD47" t="n">
+        <v>9456606</v>
+      </c>
+      <c r="AE47" t="inlineStr">
+        <is>
+          <t>Consolidação de unidades de conservação estaduais na Bacia Hidrográfica do Rio Doce, a partir do investimento e custeio de suas estruturas e serviços prestados, de acordo com seus objetivos de criação; criação, se necessário, de nova(s) unidade(s) de conservação na Bacia Hidrográfica do Rio Doce de acordo com mapeamento de áreas prioritárias para conservação; realização de atividades de prevenção e combate a incêndios e regularização fundiária das unidades de conservação</t>
+        </is>
+      </c>
+      <c r="AF47" t="inlineStr">
+        <is>
+          <t>Acordo Judicial do Rio Doce - ANEXO 12 - 9456606 - Consolidação de unidades de conservação estaduais na Bacia Hidrográfica do Rio Doce, a partir do investimento e custeio de suas estruturas e serviços prestados, de acordo com seus objetivos de criação; criação, se necessário, de nova(s) unidade(s) de conservação na Bacia Hidrográfica do Rio Doce de acordo com mapeamento de áreas prioritárias para conservação; realização de atividades de prevenção e combate a incêndios e regularização fundiária das unidades de conservação</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B48" t="n">
+        <v>1370</v>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>SECRETARIA DE ESTADO DE MEIO AMBIENTE E DESENVOLVIMENTO SUSTENTÁVEL - SEMAD</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>3</v>
+      </c>
+      <c r="E48" t="n">
+        <v>0</v>
+      </c>
+      <c r="F48" t="n">
+        <v>2101</v>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>INSTITUTO ESTADUAL DE FLORESTAS - IEF</t>
+        </is>
+      </c>
+      <c r="H48" t="n">
+        <v>3</v>
+      </c>
+      <c r="I48" t="n">
+        <v>3</v>
+      </c>
+      <c r="J48" t="n">
+        <v>90</v>
+      </c>
+      <c r="K48" t="n">
+        <v>36</v>
+      </c>
+      <c r="L48" t="n">
+        <v>80</v>
+      </c>
+      <c r="M48" t="n">
+        <v>1</v>
+      </c>
+      <c r="N48" t="n">
+        <v>11201</v>
+      </c>
+      <c r="O48" t="n">
+        <v>18</v>
+      </c>
+      <c r="P48" t="n">
+        <v>541</v>
+      </c>
+      <c r="Q48" t="n">
+        <v>31</v>
+      </c>
+      <c r="R48" t="n">
+        <v>4</v>
+      </c>
+      <c r="S48" t="n">
+        <v>500</v>
+      </c>
+      <c r="T48" t="n">
+        <v>4500</v>
+      </c>
+      <c r="U48" t="n">
+        <v>1</v>
+      </c>
+      <c r="V48" t="n">
+        <v>13318032</v>
+      </c>
+      <c r="W48" t="n">
+        <v>13318032</v>
+      </c>
+      <c r="X48" t="n">
+        <v>13318032</v>
+      </c>
+      <c r="Y48" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>REGULARIZAÇÃO FUNDIÁRIA DE UNIDADES DE CONSERVAÇÃO</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>PROTEÇÃO DAS ÁREAS AMBIENTALMENTE CONSERVADAS, DA FAUNA E DA BIODIVERSIDADE FLORESTAL</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>Acordo Judicial do Rio Doce</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>ANEXO 12</t>
+        </is>
+      </c>
+      <c r="AD48" t="n">
+        <v>9456606</v>
+      </c>
+      <c r="AE48" t="inlineStr">
+        <is>
+          <t>Consolidação de unidades de conservação estaduais na Bacia Hidrográfica do Rio Doce, a partir do investimento e custeio de suas estruturas e serviços prestados, de acordo com seus objetivos de criação; criação, se necessário, de nova(s) unidade(s) de conservação na Bacia Hidrográfica do Rio Doce de acordo com mapeamento de áreas prioritárias para conservação; realização de atividades de prevenção e combate a incêndios e regularização fundiária das unidades de conservação</t>
+        </is>
+      </c>
+      <c r="AF48" t="inlineStr">
+        <is>
+          <t>Acordo Judicial do Rio Doce - ANEXO 12 - 9456606 - Consolidação de unidades de conservação estaduais na Bacia Hidrográfica do Rio Doce, a partir do investimento e custeio de suas estruturas e serviços prestados, de acordo com seus objetivos de criação; criação, se necessário, de nova(s) unidade(s) de conservação na Bacia Hidrográfica do Rio Doce de acordo com mapeamento de áreas prioritárias para conservação; realização de atividades de prevenção e combate a incêndios e regularização fundiária das unidades de conservação</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B49" t="n">
+        <v>1370</v>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>SECRETARIA DE ESTADO DE MEIO AMBIENTE E DESENVOLVIMENTO SUSTENTÁVEL - SEMAD</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>3</v>
+      </c>
+      <c r="E49" t="n">
+        <v>0</v>
+      </c>
+      <c r="F49" t="n">
+        <v>2101</v>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>INSTITUTO ESTADUAL DE FLORESTAS - IEF</t>
+        </is>
+      </c>
+      <c r="H49" t="n">
+        <v>3</v>
+      </c>
+      <c r="I49" t="n">
+        <v>3</v>
+      </c>
+      <c r="J49" t="n">
+        <v>50</v>
+      </c>
+      <c r="K49" t="n">
+        <v>39</v>
+      </c>
+      <c r="L49" t="n">
+        <v>80</v>
+      </c>
+      <c r="M49" t="n">
+        <v>1</v>
+      </c>
+      <c r="N49" t="n">
+        <v>10273</v>
+      </c>
+      <c r="O49" t="n">
+        <v>18</v>
+      </c>
+      <c r="P49" t="n">
+        <v>543</v>
+      </c>
+      <c r="Q49" t="n">
+        <v>31</v>
+      </c>
+      <c r="R49" t="n">
+        <v>4</v>
+      </c>
+      <c r="S49" t="n">
+        <v>56</v>
+      </c>
+      <c r="T49" t="n">
+        <v>4056</v>
+      </c>
+      <c r="U49" t="n">
+        <v>1</v>
+      </c>
+      <c r="V49" t="n">
+        <v>22582986</v>
+      </c>
+      <c r="W49" t="n">
+        <v>22582986</v>
+      </c>
+      <c r="X49" t="n">
+        <v>22582986</v>
+      </c>
+      <c r="Y49" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>RECUPERAÇÃO AMBIENTAL</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>PROTEÇÃO DAS ÁREAS AMBIENTALMENTE CONSERVADAS, DA FAUNA E DA BIODIVERSIDADE FLORESTAL</t>
+        </is>
+      </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>Acordo Judicial do Rio Doce</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>ANEXO 12</t>
+        </is>
+      </c>
+      <c r="AD49" t="n">
+        <v>9445719</v>
+      </c>
+      <c r="AE49" t="inlineStr">
+        <is>
+          <t>Recuperação da vegetação nativa na Bacia Hidrográfica do Rio Doce, com prioridade às áreas de mata ripária, por meio de ações de reflorestamento, pagamento de serviços ambientais, mapeamento do uso de solo e investimento tecnológico para monitoramento da vegetação nativa e sua recuperação</t>
+        </is>
+      </c>
+      <c r="AF49" t="inlineStr">
+        <is>
+          <t>Acordo Judicial do Rio Doce - ANEXO 12 - 9445719 - Recuperação da vegetação nativa na Bacia Hidrográfica do Rio Doce, com prioridade às áreas de mata ripária, por meio de ações de reflorestamento, pagamento de serviços ambientais, mapeamento do uso de solo e investimento tecnológico para monitoramento da vegetação nativa e sua recuperação</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B50" t="n">
+        <v>1370</v>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>SECRETARIA DE ESTADO DE MEIO AMBIENTE E DESENVOLVIMENTO SUSTENTÁVEL - SEMAD</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>3</v>
+      </c>
+      <c r="E50" t="n">
+        <v>0</v>
+      </c>
+      <c r="F50" t="n">
+        <v>2241</v>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>INSTITUTO MINEIRO DE GESTÃO DAS ÁGUAS - IGAM</t>
+        </is>
+      </c>
+      <c r="H50" t="n">
+        <v>3</v>
+      </c>
+      <c r="I50" t="n">
+        <v>3</v>
+      </c>
+      <c r="J50" t="n">
+        <v>50</v>
+      </c>
+      <c r="K50" t="n">
+        <v>41</v>
+      </c>
+      <c r="L50" t="n">
+        <v>80</v>
+      </c>
+      <c r="M50" t="n">
+        <v>1</v>
+      </c>
+      <c r="N50" t="n">
+        <v>10456</v>
+      </c>
+      <c r="O50" t="n">
+        <v>18</v>
+      </c>
+      <c r="P50" t="n">
+        <v>544</v>
+      </c>
+      <c r="Q50" t="n">
+        <v>65</v>
+      </c>
+      <c r="R50" t="n">
+        <v>4</v>
+      </c>
+      <c r="S50" t="n">
+        <v>191</v>
+      </c>
+      <c r="T50" t="n">
+        <v>4191</v>
+      </c>
+      <c r="U50" t="n">
+        <v>1</v>
+      </c>
+      <c r="V50" t="n">
+        <v>6000000</v>
+      </c>
+      <c r="W50" t="n">
+        <v>6000000</v>
+      </c>
+      <c r="X50" t="n">
+        <v>6000000</v>
+      </c>
+      <c r="Y50" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>MONITORAMENTO HIDROMETEOROLOGICO</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>FORTALECIMENTO DA POLÍTICA ESTADUAL DE RECURSOS HÍDRICOS</t>
+        </is>
+      </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>Acordo Judicial do Rio Doce</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>ANEXO 12</t>
+        </is>
+      </c>
+      <c r="AD50" t="inlineStr">
+        <is>
+          <t>A SER CRIADO</t>
+        </is>
+      </c>
+      <c r="AE50" t="inlineStr">
+        <is>
+          <t>Ampliação, modernização e equipagem da rede meteorológica, rede hidrológica e Sala de Situação para eventos hidrológicos críticos, de forma a aprimorar a capacidade do Sistema Estadual de Meio Ambiente (SISEMA) de acompanhar a recuperação da Bacia Hidrográfica do Rio Doce vis-à-vis riscos decorrentes de eventos climáticos extremos.</t>
+        </is>
+      </c>
+      <c r="AF50" t="inlineStr">
+        <is>
+          <t>Acordo Judicial do Rio Doce - ANEXO 12 - A SER CRIADO - Ampliação, modernização e equipagem da rede meteorológica, rede hidrológica e Sala de Situação para eventos hidrológicos críticos, de forma a aprimorar a capacidade do Sistema Estadual de Meio Ambiente (SISEMA) de acompanhar a recuperação da Bacia Hidrográfica do Rio Doce vis-à-vis riscos decorrentes de eventos climáticos extremos.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B51" t="n">
+        <v>1370</v>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>SECRETARIA DE ESTADO DE MEIO AMBIENTE E DESENVOLVIMENTO SUSTENTÁVEL - SEMAD</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>3</v>
+      </c>
+      <c r="E51" t="n">
+        <v>0</v>
+      </c>
+      <c r="F51" t="n">
+        <v>2241</v>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>INSTITUTO MINEIRO DE GESTÃO DAS ÁGUAS - IGAM</t>
+        </is>
+      </c>
+      <c r="H51" t="n">
+        <v>3</v>
+      </c>
+      <c r="I51" t="n">
+        <v>3</v>
+      </c>
+      <c r="J51" t="n">
+        <v>90</v>
+      </c>
+      <c r="K51" t="n">
+        <v>39</v>
+      </c>
+      <c r="L51" t="n">
+        <v>80</v>
+      </c>
+      <c r="M51" t="n">
+        <v>1</v>
+      </c>
+      <c r="N51" t="n">
+        <v>10456</v>
+      </c>
+      <c r="O51" t="n">
+        <v>18</v>
+      </c>
+      <c r="P51" t="n">
+        <v>544</v>
+      </c>
+      <c r="Q51" t="n">
+        <v>65</v>
+      </c>
+      <c r="R51" t="n">
+        <v>4</v>
+      </c>
+      <c r="S51" t="n">
+        <v>191</v>
+      </c>
+      <c r="T51" t="n">
+        <v>4191</v>
+      </c>
+      <c r="U51" t="n">
+        <v>1</v>
+      </c>
+      <c r="V51" t="n">
+        <v>10000000</v>
+      </c>
+      <c r="W51" t="n">
+        <v>10000000</v>
+      </c>
+      <c r="X51" t="n">
+        <v>10000000</v>
+      </c>
+      <c r="Y51" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>MONITORAMENTO HIDROMETEOROLOGICO</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>FORTALECIMENTO DA POLÍTICA ESTADUAL DE RECURSOS HÍDRICOS</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>Acordo Judicial do Rio Doce</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>ANEXO 12</t>
+        </is>
+      </c>
+      <c r="AD51" t="inlineStr">
+        <is>
+          <t>A SER CRIADO</t>
+        </is>
+      </c>
+      <c r="AE51" t="inlineStr">
+        <is>
+          <t>Ampliação, modernização e equipagem da rede meteorológica, rede hidrológica e Sala de Situação para eventos hidrológicos críticos, de forma a aprimorar a capacidade do Sistema Estadual de Meio Ambiente (SISEMA) de acompanhar a recuperação da Bacia Hidrográfica do Rio Doce vis-à-vis riscos decorrentes de eventos climáticos extremos.</t>
+        </is>
+      </c>
+      <c r="AF51" t="inlineStr">
+        <is>
+          <t>Acordo Judicial do Rio Doce - ANEXO 12 - A SER CRIADO - Ampliação, modernização e equipagem da rede meteorológica, rede hidrológica e Sala de Situação para eventos hidrológicos críticos, de forma a aprimorar a capacidade do Sistema Estadual de Meio Ambiente (SISEMA) de acompanhar a recuperação da Bacia Hidrográfica do Rio Doce vis-à-vis riscos decorrentes de eventos climáticos extremos.</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B52" t="n">
+        <v>1370</v>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>SECRETARIA DE ESTADO DE MEIO AMBIENTE E DESENVOLVIMENTO SUSTENTÁVEL - SEMAD</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>3</v>
+      </c>
+      <c r="E52" t="n">
+        <v>0</v>
+      </c>
+      <c r="F52" t="n">
+        <v>2241</v>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>INSTITUTO MINEIRO DE GESTÃO DAS ÁGUAS - IGAM</t>
+        </is>
+      </c>
+      <c r="H52" t="n">
+        <v>3</v>
+      </c>
+      <c r="I52" t="n">
+        <v>3</v>
+      </c>
+      <c r="J52" t="n">
+        <v>90</v>
+      </c>
+      <c r="K52" t="n">
+        <v>40</v>
+      </c>
+      <c r="L52" t="n">
+        <v>80</v>
+      </c>
+      <c r="M52" t="n">
+        <v>1</v>
+      </c>
+      <c r="N52" t="n">
+        <v>10456</v>
+      </c>
+      <c r="O52" t="n">
+        <v>18</v>
+      </c>
+      <c r="P52" t="n">
+        <v>544</v>
+      </c>
+      <c r="Q52" t="n">
+        <v>65</v>
+      </c>
+      <c r="R52" t="n">
+        <v>4</v>
+      </c>
+      <c r="S52" t="n">
+        <v>191</v>
+      </c>
+      <c r="T52" t="n">
+        <v>4191</v>
+      </c>
+      <c r="U52" t="n">
+        <v>1</v>
+      </c>
+      <c r="V52" t="n">
+        <v>5335000</v>
+      </c>
+      <c r="W52" t="n">
+        <v>5335000</v>
+      </c>
+      <c r="X52" t="n">
+        <v>5335000</v>
+      </c>
+      <c r="Y52" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>MONITORAMENTO HIDROMETEOROLOGICO</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>FORTALECIMENTO DA POLÍTICA ESTADUAL DE RECURSOS HÍDRICOS</t>
+        </is>
+      </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>Acordo Judicial do Rio Doce</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>ANEXO 12</t>
+        </is>
+      </c>
+      <c r="AD52" t="inlineStr">
+        <is>
+          <t>A SER CRIADO</t>
+        </is>
+      </c>
+      <c r="AE52" t="inlineStr">
+        <is>
+          <t>Ampliação, modernização e equipagem da rede meteorológica, rede hidrológica e Sala de Situação para eventos hidrológicos críticos, de forma a aprimorar a capacidade do Sistema Estadual de Meio Ambiente (SISEMA) de acompanhar a recuperação da Bacia Hidrográfica do Rio Doce vis-à-vis riscos decorrentes de eventos climáticos extremos.</t>
+        </is>
+      </c>
+      <c r="AF52" t="inlineStr">
+        <is>
+          <t>Acordo Judicial do Rio Doce - ANEXO 12 - A SER CRIADO - Ampliação, modernização e equipagem da rede meteorológica, rede hidrológica e Sala de Situação para eventos hidrológicos críticos, de forma a aprimorar a capacidade do Sistema Estadual de Meio Ambiente (SISEMA) de acompanhar a recuperação da Bacia Hidrográfica do Rio Doce vis-à-vis riscos decorrentes de eventos climáticos extremos.</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B53" t="n">
+        <v>1370</v>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>SECRETARIA DE ESTADO DE MEIO AMBIENTE E DESENVOLVIMENTO SUSTENTÁVEL - SEMAD</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>3</v>
+      </c>
+      <c r="E53" t="n">
+        <v>0</v>
+      </c>
+      <c r="F53" t="n">
+        <v>2241</v>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>INSTITUTO MINEIRO DE GESTÃO DAS ÁGUAS - IGAM</t>
+        </is>
+      </c>
+      <c r="H53" t="n">
+        <v>4</v>
+      </c>
+      <c r="I53" t="n">
+        <v>4</v>
+      </c>
+      <c r="J53" t="n">
+        <v>90</v>
+      </c>
+      <c r="K53" t="n">
+        <v>52</v>
+      </c>
+      <c r="L53" t="n">
+        <v>80</v>
+      </c>
+      <c r="M53" t="n">
+        <v>1</v>
+      </c>
+      <c r="N53" t="n">
+        <v>10456</v>
+      </c>
+      <c r="O53" t="n">
+        <v>18</v>
+      </c>
+      <c r="P53" t="n">
+        <v>544</v>
+      </c>
+      <c r="Q53" t="n">
+        <v>65</v>
+      </c>
+      <c r="R53" t="n">
+        <v>4</v>
+      </c>
+      <c r="S53" t="n">
+        <v>191</v>
+      </c>
+      <c r="T53" t="n">
+        <v>4191</v>
+      </c>
+      <c r="U53" t="n">
+        <v>1</v>
+      </c>
+      <c r="V53" t="n">
+        <v>35000000</v>
+      </c>
+      <c r="W53" t="n">
+        <v>35000000</v>
+      </c>
+      <c r="X53" t="n">
+        <v>35000000</v>
+      </c>
+      <c r="Y53" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>MONITORAMENTO HIDROMETEOROLOGICO</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>FORTALECIMENTO DA POLÍTICA ESTADUAL DE RECURSOS HÍDRICOS</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>Acordo Judicial do Rio Doce</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>ANEXO 12</t>
+        </is>
+      </c>
+      <c r="AD53" t="inlineStr">
+        <is>
+          <t>A SER CRIADO</t>
+        </is>
+      </c>
+      <c r="AE53" t="inlineStr">
+        <is>
+          <t>Ampliação, modernização e equipagem da rede meteorológica, rede hidrológica e Sala de Situação para eventos hidrológicos críticos, de forma a aprimorar a capacidade do Sistema Estadual de Meio Ambiente (SISEMA) de acompanhar a recuperação da Bacia Hidrográfica do Rio Doce vis-à-vis riscos decorrentes de eventos climáticos extremos.</t>
+        </is>
+      </c>
+      <c r="AF53" t="inlineStr">
+        <is>
+          <t>Acordo Judicial do Rio Doce - ANEXO 12 - A SER CRIADO - Ampliação, modernização e equipagem da rede meteorológica, rede hidrológica e Sala de Situação para eventos hidrológicos críticos, de forma a aprimorar a capacidade do Sistema Estadual de Meio Ambiente (SISEMA) de acompanhar a recuperação da Bacia Hidrográfica do Rio Doce vis-à-vis riscos decorrentes de eventos climáticos extremos.</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B54" t="n">
+        <v>1370</v>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>SECRETARIA DE ESTADO DE MEIO AMBIENTE E DESENVOLVIMENTO SUSTENTÁVEL - SEMAD</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>3</v>
+      </c>
+      <c r="E54" t="n">
+        <v>0</v>
+      </c>
+      <c r="F54" t="n">
+        <v>2241</v>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>INSTITUTO MINEIRO DE GESTÃO DAS ÁGUAS - IGAM</t>
+        </is>
+      </c>
+      <c r="H54" t="n">
+        <v>3</v>
+      </c>
+      <c r="I54" t="n">
+        <v>3</v>
+      </c>
+      <c r="J54" t="n">
+        <v>90</v>
+      </c>
+      <c r="K54" t="n">
+        <v>40</v>
+      </c>
+      <c r="L54" t="n">
+        <v>80</v>
+      </c>
+      <c r="M54" t="n">
+        <v>1</v>
+      </c>
+      <c r="N54" t="n">
+        <v>10457</v>
+      </c>
+      <c r="O54" t="n">
+        <v>18</v>
+      </c>
+      <c r="P54" t="n">
+        <v>544</v>
+      </c>
+      <c r="Q54" t="n">
+        <v>65</v>
+      </c>
+      <c r="R54" t="n">
+        <v>4</v>
+      </c>
+      <c r="S54" t="n">
+        <v>192</v>
+      </c>
+      <c r="T54" t="n">
+        <v>4192</v>
+      </c>
+      <c r="U54" t="n">
+        <v>1</v>
+      </c>
+      <c r="V54" t="n">
+        <v>1686667</v>
+      </c>
+      <c r="W54" t="n">
+        <v>1686667</v>
+      </c>
+      <c r="X54" t="n">
+        <v>1686667</v>
+      </c>
+      <c r="Y54" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>SEGURANÇA DE BARRAGENS</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>FORTALECIMENTO DA POLÍTICA ESTADUAL DE RECURSOS HÍDRICOS</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>Acordo Judicial do Rio Doce</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>ANEXO 12</t>
+        </is>
+      </c>
+      <c r="AD54" t="inlineStr">
+        <is>
+          <t>A SER CRIADO</t>
+        </is>
+      </c>
+      <c r="AE54" t="inlineStr">
+        <is>
+          <t>Melhoria na capacidade estadual fiscalizatória de barragens nas estruturas localizadas na extensão territorial da Bacia Hidrográfica do Rio Doce: aquisição de equipamentos físicos e tecnológicos, contratação de serviços de consultoria</t>
+        </is>
+      </c>
+      <c r="AF54" t="inlineStr">
+        <is>
+          <t>Acordo Judicial do Rio Doce - ANEXO 12 - A SER CRIADO - Melhoria na capacidade estadual fiscalizatória de barragens nas estruturas localizadas na extensão territorial da Bacia Hidrográfica do Rio Doce: aquisição de equipamentos físicos e tecnológicos, contratação de serviços de consultoria</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B55" t="n">
+        <v>1480</v>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO SOCIAL - SEDESE</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>3</v>
+      </c>
+      <c r="E55" t="n">
+        <v>0</v>
+      </c>
+      <c r="F55" t="n">
+        <v>1481</v>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO SOCIAL - SEDESE</t>
+        </is>
+      </c>
+      <c r="H55" t="n">
+        <v>3</v>
+      </c>
+      <c r="I55" t="n">
+        <v>3</v>
+      </c>
+      <c r="J55" t="n">
+        <v>90</v>
+      </c>
+      <c r="K55" t="n">
+        <v>37</v>
+      </c>
+      <c r="L55" t="n">
+        <v>80</v>
+      </c>
+      <c r="M55" t="n">
+        <v>1</v>
+      </c>
+      <c r="N55" t="n">
+        <v>10419</v>
+      </c>
+      <c r="O55" t="n">
+        <v>11</v>
+      </c>
+      <c r="P55" t="n">
+        <v>334</v>
+      </c>
+      <c r="Q55" t="n">
+        <v>66</v>
+      </c>
+      <c r="R55" t="n">
+        <v>4</v>
+      </c>
+      <c r="S55" t="n">
+        <v>154</v>
+      </c>
+      <c r="T55" t="n">
+        <v>4154</v>
+      </c>
+      <c r="U55" t="n">
+        <v>1</v>
+      </c>
+      <c r="V55" t="n">
+        <v>220000</v>
+      </c>
+      <c r="W55" t="n">
+        <v>220000</v>
+      </c>
+      <c r="X55" t="n">
+        <v>220000</v>
+      </c>
+      <c r="Y55" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>FOMENTO PARA ECONOMIA POPULAR SOLIDÁRIA E PROMOÇÃO DA INCLUSÃO PRODUTIVA</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>POLÍTICAS DE TRABALHO E EMPREGO</t>
+        </is>
+      </c>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>Acordo Judicial do Rio Doce</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>ANEXO 12</t>
+        </is>
+      </c>
+      <c r="AD55" t="n">
+        <v>9456618</v>
+      </c>
+      <c r="AE55" t="inlineStr">
+        <is>
+          <t>Disponibilização de microcrédito para financiamento de atividades produtivas, podendo ter o apoio de agentes de crédito facilitadores</t>
+        </is>
+      </c>
+      <c r="AF55" t="inlineStr">
+        <is>
+          <t>Acordo Judicial do Rio Doce - ANEXO 12 - 9456618 - Disponibilização de microcrédito para financiamento de atividades produtivas, podendo ter o apoio de agentes de crédito facilitadores</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B56" t="n">
+        <v>1480</v>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO SOCIAL - SEDESE</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>3</v>
+      </c>
+      <c r="E56" t="n">
+        <v>0</v>
+      </c>
+      <c r="F56" t="n">
+        <v>1481</v>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO SOCIAL - SEDESE</t>
+        </is>
+      </c>
+      <c r="H56" t="n">
+        <v>3</v>
+      </c>
+      <c r="I56" t="n">
+        <v>3</v>
+      </c>
+      <c r="J56" t="n">
+        <v>90</v>
+      </c>
+      <c r="K56" t="n">
+        <v>39</v>
+      </c>
+      <c r="L56" t="n">
+        <v>80</v>
+      </c>
+      <c r="M56" t="n">
+        <v>1</v>
+      </c>
+      <c r="N56" t="n">
+        <v>10419</v>
+      </c>
+      <c r="O56" t="n">
+        <v>11</v>
+      </c>
+      <c r="P56" t="n">
+        <v>334</v>
+      </c>
+      <c r="Q56" t="n">
+        <v>66</v>
+      </c>
+      <c r="R56" t="n">
+        <v>4</v>
+      </c>
+      <c r="S56" t="n">
+        <v>154</v>
+      </c>
+      <c r="T56" t="n">
+        <v>4154</v>
+      </c>
+      <c r="U56" t="n">
+        <v>1</v>
+      </c>
+      <c r="V56" t="n">
+        <v>6878500</v>
+      </c>
+      <c r="W56" t="n">
+        <v>6878500</v>
+      </c>
+      <c r="X56" t="n">
+        <v>6878500</v>
+      </c>
+      <c r="Y56" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>FOMENTO PARA ECONOMIA POPULAR SOLIDÁRIA E PROMOÇÃO DA INCLUSÃO PRODUTIVA</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>POLÍTICAS DE TRABALHO E EMPREGO</t>
+        </is>
+      </c>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>Acordo Judicial do Rio Doce</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>ANEXO 12</t>
+        </is>
+      </c>
+      <c r="AD56" t="n">
+        <v>9456618</v>
+      </c>
+      <c r="AE56" t="inlineStr">
+        <is>
+          <t>Disponibilização de microcrédito para financiamento de atividades produtivas, podendo ter o apoio de agentes de crédito facilitadores</t>
+        </is>
+      </c>
+      <c r="AF56" t="inlineStr">
+        <is>
+          <t>Acordo Judicial do Rio Doce - ANEXO 12 - 9456618 - Disponibilização de microcrédito para financiamento de atividades produtivas, podendo ter o apoio de agentes de crédito facilitadores</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B57" t="n">
+        <v>1480</v>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO SOCIAL - SEDESE</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>3</v>
+      </c>
+      <c r="E57" t="n">
+        <v>0</v>
+      </c>
+      <c r="F57" t="n">
+        <v>1481</v>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO SOCIAL - SEDESE</t>
+        </is>
+      </c>
+      <c r="H57" t="n">
+        <v>3</v>
+      </c>
+      <c r="I57" t="n">
+        <v>3</v>
+      </c>
+      <c r="J57" t="n">
+        <v>90</v>
+      </c>
+      <c r="K57" t="n">
+        <v>37</v>
+      </c>
+      <c r="L57" t="n">
+        <v>80</v>
+      </c>
+      <c r="M57" t="n">
+        <v>1</v>
+      </c>
+      <c r="N57" t="n">
+        <v>10423</v>
+      </c>
+      <c r="O57" t="n">
+        <v>11</v>
+      </c>
+      <c r="P57" t="n">
+        <v>363</v>
+      </c>
+      <c r="Q57" t="n">
+        <v>67</v>
+      </c>
+      <c r="R57" t="n">
+        <v>4</v>
+      </c>
+      <c r="S57" t="n">
+        <v>158</v>
+      </c>
+      <c r="T57" t="n">
+        <v>4158</v>
+      </c>
+      <c r="U57" t="n">
+        <v>1</v>
+      </c>
+      <c r="V57" t="n">
+        <v>440000</v>
+      </c>
+      <c r="W57" t="n">
+        <v>440000</v>
+      </c>
+      <c r="X57" t="n">
+        <v>440000</v>
+      </c>
+      <c r="Y57" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>QUALIFICAÇÃO PROFISSIONAL</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>REDE DE DESENVOLVIMENTO DA EDUCAÇÃO PROFISSIONAL</t>
+        </is>
+      </c>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>Acordo Judicial do Rio Doce</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>ANEXO 12</t>
+        </is>
+      </c>
+      <c r="AD57" t="n">
+        <v>9456621</v>
+      </c>
+      <c r="AE57" t="inlineStr">
+        <is>
+          <t>Oferta de cursos de qualificação profissional a partir de estudo de demandas do mercado de trabalho - SEDESE</t>
+        </is>
+      </c>
+      <c r="AF57" t="inlineStr">
+        <is>
+          <t>Acordo Judicial do Rio Doce - ANEXO 12 - 9456621 - Oferta de cursos de qualificação profissional a partir de estudo de demandas do mercado de trabalho - SEDESE</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B58" t="n">
+        <v>1480</v>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO SOCIAL - SEDESE</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>3</v>
+      </c>
+      <c r="E58" t="n">
+        <v>0</v>
+      </c>
+      <c r="F58" t="n">
+        <v>1481</v>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO SOCIAL - SEDESE</t>
+        </is>
+      </c>
+      <c r="H58" t="n">
+        <v>3</v>
+      </c>
+      <c r="I58" t="n">
+        <v>3</v>
+      </c>
+      <c r="J58" t="n">
+        <v>90</v>
+      </c>
+      <c r="K58" t="n">
+        <v>39</v>
+      </c>
+      <c r="L58" t="n">
+        <v>80</v>
+      </c>
+      <c r="M58" t="n">
+        <v>1</v>
+      </c>
+      <c r="N58" t="n">
+        <v>10423</v>
+      </c>
+      <c r="O58" t="n">
+        <v>11</v>
+      </c>
+      <c r="P58" t="n">
+        <v>363</v>
+      </c>
+      <c r="Q58" t="n">
+        <v>67</v>
+      </c>
+      <c r="R58" t="n">
+        <v>4</v>
+      </c>
+      <c r="S58" t="n">
+        <v>158</v>
+      </c>
+      <c r="T58" t="n">
+        <v>4158</v>
+      </c>
+      <c r="U58" t="n">
+        <v>1</v>
+      </c>
+      <c r="V58" t="n">
+        <v>2709019</v>
+      </c>
+      <c r="W58" t="n">
+        <v>2709019</v>
+      </c>
+      <c r="X58" t="n">
+        <v>2709019</v>
+      </c>
+      <c r="Y58" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>QUALIFICAÇÃO PROFISSIONAL</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>REDE DE DESENVOLVIMENTO DA EDUCAÇÃO PROFISSIONAL</t>
+        </is>
+      </c>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>Acordo Judicial do Rio Doce</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>ANEXO 12</t>
+        </is>
+      </c>
+      <c r="AD58" t="n">
+        <v>9456621</v>
+      </c>
+      <c r="AE58" t="inlineStr">
+        <is>
+          <t>Oferta de cursos de qualificação profissional a partir de estudo de demandas do mercado de trabalho - SEDESE</t>
+        </is>
+      </c>
+      <c r="AF58" t="inlineStr">
+        <is>
+          <t>Acordo Judicial do Rio Doce - ANEXO 12 - 9456621 - Oferta de cursos de qualificação profissional a partir de estudo de demandas do mercado de trabalho - SEDESE</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B59" t="n">
+        <v>1480</v>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO SOCIAL - SEDESE</t>
+        </is>
+      </c>
+      <c r="D59" t="n">
+        <v>3</v>
+      </c>
+      <c r="E59" t="n">
+        <v>0</v>
+      </c>
+      <c r="F59" t="n">
+        <v>4251</v>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>FUNDO ESTADUAL DE ASSISTÊNCIA SOCIAL - FEAS</t>
+        </is>
+      </c>
+      <c r="H59" t="n">
+        <v>3</v>
+      </c>
+      <c r="I59" t="n">
+        <v>3</v>
+      </c>
+      <c r="J59" t="n">
+        <v>41</v>
+      </c>
+      <c r="K59" t="n">
+        <v>41</v>
+      </c>
+      <c r="L59" t="n">
+        <v>80</v>
+      </c>
+      <c r="M59" t="n">
+        <v>1</v>
+      </c>
+      <c r="N59" t="n">
+        <v>11267</v>
+      </c>
+      <c r="O59" t="n">
+        <v>8</v>
+      </c>
+      <c r="P59" t="n">
+        <v>244</v>
+      </c>
+      <c r="Q59" t="n">
+        <v>71</v>
+      </c>
+      <c r="R59" t="n">
+        <v>4</v>
+      </c>
+      <c r="S59" t="n">
+        <v>402</v>
+      </c>
+      <c r="T59" t="n">
+        <v>4402</v>
+      </c>
+      <c r="U59" t="n">
+        <v>1</v>
+      </c>
+      <c r="V59" t="n">
+        <v>5952959</v>
+      </c>
+      <c r="W59" t="n">
+        <v>5952959</v>
+      </c>
+      <c r="X59" t="n">
+        <v>5952959</v>
+      </c>
+      <c r="Y59" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t>FORTALECIMENTO DO SUAS NA BACIA DO RIO DOCE</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>FORTALECIMENTO DO SISTEMA ÚNICO DE ASSISTÊNCIA SOCIAL - SUAS</t>
+        </is>
+      </c>
+      <c r="AB59" t="inlineStr">
+        <is>
+          <t>Acordo Judicial do Rio Doce</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>ANEXO 12</t>
+        </is>
+      </c>
+      <c r="AD59" t="n">
+        <v>9445718</v>
+      </c>
+      <c r="AE59" t="inlineStr">
+        <is>
+          <t>Fortalecimento do atendimento da rede socioassistencial com execução de um plano de melhorias, que inclua, preferencialmente, construção e reforma de unidades do Centro de Referência de Assistência Social (CRAS) e Centro de Referência Especializado de Assistência Social (CREAS), contratação de equipe técnica e aquisição de material de consumo de acordo com detalhamento a ser construído prioritariamente</t>
+        </is>
+      </c>
+      <c r="AF59" t="inlineStr">
+        <is>
+          <t>Acordo Judicial do Rio Doce - ANEXO 12 - 9445718 - Fortalecimento do atendimento da rede socioassistencial com execução de um plano de melhorias, que inclua, preferencialmente, construção e reforma de unidades do Centro de Referência de Assistência Social (CRAS) e Centro de Referência Especializado de Assistência Social (CREAS), contratação de equipe técnica e aquisição de material de consumo de acordo com detalhamento a ser construído prioritariamente</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B60" t="n">
+        <v>1480</v>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO SOCIAL - SEDESE</t>
+        </is>
+      </c>
+      <c r="D60" t="n">
+        <v>3</v>
+      </c>
+      <c r="E60" t="n">
+        <v>0</v>
+      </c>
+      <c r="F60" t="n">
+        <v>4251</v>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>FUNDO ESTADUAL DE ASSISTÊNCIA SOCIAL - FEAS</t>
+        </is>
+      </c>
+      <c r="H60" t="n">
+        <v>4</v>
+      </c>
+      <c r="I60" t="n">
+        <v>4</v>
+      </c>
+      <c r="J60" t="n">
+        <v>40</v>
+      </c>
+      <c r="K60" t="n">
+        <v>42</v>
+      </c>
+      <c r="L60" t="n">
+        <v>80</v>
+      </c>
+      <c r="M60" t="n">
+        <v>1</v>
+      </c>
+      <c r="N60" t="n">
+        <v>11267</v>
+      </c>
+      <c r="O60" t="n">
+        <v>8</v>
+      </c>
+      <c r="P60" t="n">
+        <v>244</v>
+      </c>
+      <c r="Q60" t="n">
+        <v>71</v>
+      </c>
+      <c r="R60" t="n">
+        <v>4</v>
+      </c>
+      <c r="S60" t="n">
+        <v>402</v>
+      </c>
+      <c r="T60" t="n">
+        <v>4402</v>
+      </c>
+      <c r="U60" t="n">
+        <v>1</v>
+      </c>
+      <c r="V60" t="n">
+        <v>27847404</v>
+      </c>
+      <c r="W60" t="n">
+        <v>27847404</v>
+      </c>
+      <c r="X60" t="n">
+        <v>27847404</v>
+      </c>
+      <c r="Y60" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z60" t="inlineStr">
+        <is>
+          <t>FORTALECIMENTO DO SUAS NA BACIA DO RIO DOCE</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>FORTALECIMENTO DO SISTEMA ÚNICO DE ASSISTÊNCIA SOCIAL - SUAS</t>
+        </is>
+      </c>
+      <c r="AB60" t="inlineStr">
+        <is>
+          <t>Acordo Judicial do Rio Doce</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>ANEXO 12</t>
+        </is>
+      </c>
+      <c r="AD60" t="n">
+        <v>9445718</v>
+      </c>
+      <c r="AE60" t="inlineStr">
+        <is>
+          <t>Fortalecimento do atendimento da rede socioassistencial com execução de um plano de melhorias, que inclua, preferencialmente, construção e reforma de unidades do Centro de Referência de Assistência Social (CRAS) e Centro de Referência Especializado de Assistência Social (CREAS), contratação de equipe técnica e aquisição de material de consumo de acordo com detalhamento a ser construído prioritariamente</t>
+        </is>
+      </c>
+      <c r="AF60" t="inlineStr">
+        <is>
+          <t>Acordo Judicial do Rio Doce - ANEXO 12 - 9445718 - Fortalecimento do atendimento da rede socioassistencial com execução de um plano de melhorias, que inclua, preferencialmente, construção e reforma de unidades do Centro de Referência de Assistência Social (CRAS) e Centro de Referência Especializado de Assistência Social (CREAS), contratação de equipe técnica e aquisição de material de consumo de acordo com detalhamento a ser construído prioritariamente</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B61" t="n">
+        <v>1480</v>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO SOCIAL - SEDESE</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
+        <v>3</v>
+      </c>
+      <c r="E61" t="n">
+        <v>0</v>
+      </c>
+      <c r="F61" t="n">
+        <v>4251</v>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>FUNDO ESTADUAL DE ASSISTÊNCIA SOCIAL - FEAS</t>
+        </is>
+      </c>
+      <c r="H61" t="n">
+        <v>3</v>
+      </c>
+      <c r="I61" t="n">
+        <v>3</v>
+      </c>
+      <c r="J61" t="n">
+        <v>90</v>
+      </c>
+      <c r="K61" t="n">
+        <v>37</v>
+      </c>
+      <c r="L61" t="n">
+        <v>80</v>
+      </c>
+      <c r="M61" t="n">
+        <v>1</v>
+      </c>
+      <c r="N61" t="n">
+        <v>10777</v>
+      </c>
+      <c r="O61" t="n">
+        <v>8</v>
+      </c>
+      <c r="P61" t="n">
+        <v>244</v>
+      </c>
+      <c r="Q61" t="n">
+        <v>71</v>
+      </c>
+      <c r="R61" t="n">
+        <v>4</v>
+      </c>
+      <c r="S61" t="n">
+        <v>433</v>
+      </c>
+      <c r="T61" t="n">
+        <v>4433</v>
+      </c>
+      <c r="U61" t="n">
+        <v>1</v>
+      </c>
+      <c r="V61" t="n">
+        <v>1600000</v>
+      </c>
+      <c r="W61" t="n">
+        <v>1600000</v>
+      </c>
+      <c r="X61" t="n">
+        <v>1600000</v>
+      </c>
+      <c r="Y61" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z61" t="inlineStr">
+        <is>
+          <t>GESTÃO DA POLÍTICA ESTADUAL DE ASSISTÊNCIA SOCIAL</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>FORTALECIMENTO DO SISTEMA ÚNICO DE ASSISTÊNCIA SOCIAL - SUAS</t>
+        </is>
+      </c>
+      <c r="AB61" t="inlineStr">
+        <is>
+          <t>Acordo Judicial do Rio Doce</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>ANEXO 07</t>
+        </is>
+      </c>
+      <c r="AD61" t="n">
+        <v>9445684</v>
+      </c>
+      <c r="AE61" t="inlineStr">
+        <is>
+          <t>Repasse ao Fundo Estadual de Assistência Social (FEAS) do ESTADO DE MINAS GERAIS  (pendente criação de inciativas)</t>
+        </is>
+      </c>
+      <c r="AF61" t="inlineStr">
+        <is>
+          <t>Acordo Judicial do Rio Doce - ANEXO 07 - 9445684 - Repasse ao Fundo Estadual de Assistência Social (FEAS) do ESTADO DE MINAS GERAIS  (pendente criação de inciativas)</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B62" t="n">
+        <v>1500</v>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>SECRETARIA DE ESTADO DE PLANEJAMENTO E GESTÃO - SEPLAG</t>
+        </is>
+      </c>
+      <c r="D62" t="n">
+        <v>3</v>
+      </c>
+      <c r="E62" t="n">
+        <v>0</v>
+      </c>
+      <c r="F62" t="n">
+        <v>1501</v>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>SECRETARIA DE ESTADO DE PLANEJAMENTO E GESTÃO - SEPLAG</t>
+        </is>
+      </c>
+      <c r="H62" t="n">
+        <v>3</v>
+      </c>
+      <c r="I62" t="n">
+        <v>1</v>
+      </c>
+      <c r="J62" t="n">
+        <v>90</v>
+      </c>
+      <c r="K62" t="n">
+        <v>11</v>
+      </c>
+      <c r="L62" t="n">
+        <v>80</v>
+      </c>
+      <c r="M62" t="n">
+        <v>1</v>
+      </c>
+      <c r="N62" t="n">
+        <v>10819</v>
+      </c>
+      <c r="O62" t="n">
+        <v>4</v>
+      </c>
+      <c r="P62" t="n">
+        <v>122</v>
+      </c>
+      <c r="Q62" t="n">
+        <v>155</v>
+      </c>
+      <c r="R62" t="n">
+        <v>4</v>
+      </c>
+      <c r="S62" t="n">
+        <v>461</v>
+      </c>
+      <c r="T62" t="n">
+        <v>4461</v>
+      </c>
+      <c r="U62" t="n">
+        <v>1</v>
+      </c>
+      <c r="V62" t="n">
+        <v>465500</v>
+      </c>
+      <c r="W62" t="n">
+        <v>465500</v>
+      </c>
+      <c r="X62" t="n">
+        <v>465500</v>
+      </c>
+      <c r="Y62" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z62" t="inlineStr">
+        <is>
+          <t>RECUPERAÇÃO E COMPENSAÇÃO DOS DANOS EM FUNÇÃO DO DESASTRE MINERÁRIO DA SAMARCO EM MARIANA</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>REPARAÇÃO DOS DANOS DOS ROMPIMENTOS EM BRUMADINHO E MARIANA</t>
+        </is>
+      </c>
+      <c r="AB62" t="inlineStr">
+        <is>
+          <t>Acordo Judicial do Rio Doce</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>ANEXO 12</t>
+        </is>
+      </c>
+      <c r="AD62" t="n">
+        <v>9468055</v>
+      </c>
+      <c r="AE62" t="inlineStr">
+        <is>
+          <t>Suporte gerencial, administrativo, tecnológico e de comunicação social à implementação das iniciativas</t>
+        </is>
+      </c>
+      <c r="AF62" t="inlineStr">
+        <is>
+          <t>Acordo Judicial do Rio Doce - ANEXO 12 - 9468055 - Suporte gerencial, administrativo, tecnológico e de comunicação social à implementação das iniciativas</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B63" t="n">
+        <v>1500</v>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>SECRETARIA DE ESTADO DE PLANEJAMENTO E GESTÃO - SEPLAG</t>
+        </is>
+      </c>
+      <c r="D63" t="n">
+        <v>3</v>
+      </c>
+      <c r="E63" t="n">
+        <v>0</v>
+      </c>
+      <c r="F63" t="n">
+        <v>1501</v>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>SECRETARIA DE ESTADO DE PLANEJAMENTO E GESTÃO - SEPLAG</t>
+        </is>
+      </c>
+      <c r="H63" t="n">
+        <v>3</v>
+      </c>
+      <c r="I63" t="n">
+        <v>3</v>
+      </c>
+      <c r="J63" t="n">
+        <v>90</v>
+      </c>
+      <c r="K63" t="n">
+        <v>14</v>
+      </c>
+      <c r="L63" t="n">
+        <v>80</v>
+      </c>
+      <c r="M63" t="n">
+        <v>1</v>
+      </c>
+      <c r="N63" t="n">
+        <v>10819</v>
+      </c>
+      <c r="O63" t="n">
+        <v>4</v>
+      </c>
+      <c r="P63" t="n">
+        <v>122</v>
+      </c>
+      <c r="Q63" t="n">
+        <v>155</v>
+      </c>
+      <c r="R63" t="n">
+        <v>4</v>
+      </c>
+      <c r="S63" t="n">
+        <v>461</v>
+      </c>
+      <c r="T63" t="n">
+        <v>4461</v>
+      </c>
+      <c r="U63" t="n">
+        <v>1</v>
+      </c>
+      <c r="V63" t="n">
+        <v>125000</v>
+      </c>
+      <c r="W63" t="n">
+        <v>125000</v>
+      </c>
+      <c r="X63" t="n">
+        <v>125000</v>
+      </c>
+      <c r="Y63" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z63" t="inlineStr">
+        <is>
+          <t>RECUPERAÇÃO E COMPENSAÇÃO DOS DANOS EM FUNÇÃO DO DESASTRE MINERÁRIO DA SAMARCO EM MARIANA</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>REPARAÇÃO DOS DANOS DOS ROMPIMENTOS EM BRUMADINHO E MARIANA</t>
+        </is>
+      </c>
+      <c r="AB63" t="inlineStr">
+        <is>
+          <t>Acordo Judicial do Rio Doce</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>ANEXO 12</t>
+        </is>
+      </c>
+      <c r="AD63" t="n">
+        <v>9468055</v>
+      </c>
+      <c r="AE63" t="inlineStr">
+        <is>
+          <t>Suporte gerencial, administrativo, tecnológico e de comunicação social à implementação das iniciativas</t>
+        </is>
+      </c>
+      <c r="AF63" t="inlineStr">
+        <is>
+          <t>Acordo Judicial do Rio Doce - ANEXO 12 - 9468055 - Suporte gerencial, administrativo, tecnológico e de comunicação social à implementação das iniciativas</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B64" t="n">
+        <v>1500</v>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>SECRETARIA DE ESTADO DE PLANEJAMENTO E GESTÃO - SEPLAG</t>
+        </is>
+      </c>
+      <c r="D64" t="n">
+        <v>3</v>
+      </c>
+      <c r="E64" t="n">
+        <v>0</v>
+      </c>
+      <c r="F64" t="n">
+        <v>1501</v>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>SECRETARIA DE ESTADO DE PLANEJAMENTO E GESTÃO - SEPLAG</t>
+        </is>
+      </c>
+      <c r="H64" t="n">
+        <v>3</v>
+      </c>
+      <c r="I64" t="n">
+        <v>3</v>
+      </c>
+      <c r="J64" t="n">
+        <v>90</v>
+      </c>
+      <c r="K64" t="n">
+        <v>33</v>
+      </c>
+      <c r="L64" t="n">
+        <v>80</v>
+      </c>
+      <c r="M64" t="n">
+        <v>1</v>
+      </c>
+      <c r="N64" t="n">
+        <v>10819</v>
+      </c>
+      <c r="O64" t="n">
+        <v>4</v>
+      </c>
+      <c r="P64" t="n">
+        <v>122</v>
+      </c>
+      <c r="Q64" t="n">
+        <v>155</v>
+      </c>
+      <c r="R64" t="n">
+        <v>4</v>
+      </c>
+      <c r="S64" t="n">
+        <v>461</v>
+      </c>
+      <c r="T64" t="n">
+        <v>4461</v>
+      </c>
+      <c r="U64" t="n">
+        <v>1</v>
+      </c>
+      <c r="V64" t="n">
+        <v>50000</v>
+      </c>
+      <c r="W64" t="n">
+        <v>50000</v>
+      </c>
+      <c r="X64" t="n">
+        <v>50000</v>
+      </c>
+      <c r="Y64" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z64" t="inlineStr">
+        <is>
+          <t>RECUPERAÇÃO E COMPENSAÇÃO DOS DANOS EM FUNÇÃO DO DESASTRE MINERÁRIO DA SAMARCO EM MARIANA</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>REPARAÇÃO DOS DANOS DOS ROMPIMENTOS EM BRUMADINHO E MARIANA</t>
+        </is>
+      </c>
+      <c r="AB64" t="inlineStr">
+        <is>
+          <t>Acordo Judicial do Rio Doce</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>ANEXO 12</t>
+        </is>
+      </c>
+      <c r="AD64" t="n">
+        <v>9468055</v>
+      </c>
+      <c r="AE64" t="inlineStr">
+        <is>
+          <t>Suporte gerencial, administrativo, tecnológico e de comunicação social à implementação das iniciativas</t>
+        </is>
+      </c>
+      <c r="AF64" t="inlineStr">
+        <is>
+          <t>Acordo Judicial do Rio Doce - ANEXO 12 - 9468055 - Suporte gerencial, administrativo, tecnológico e de comunicação social à implementação das iniciativas</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B65" t="n">
+        <v>1500</v>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>SECRETARIA DE ESTADO DE PLANEJAMENTO E GESTÃO - SEPLAG</t>
+        </is>
+      </c>
+      <c r="D65" t="n">
+        <v>3</v>
+      </c>
+      <c r="E65" t="n">
+        <v>0</v>
+      </c>
+      <c r="F65" t="n">
+        <v>1501</v>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>SECRETARIA DE ESTADO DE PLANEJAMENTO E GESTÃO - SEPLAG</t>
+        </is>
+      </c>
+      <c r="H65" t="n">
+        <v>3</v>
+      </c>
+      <c r="I65" t="n">
+        <v>3</v>
+      </c>
+      <c r="J65" t="n">
+        <v>90</v>
+      </c>
+      <c r="K65" t="n">
+        <v>35</v>
+      </c>
+      <c r="L65" t="n">
+        <v>80</v>
+      </c>
+      <c r="M65" t="n">
+        <v>1</v>
+      </c>
+      <c r="N65" t="n">
+        <v>10819</v>
+      </c>
+      <c r="O65" t="n">
+        <v>4</v>
+      </c>
+      <c r="P65" t="n">
+        <v>122</v>
+      </c>
+      <c r="Q65" t="n">
+        <v>155</v>
+      </c>
+      <c r="R65" t="n">
+        <v>4</v>
+      </c>
+      <c r="S65" t="n">
+        <v>461</v>
+      </c>
+      <c r="T65" t="n">
+        <v>4461</v>
+      </c>
+      <c r="U65" t="n">
+        <v>1</v>
+      </c>
+      <c r="V65" t="n">
+        <v>2000000</v>
+      </c>
+      <c r="W65" t="n">
+        <v>2000000</v>
+      </c>
+      <c r="X65" t="n">
+        <v>2000000</v>
+      </c>
+      <c r="Y65" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z65" t="inlineStr">
+        <is>
+          <t>RECUPERAÇÃO E COMPENSAÇÃO DOS DANOS EM FUNÇÃO DO DESASTRE MINERÁRIO DA SAMARCO EM MARIANA</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>REPARAÇÃO DOS DANOS DOS ROMPIMENTOS EM BRUMADINHO E MARIANA</t>
+        </is>
+      </c>
+      <c r="AB65" t="inlineStr">
+        <is>
+          <t>Acordo Judicial do Rio Doce</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>ANEXO 12</t>
+        </is>
+      </c>
+      <c r="AD65" t="n">
+        <v>9468055</v>
+      </c>
+      <c r="AE65" t="inlineStr">
+        <is>
+          <t>Suporte gerencial, administrativo, tecnológico e de comunicação social à implementação das iniciativas</t>
+        </is>
+      </c>
+      <c r="AF65" t="inlineStr">
+        <is>
+          <t>Acordo Judicial do Rio Doce - ANEXO 12 - 9468055 - Suporte gerencial, administrativo, tecnológico e de comunicação social à implementação das iniciativas</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B66" t="n">
+        <v>1500</v>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>SECRETARIA DE ESTADO DE PLANEJAMENTO E GESTÃO - SEPLAG</t>
+        </is>
+      </c>
+      <c r="D66" t="n">
+        <v>3</v>
+      </c>
+      <c r="E66" t="n">
+        <v>0</v>
+      </c>
+      <c r="F66" t="n">
+        <v>1501</v>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>SECRETARIA DE ESTADO DE PLANEJAMENTO E GESTÃO - SEPLAG</t>
+        </is>
+      </c>
+      <c r="H66" t="n">
+        <v>3</v>
+      </c>
+      <c r="I66" t="n">
+        <v>3</v>
+      </c>
+      <c r="J66" t="n">
+        <v>90</v>
+      </c>
+      <c r="K66" t="n">
+        <v>37</v>
+      </c>
+      <c r="L66" t="n">
+        <v>80</v>
+      </c>
+      <c r="M66" t="n">
+        <v>1</v>
+      </c>
+      <c r="N66" t="n">
+        <v>10819</v>
+      </c>
+      <c r="O66" t="n">
+        <v>4</v>
+      </c>
+      <c r="P66" t="n">
+        <v>122</v>
+      </c>
+      <c r="Q66" t="n">
+        <v>155</v>
+      </c>
+      <c r="R66" t="n">
+        <v>4</v>
+      </c>
+      <c r="S66" t="n">
+        <v>461</v>
+      </c>
+      <c r="T66" t="n">
+        <v>4461</v>
+      </c>
+      <c r="U66" t="n">
+        <v>1</v>
+      </c>
+      <c r="V66" t="n">
+        <v>13596679</v>
+      </c>
+      <c r="W66" t="n">
+        <v>13596679</v>
+      </c>
+      <c r="X66" t="n">
+        <v>13596679</v>
+      </c>
+      <c r="Y66" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z66" t="inlineStr">
+        <is>
+          <t>RECUPERAÇÃO E COMPENSAÇÃO DOS DANOS EM FUNÇÃO DO DESASTRE MINERÁRIO DA SAMARCO EM MARIANA</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>REPARAÇÃO DOS DANOS DOS ROMPIMENTOS EM BRUMADINHO E MARIANA</t>
+        </is>
+      </c>
+      <c r="AB66" t="inlineStr">
+        <is>
+          <t>Acordo Judicial do Rio Doce</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>ANEXO 12</t>
+        </is>
+      </c>
+      <c r="AD66" t="n">
+        <v>9468055</v>
+      </c>
+      <c r="AE66" t="inlineStr">
+        <is>
+          <t>Suporte gerencial, administrativo, tecnológico e de comunicação social à implementação das iniciativas</t>
+        </is>
+      </c>
+      <c r="AF66" t="inlineStr">
+        <is>
+          <t>Acordo Judicial do Rio Doce - ANEXO 12 - 9468055 - Suporte gerencial, administrativo, tecnológico e de comunicação social à implementação das iniciativas</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B67" t="n">
+        <v>1500</v>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>SECRETARIA DE ESTADO DE PLANEJAMENTO E GESTÃO - SEPLAG</t>
+        </is>
+      </c>
+      <c r="D67" t="n">
+        <v>3</v>
+      </c>
+      <c r="E67" t="n">
+        <v>0</v>
+      </c>
+      <c r="F67" t="n">
+        <v>1501</v>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>SECRETARIA DE ESTADO DE PLANEJAMENTO E GESTÃO - SEPLAG</t>
+        </is>
+      </c>
+      <c r="H67" t="n">
+        <v>3</v>
+      </c>
+      <c r="I67" t="n">
+        <v>3</v>
+      </c>
+      <c r="J67" t="n">
+        <v>90</v>
+      </c>
+      <c r="K67" t="n">
+        <v>39</v>
+      </c>
+      <c r="L67" t="n">
+        <v>80</v>
+      </c>
+      <c r="M67" t="n">
+        <v>1</v>
+      </c>
+      <c r="N67" t="n">
+        <v>10819</v>
+      </c>
+      <c r="O67" t="n">
+        <v>4</v>
+      </c>
+      <c r="P67" t="n">
+        <v>122</v>
+      </c>
+      <c r="Q67" t="n">
+        <v>155</v>
+      </c>
+      <c r="R67" t="n">
+        <v>4</v>
+      </c>
+      <c r="S67" t="n">
+        <v>461</v>
+      </c>
+      <c r="T67" t="n">
+        <v>4461</v>
+      </c>
+      <c r="U67" t="n">
+        <v>1</v>
+      </c>
+      <c r="V67" t="n">
+        <v>152100</v>
+      </c>
+      <c r="W67" t="n">
+        <v>152100</v>
+      </c>
+      <c r="X67" t="n">
+        <v>152100</v>
+      </c>
+      <c r="Y67" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z67" t="inlineStr">
+        <is>
+          <t>RECUPERAÇÃO E COMPENSAÇÃO DOS DANOS EM FUNÇÃO DO DESASTRE MINERÁRIO DA SAMARCO EM MARIANA</t>
+        </is>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>REPARAÇÃO DOS DANOS DOS ROMPIMENTOS EM BRUMADINHO E MARIANA</t>
+        </is>
+      </c>
+      <c r="AB67" t="inlineStr">
+        <is>
+          <t>Acordo Judicial do Rio Doce</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>ANEXO 12</t>
+        </is>
+      </c>
+      <c r="AD67" t="n">
+        <v>9468055</v>
+      </c>
+      <c r="AE67" t="inlineStr">
+        <is>
+          <t>Suporte gerencial, administrativo, tecnológico e de comunicação social à implementação das iniciativas</t>
+        </is>
+      </c>
+      <c r="AF67" t="inlineStr">
+        <is>
+          <t>Acordo Judicial do Rio Doce - ANEXO 12 - 9468055 - Suporte gerencial, administrativo, tecnológico e de comunicação social à implementação das iniciativas</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B68" t="n">
+        <v>1500</v>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>SECRETARIA DE ESTADO DE PLANEJAMENTO E GESTÃO - SEPLAG</t>
+        </is>
+      </c>
+      <c r="D68" t="n">
+        <v>3</v>
+      </c>
+      <c r="E68" t="n">
+        <v>0</v>
+      </c>
+      <c r="F68" t="n">
+        <v>1501</v>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>SECRETARIA DE ESTADO DE PLANEJAMENTO E GESTÃO - SEPLAG</t>
+        </is>
+      </c>
+      <c r="H68" t="n">
+        <v>3</v>
+      </c>
+      <c r="I68" t="n">
+        <v>3</v>
+      </c>
+      <c r="J68" t="n">
+        <v>90</v>
+      </c>
+      <c r="K68" t="n">
+        <v>37</v>
+      </c>
+      <c r="L68" t="n">
+        <v>95</v>
+      </c>
+      <c r="M68" t="n">
+        <v>1</v>
+      </c>
+      <c r="N68" t="n">
+        <v>10821</v>
+      </c>
+      <c r="O68" t="n">
+        <v>4</v>
+      </c>
+      <c r="P68" t="n">
+        <v>122</v>
+      </c>
+      <c r="Q68" t="n">
+        <v>155</v>
+      </c>
+      <c r="R68" t="n">
+        <v>4</v>
+      </c>
+      <c r="S68" t="n">
+        <v>462</v>
+      </c>
+      <c r="T68" t="n">
+        <v>4462</v>
+      </c>
+      <c r="U68" t="n">
+        <v>1</v>
+      </c>
+      <c r="V68" t="n">
+        <v>1000</v>
+      </c>
+      <c r="W68" t="n">
+        <v>1000</v>
+      </c>
+      <c r="X68" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y68" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z68" t="inlineStr">
+        <is>
+          <t>RECUPERAÇÃO E COMPENSAÇÃO DOS DANOS EM FUNÇÃO DO DESASTRE MINERÁRIO DA VALE S.A EM BRUMADINHO</t>
+        </is>
+      </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>REPARAÇÃO DOS DANOS DOS ROMPIMENTOS EM BRUMADINHO E MARIANA</t>
+        </is>
+      </c>
+      <c r="AB68" t="inlineStr">
+        <is>
+          <t>Acordo Judicial Vale</t>
+        </is>
+      </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>Ressarcimentos e contratações temporárias</t>
+        </is>
+      </c>
+      <c r="AD68" t="n">
+        <v>9288191</v>
+      </c>
+      <c r="AE68" t="inlineStr">
+        <is>
+          <t>Ressarcimentos de despesas públicas</t>
+        </is>
+      </c>
+      <c r="AF68" t="inlineStr">
+        <is>
+          <t>Acordo Judicial Vale - Ressarcimentos e contratações temporárias - 9288191 - Ressarcimentos de despesas públicas</t>
         </is>
       </c>
     </row>

--- a/bancos/SISOR/BASE_QDD_FISCAL_FONTE_95.xlsx
+++ b/bancos/SISOR/BASE_QDD_FISCAL_FONTE_95.xlsx
@@ -2,14 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="500" windowWidth="38400" windowHeight="21100" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="base_qdd_fiscal" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="191029" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -49,7 +50,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -412,8 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AF68"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -5242,13 +5242,13 @@
         <v>1</v>
       </c>
       <c r="V42" t="n">
-        <v>10024937.95</v>
+        <v>10024938</v>
       </c>
       <c r="W42" t="n">
-        <v>10024937.95</v>
+        <v>10024938</v>
       </c>
       <c r="X42" t="n">
-        <v>10024937.95</v>
+        <v>10024938</v>
       </c>
       <c r="Y42" t="n">
         <v>0</v>
@@ -5358,13 +5358,13 @@
         <v>1</v>
       </c>
       <c r="V43" t="n">
-        <v>3392647.75</v>
+        <v>3392647</v>
       </c>
       <c r="W43" t="n">
-        <v>3392647.75</v>
+        <v>3392647</v>
       </c>
       <c r="X43" t="n">
-        <v>3392647.75</v>
+        <v>3392647</v>
       </c>
       <c r="Y43" t="n">
         <v>0</v>
@@ -5472,13 +5472,13 @@
         <v>1</v>
       </c>
       <c r="V44" t="n">
-        <v>10542586.43</v>
+        <v>10542587</v>
       </c>
       <c r="W44" t="n">
-        <v>10542586.43</v>
+        <v>10542587</v>
       </c>
       <c r="X44" t="n">
-        <v>10542586.43</v>
+        <v>10542587</v>
       </c>
       <c r="Y44" t="n">
         <v>0</v>
@@ -5586,13 +5586,13 @@
         <v>1</v>
       </c>
       <c r="V45" t="n">
-        <v>726819.2</v>
+        <v>726819</v>
       </c>
       <c r="W45" t="n">
-        <v>726819.2</v>
+        <v>726819</v>
       </c>
       <c r="X45" t="n">
-        <v>726819.2</v>
+        <v>726819</v>
       </c>
       <c r="Y45" t="n">
         <v>0</v>

--- a/bancos/SISOR/BASE_QDD_FISCAL_FONTE_95.xlsx
+++ b/bancos/SISOR/BASE_QDD_FISCAL_FONTE_95.xlsx
@@ -413,6 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:AF68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -679,7 +680,7 @@
       </c>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>A SER CRIADO</t>
+          <t>INSTRUMENTO A SER CRIADO</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
@@ -689,7 +690,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>Acordo Judicial do Rio Doce - ANEXO 12 - A SER CRIADO - Disponibilização de acesso à água</t>
+          <t>Acordo Judicial do Rio Doce - ANEXO 12 - INSTRUMENTO A SER CRIADO - Disponibilização de acesso à água</t>
         </is>
       </c>
     </row>
@@ -1365,7 +1366,7 @@
       </c>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>A SER CRIADO</t>
+          <t>INSTRUMENTO A SER CRIADO</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
@@ -1375,7 +1376,7 @@
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>Acordo Judicial do Rio Doce - ANEXO 12 - A SER CRIADO - Criação de fundo de disponibilização de crédito para recuperação econômica de pequenas, médias e grandes empresas dos municípios atingidos, além de fundo garantidor para facilitar o acesso a essa linha de crédito</t>
+          <t>Acordo Judicial do Rio Doce - ANEXO 12 - INSTRUMENTO A SER CRIADO - Criação de fundo de disponibilização de crédito para recuperação econômica de pequenas, médias e grandes empresas dos municípios atingidos, além de fundo garantidor para facilitar o acesso a essa linha de crédito</t>
         </is>
       </c>
     </row>
@@ -1481,7 +1482,7 @@
       </c>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>A SER CRIADO</t>
+          <t>INSTRUMENTO A SER CRIADO</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
@@ -1491,7 +1492,7 @@
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>Acordo Judicial do Rio Doce - ANEXO 12 - A SER CRIADO - Criação de fundo de disponibilização de crédito para recuperação econômica de pequenas, médias e grandes empresas dos municípios atingidos, além de fundo garantidor para facilitar o acesso a essa linha de crédito</t>
+          <t>Acordo Judicial do Rio Doce - ANEXO 12 - INSTRUMENTO A SER CRIADO - Criação de fundo de disponibilização de crédito para recuperação econômica de pequenas, médias e grandes empresas dos municípios atingidos, além de fundo garantidor para facilitar o acesso a essa linha de crédito</t>
         </is>
       </c>
     </row>
@@ -1597,7 +1598,7 @@
       </c>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>A SER CRIADO</t>
+          <t>INSTRUMENTO A SER CRIADO</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
@@ -1607,7 +1608,7 @@
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>Acordo Judicial do Rio Doce - ANEXO 12 - A SER CRIADO - Fomento ao associativismo e ao cooperativismo a partir de assessoria às organizações, podendo incluir aprimoramento da gestão, qualificação de produtos e serviços, apoio na comunicação e marketing, mapeamento de necessidades de infraestrutura e fornecimento de equipamentos e insumos</t>
+          <t>Acordo Judicial do Rio Doce - ANEXO 12 - INSTRUMENTO A SER CRIADO - Fomento ao associativismo e ao cooperativismo a partir de assessoria às organizações, podendo incluir aprimoramento da gestão, qualificação de produtos e serviços, apoio na comunicação e marketing, mapeamento de necessidades de infraestrutura e fornecimento de equipamentos e insumos</t>
         </is>
       </c>
     </row>
@@ -1713,7 +1714,7 @@
       </c>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>A SER CRIADO</t>
+          <t>INSTRUMENTO A SER CRIADO</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
@@ -1723,7 +1724,7 @@
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>Acordo Judicial do Rio Doce - ANEXO 12 - A SER CRIADO - Fomento ao associativismo e ao cooperativismo a partir de assessoria às organizações, podendo incluir aprimoramento da gestão, qualificação de produtos e serviços, apoio na comunicação e marketing, mapeamento de necessidades de infraestrutura e fornecimento de equipamentos e insumos</t>
+          <t>Acordo Judicial do Rio Doce - ANEXO 12 - INSTRUMENTO A SER CRIADO - Fomento ao associativismo e ao cooperativismo a partir de assessoria às organizações, podendo incluir aprimoramento da gestão, qualificação de produtos e serviços, apoio na comunicação e marketing, mapeamento de necessidades de infraestrutura e fornecimento de equipamentos e insumos</t>
         </is>
       </c>
     </row>
@@ -1829,7 +1830,7 @@
       </c>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>A SER CRIADO</t>
+          <t>INSTRUMENTO A SER CRIADO</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
@@ -1839,7 +1840,7 @@
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>Acordo Judicial do Rio Doce - ANEXO 12 - A SER CRIADO - Fomento ao associativismo e ao cooperativismo a partir de assessoria às organizações, podendo incluir aprimoramento da gestão, qualificação de produtos e serviços, apoio na comunicação e marketing, mapeamento de necessidades de infraestrutura e fornecimento de equipamentos e insumos</t>
+          <t>Acordo Judicial do Rio Doce - ANEXO 12 - INSTRUMENTO A SER CRIADO - Fomento ao associativismo e ao cooperativismo a partir de assessoria às organizações, podendo incluir aprimoramento da gestão, qualificação de produtos e serviços, apoio na comunicação e marketing, mapeamento de necessidades de infraestrutura e fornecimento de equipamentos e insumos</t>
         </is>
       </c>
     </row>
@@ -1945,7 +1946,7 @@
       </c>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>A SER CRIADO</t>
+          <t>INSTRUMENTO A SER CRIADO</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
@@ -1955,7 +1956,7 @@
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>Acordo Judicial do Rio Doce - ANEXO 12 - A SER CRIADO - Fomento ao associativismo e ao cooperativismo a partir de assessoria às organizações, podendo incluir aprimoramento da gestão, qualificação de produtos e serviços, apoio na comunicação e marketing, mapeamento de necessidades de infraestrutura e fornecimento de equipamentos e insumos</t>
+          <t>Acordo Judicial do Rio Doce - ANEXO 12 - INSTRUMENTO A SER CRIADO - Fomento ao associativismo e ao cooperativismo a partir de assessoria às organizações, podendo incluir aprimoramento da gestão, qualificação de produtos e serviços, apoio na comunicação e marketing, mapeamento de necessidades de infraestrutura e fornecimento de equipamentos e insumos</t>
         </is>
       </c>
     </row>
@@ -2061,7 +2062,7 @@
       </c>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>A SER CRIADO</t>
+          <t>INSTRUMENTO A SER CRIADO</t>
         </is>
       </c>
       <c r="AE14" t="inlineStr">
@@ -2071,7 +2072,7 @@
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>Acordo Judicial do Rio Doce - ANEXO 12 - A SER CRIADO - Fomento ao associativismo e ao cooperativismo a partir de assessoria às organizações, podendo incluir aprimoramento da gestão, qualificação de produtos e serviços, apoio na comunicação e marketing, mapeamento de necessidades de infraestrutura e fornecimento de equipamentos e insumos</t>
+          <t>Acordo Judicial do Rio Doce - ANEXO 12 - INSTRUMENTO A SER CRIADO - Fomento ao associativismo e ao cooperativismo a partir de assessoria às organizações, podendo incluir aprimoramento da gestão, qualificação de produtos e serviços, apoio na comunicação e marketing, mapeamento de necessidades de infraestrutura e fornecimento de equipamentos e insumos</t>
         </is>
       </c>
     </row>
@@ -2177,7 +2178,7 @@
       </c>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>A SER CRIADO</t>
+          <t>INSTRUMENTO A SER CRIADO</t>
         </is>
       </c>
       <c r="AE15" t="inlineStr">
@@ -2187,7 +2188,7 @@
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>Acordo Judicial do Rio Doce - ANEXO 12 - A SER CRIADO - Fomento ao associativismo e ao cooperativismo a partir de assessoria às organizações, podendo incluir aprimoramento da gestão, qualificação de produtos e serviços, apoio na comunicação e marketing, mapeamento de necessidades de infraestrutura e fornecimento de equipamentos e insumos</t>
+          <t>Acordo Judicial do Rio Doce - ANEXO 12 - INSTRUMENTO A SER CRIADO - Fomento ao associativismo e ao cooperativismo a partir de assessoria às organizações, podendo incluir aprimoramento da gestão, qualificação de produtos e serviços, apoio na comunicação e marketing, mapeamento de necessidades de infraestrutura e fornecimento de equipamentos e insumos</t>
         </is>
       </c>
     </row>
@@ -2293,17 +2294,17 @@
       </c>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>A SER CRIADO</t>
+          <t>INSTRUMENTO A SER CRIADO</t>
         </is>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>A SER CRIADA</t>
+          <t>Fortalecimento dos Serviços de Inspeção Municipais</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>Acordo Judicial do Rio Doce - ANEXO 10 - A SER CRIADO - A SER CRIADA</t>
+          <t>Acordo Judicial do Rio Doce - ANEXO 10 - INSTRUMENTO A SER CRIADO - Fortalecimento dos Serviços de Inspeção Municipais</t>
         </is>
       </c>
     </row>
@@ -2409,17 +2410,17 @@
       </c>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>A SER CRIADO</t>
+          <t>INSTRUMENTO A SER CRIADO</t>
         </is>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>A SER CRIADA</t>
+          <t>Circuitos De Comercialização E Mercados Institucionais</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>Acordo Judicial do Rio Doce - ANEXO 10 - A SER CRIADO - A SER CRIADA</t>
+          <t>Acordo Judicial do Rio Doce - ANEXO 10 - INSTRUMENTO A SER CRIADO - Circuitos De Comercialização E Mercados Institucionais</t>
         </is>
       </c>
     </row>
@@ -2639,17 +2640,17 @@
       </c>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>A SER CRIADO</t>
+          <t>INSTRUMENTO A SER CRIADO</t>
         </is>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>A SER CRIADA</t>
+          <t>Arranjo Produtivo Local Projeto Apicultura</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>Acordo Judicial do Rio Doce - ANEXO 10 - A SER CRIADO - A SER CRIADA</t>
+          <t>Acordo Judicial do Rio Doce - ANEXO 10 - INSTRUMENTO A SER CRIADO - Arranjo Produtivo Local Projeto Apicultura</t>
         </is>
       </c>
     </row>
@@ -2869,17 +2870,17 @@
       </c>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>A SER CRIADO</t>
+          <t>INSTRUMENTO A SER CRIADO</t>
         </is>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>A SER CRIADA</t>
+          <t>Fortalecimento dos Serviços de Inspeção Municipais</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>Acordo Judicial do Rio Doce - ANEXO 10 - A SER CRIADO - A SER CRIADA</t>
+          <t>Acordo Judicial do Rio Doce - ANEXO 10 - INSTRUMENTO A SER CRIADO - Fortalecimento dos Serviços de Inspeção Municipais</t>
         </is>
       </c>
     </row>
@@ -2985,17 +2986,17 @@
       </c>
       <c r="AD22" t="inlineStr">
         <is>
-          <t>A SER CRIADO</t>
+          <t>INSTRUMENTO A SER CRIADO</t>
         </is>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>A SER CRIADA</t>
+          <t>Reestruturação Do Laboratório De Química Agropecuária Do Instituto Mineiro De Agropecuária.</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>Acordo Judicial do Rio Doce - ANEXO 10 - A SER CRIADO - A SER CRIADA</t>
+          <t>Acordo Judicial do Rio Doce - ANEXO 10 - INSTRUMENTO A SER CRIADO - Reestruturação Do Laboratório De Química Agropecuária Do Instituto Mineiro De Agropecuária.</t>
         </is>
       </c>
     </row>
@@ -3101,7 +3102,7 @@
       </c>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>A SER CRIADO</t>
+          <t>INSTRUMENTO A SER CRIADO</t>
         </is>
       </c>
       <c r="AE23" t="inlineStr">
@@ -3111,7 +3112,7 @@
       </c>
       <c r="AF23" t="inlineStr">
         <is>
-          <t>Acordo Judicial do Rio Doce - ANEXO 12 - A SER CRIADO - Oferta de serviços de assistência técnica e extensão rural (metodologia ISA/PASEA), visando à produção de alimentos e estímulo à comercialização e adequação socioeconômica e ambiental de propriedades rurais</t>
+          <t>Acordo Judicial do Rio Doce - ANEXO 12 - INSTRUMENTO A SER CRIADO - Oferta de serviços de assistência técnica e extensão rural (metodologia ISA/PASEA), visando à produção de alimentos e estímulo à comercialização e adequação socioeconômica e ambiental de propriedades rurais</t>
         </is>
       </c>
     </row>
@@ -3217,7 +3218,7 @@
       </c>
       <c r="AD24" t="inlineStr">
         <is>
-          <t>A SER CRIADO</t>
+          <t>INSTRUMENTO A SER CRIADO</t>
         </is>
       </c>
       <c r="AE24" t="inlineStr">
@@ -3227,7 +3228,7 @@
       </c>
       <c r="AF24" t="inlineStr">
         <is>
-          <t>Acordo Judicial do Rio Doce - ANEXO 12 - A SER CRIADO - Oferta de serviços de assistência técnica e extensão rural (metodologia ISA/PASEA), visando à produção de alimentos e estímulo à comercialização e adequação socioeconômica e ambiental de propriedades rurais</t>
+          <t>Acordo Judicial do Rio Doce - ANEXO 12 - INSTRUMENTO A SER CRIADO - Oferta de serviços de assistência técnica e extensão rural (metodologia ISA/PASEA), visando à produção de alimentos e estímulo à comercialização e adequação socioeconômica e ambiental de propriedades rurais</t>
         </is>
       </c>
     </row>
@@ -3328,7 +3329,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>III</t>
+          <t>ANEXO III</t>
         </is>
       </c>
       <c r="AD25" t="n">
@@ -3341,7 +3342,7 @@
       </c>
       <c r="AF25" t="inlineStr">
         <is>
-          <t>Acordo Judicial Vale - III - 9288180 - Implantação do Rodoanel da Região Metropolitana de Belo Horizonte</t>
+          <t>Acordo Judicial Vale - ANEXO III - 9288180 - Implantação do Rodoanel da Região Metropolitana de Belo Horizonte</t>
         </is>
       </c>
     </row>
@@ -3442,7 +3443,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>IV</t>
+          <t>ANEXO IV</t>
         </is>
       </c>
       <c r="AD26" t="n">
@@ -3455,7 +3456,7 @@
       </c>
       <c r="AF26" t="inlineStr">
         <is>
-          <t>Acordo Judicial Vale - IV - 9288178 - Prevenção de Enchentes - Construção de Bacias de Contenção no Córrego Ferrugem</t>
+          <t>Acordo Judicial Vale - ANEXO IV - 9288178 - Prevenção de Enchentes - Construção de Bacias de Contenção no Córrego Ferrugem</t>
         </is>
       </c>
     </row>
@@ -3556,7 +3557,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>IV</t>
+          <t>ANEXO IV</t>
         </is>
       </c>
       <c r="AD27" t="n">
@@ -3569,7 +3570,7 @@
       </c>
       <c r="AF27" t="inlineStr">
         <is>
-          <t>Acordo Judicial Vale - IV - 9288179 - Prevenção de Enchentes - Desapropriação para construção de bacias de contenção no Córrego Riacho das Pedras</t>
+          <t>Acordo Judicial Vale - ANEXO IV - 9288179 - Prevenção de Enchentes - Desapropriação para construção de bacias de contenção no Córrego Riacho das Pedras</t>
         </is>
       </c>
     </row>
@@ -4012,7 +4013,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>III</t>
+          <t>ANEXO III</t>
         </is>
       </c>
       <c r="AD31" t="n">
@@ -4025,7 +4026,7 @@
       </c>
       <c r="AF31" t="inlineStr">
         <is>
-          <t>Acordo Judicial Vale - III - 9288132 - Construção de pontes em São Francisco, Manga e São Romão sobre o Rio São Francisco</t>
+          <t>Acordo Judicial Vale - ANEXO III - 9288132 - Construção de pontes em São Francisco, Manga e São Romão sobre o Rio São Francisco</t>
         </is>
       </c>
     </row>
@@ -4126,7 +4127,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>III</t>
+          <t>ANEXO III</t>
         </is>
       </c>
       <c r="AD32" t="n">
@@ -4139,7 +4140,7 @@
       </c>
       <c r="AF32" t="inlineStr">
         <is>
-          <t>Acordo Judicial Vale - III - 9288133 - Recuperação de rodovias pavimentadas em pior estado, conforme avaliação técnica do DER-MG/conclusão de corredor logístico estruturante, conforme critérios técnicos da SEINFRA</t>
+          <t>Acordo Judicial Vale - ANEXO III - 9288133 - Recuperação de rodovias pavimentadas em pior estado, conforme avaliação técnica do DER-MG/conclusão de corredor logístico estruturante, conforme critérios técnicos da SEINFRA</t>
         </is>
       </c>
     </row>
@@ -4582,7 +4583,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>III</t>
+          <t>ANEXO III</t>
         </is>
       </c>
       <c r="AD36" t="n">
@@ -4595,7 +4596,7 @@
       </c>
       <c r="AF36" t="inlineStr">
         <is>
-          <t>Acordo Judicial Vale - III - 9288180 - Implantação do Rodoanel da Região Metropolitana de Belo Horizonte</t>
+          <t>Acordo Judicial Vale - ANEXO III - 9288180 - Implantação do Rodoanel da Região Metropolitana de Belo Horizonte</t>
         </is>
       </c>
     </row>
@@ -4704,12 +4705,12 @@
       </c>
       <c r="AE37" t="inlineStr">
         <is>
-          <t>Políticas e ações de competência e execução direta do ESTADO DE MINAS GERAIS para aplicação em saúde nos municípios  (pendente criação de inciativas)</t>
+          <t>Fortalecimento do Sistema Único de Saúde (SUS)</t>
         </is>
       </c>
       <c r="AF37" t="inlineStr">
         <is>
-          <t>Acordo Judicial do Rio Doce - ANEXO 08 - 9445683 - Políticas e ações de competência e execução direta do ESTADO DE MINAS GERAIS para aplicação em saúde nos municípios  (pendente criação de inciativas)</t>
+          <t>Acordo Judicial do Rio Doce - ANEXO 08 - 9445683 - Fortalecimento do Sistema Único de Saúde (SUS)</t>
         </is>
       </c>
     </row>
@@ -4815,7 +4816,7 @@
       </c>
       <c r="AD38" t="inlineStr">
         <is>
-          <t>A SER CRIADO</t>
+          <t>INSTRUMENTO A SER CRIADO</t>
         </is>
       </c>
       <c r="AE38" t="inlineStr">
@@ -4825,7 +4826,7 @@
       </c>
       <c r="AF38" t="inlineStr">
         <is>
-          <t>Acordo Judicial do Rio Doce - ANEXO 12 - A SER CRIADO - Suporte gerencial, administrativo, tecnológico e de comunicação social à implementação das iniciativas ambientais</t>
+          <t>Acordo Judicial do Rio Doce - ANEXO 12 - INSTRUMENTO A SER CRIADO - Suporte gerencial, administrativo, tecnológico e de comunicação social à implementação das iniciativas ambientais</t>
         </is>
       </c>
     </row>
@@ -4931,7 +4932,7 @@
       </c>
       <c r="AD39" t="inlineStr">
         <is>
-          <t>A SER CRIADO</t>
+          <t>INSTRUMENTO A SER CRIADO</t>
         </is>
       </c>
       <c r="AE39" t="inlineStr">
@@ -4941,7 +4942,7 @@
       </c>
       <c r="AF39" t="inlineStr">
         <is>
-          <t>Acordo Judicial do Rio Doce - ANEXO 12 - A SER CRIADO - Melhoria na capacidade estadual fiscalizatória de barragens nas estruturas localizadas na extensão territorial da Bacia Hidrográfica do Rio Doce: aquisição de equipamentos físicos e tecnológicos, contratação de serviços de consultoria</t>
+          <t>Acordo Judicial do Rio Doce - ANEXO 12 - INSTRUMENTO A SER CRIADO - Melhoria na capacidade estadual fiscalizatória de barragens nas estruturas localizadas na extensão territorial da Bacia Hidrográfica do Rio Doce: aquisição de equipamentos físicos e tecnológicos, contratação de serviços de consultoria</t>
         </is>
       </c>
     </row>
@@ -5050,12 +5051,12 @@
       </c>
       <c r="AE40" t="inlineStr">
         <is>
-          <t>Consolidação de unidades de conservação estaduais na Bacia Hidrográfica do Rio Doce, a partir do investimento e custeio de suas estruturas e serviços prestados, de acordo com seus objetivos de criação; criação, se necessário, de nova(s) unidade(s) de conservação na Bacia Hidrográfica do Rio Doce de acordo com mapeamento de áreas prioritárias para conservação; realização de atividades de prevenção e combate a incêndios e regularização fundiária das unidades de conservação.</t>
+          <t>Consolidação de unidades de conservação estaduais na Bacia Hidrográfica do Rio Doce, a partir do investimento e custeio de suas estruturas e serviços prestados, de acordo com seus objetivos de criação; criação, se necessário, de nova(s) unidade(s) de conservação na Bacia Hidrográfica do Rio Doce de acordo com mapeamento de áreas prioritárias para conservação; realização de atividades de prevenção e combate a incêndios e regularização fundiária das unidades de conservação</t>
         </is>
       </c>
       <c r="AF40" t="inlineStr">
         <is>
-          <t>Acordo Judicial do Rio Doce - ANEXO 12 - 9456606 - Consolidação de unidades de conservação estaduais na Bacia Hidrográfica do Rio Doce, a partir do investimento e custeio de suas estruturas e serviços prestados, de acordo com seus objetivos de criação; criação, se necessário, de nova(s) unidade(s) de conservação na Bacia Hidrográfica do Rio Doce de acordo com mapeamento de áreas prioritárias para conservação; realização de atividades de prevenção e combate a incêndios e regularização fundiária das unidades de conservação.</t>
+          <t>Acordo Judicial do Rio Doce - ANEXO 12 - 9456606 - Consolidação de unidades de conservação estaduais na Bacia Hidrográfica do Rio Doce, a partir do investimento e custeio de suas estruturas e serviços prestados, de acordo com seus objetivos de criação; criação, se necessário, de nova(s) unidade(s) de conservação na Bacia Hidrográfica do Rio Doce de acordo com mapeamento de áreas prioritárias para conservação; realização de atividades de prevenção e combate a incêndios e regularização fundiária das unidades de conservação</t>
         </is>
       </c>
     </row>
@@ -5164,12 +5165,12 @@
       </c>
       <c r="AE41" t="inlineStr">
         <is>
-          <t>Consolidação de unidades de conservação estaduais na Bacia Hidrográfica do Rio Doce, a partir do investimento e custeio de suas estruturas e serviços prestados, de acordo com seus objetivos de criação; criação, se necessário, de nova(s) unidade(s) de conservação na Bacia Hidrográfica do Rio Doce de acordo com mapeamento de áreas prioritárias para conservação; realização de atividades de prevenção e combate a incêndios e regularização fundiária das unidades de conservação.</t>
+          <t>Consolidação de unidades de conservação estaduais na Bacia Hidrográfica do Rio Doce, a partir do investimento e custeio de suas estruturas e serviços prestados, de acordo com seus objetivos de criação; criação, se necessário, de nova(s) unidade(s) de conservação na Bacia Hidrográfica do Rio Doce de acordo com mapeamento de áreas prioritárias para conservação; realização de atividades de prevenção e combate a incêndios e regularização fundiária das unidades de conservação</t>
         </is>
       </c>
       <c r="AF41" t="inlineStr">
         <is>
-          <t>Acordo Judicial do Rio Doce - ANEXO 12 - 9456606 - Consolidação de unidades de conservação estaduais na Bacia Hidrográfica do Rio Doce, a partir do investimento e custeio de suas estruturas e serviços prestados, de acordo com seus objetivos de criação; criação, se necessário, de nova(s) unidade(s) de conservação na Bacia Hidrográfica do Rio Doce de acordo com mapeamento de áreas prioritárias para conservação; realização de atividades de prevenção e combate a incêndios e regularização fundiária das unidades de conservação.</t>
+          <t>Acordo Judicial do Rio Doce - ANEXO 12 - 9456606 - Consolidação de unidades de conservação estaduais na Bacia Hidrográfica do Rio Doce, a partir do investimento e custeio de suas estruturas e serviços prestados, de acordo com seus objetivos de criação; criação, se necessário, de nova(s) unidade(s) de conservação na Bacia Hidrográfica do Rio Doce de acordo com mapeamento de áreas prioritárias para conservação; realização de atividades de prevenção e combate a incêndios e regularização fundiária das unidades de conservação</t>
         </is>
       </c>
     </row>
@@ -5275,7 +5276,7 @@
       </c>
       <c r="AD42" t="inlineStr">
         <is>
-          <t>A CRIAR</t>
+          <t>INSTRUMENTO A SER CRIADO</t>
         </is>
       </c>
       <c r="AE42" t="inlineStr">
@@ -5285,7 +5286,7 @@
       </c>
       <c r="AF42" t="inlineStr">
         <is>
-          <t>Acordo Judicial do Rio Doce - ANEXO 10 - A CRIAR -  Elaboração e/ou atualização do ordenamento pesqueiro, na forma da Lei n. 11.959, de 29 de junho de 2009. III. Recomposição da biota, dos recursos e dos estoques pesqueiros do ecossistema como um todo na Bacia Hidrográfica do rio Doce, em sua foz e região costeira e marinha.</t>
+          <t>Acordo Judicial do Rio Doce - ANEXO 10 - INSTRUMENTO A SER CRIADO -  Elaboração e/ou atualização do ordenamento pesqueiro, na forma da Lei n. 11.959, de 29 de junho de 2009. III. Recomposição da biota, dos recursos e dos estoques pesqueiros do ecossistema como um todo na Bacia Hidrográfica do rio Doce, em sua foz e região costeira e marinha.</t>
         </is>
       </c>
     </row>
@@ -5622,12 +5623,12 @@
       </c>
       <c r="AE45" t="inlineStr">
         <is>
-          <t>Fortalecimento da política pública de gestão do manejo da fauna silvestre, de acordo com mapeamento de necessidades a ser detalhado, a partir de ações como da estruturação e custeio dos serviços prestados porelos Cetras que atendam à bacia hidrográfica do rio Doce; contratação de serviços veterinários especializados; construção de viveiros em áreas de parceiros para a reabilitação e conservação da faun</t>
+          <t>Fortalecimento da política pública de gestão do manejo da fauna silvestre, de acordo com mapeamento de necessidades a ser detalhado, a partir de ações como da estruturação e custeio dos serviços prestados porelos Cetras que atendam à bacia hidrográfica do rio Doce; contratação de serviços veterinários especializados; construção de viveiros em áreas de parceiros para a reabilitação e conservação da faunA</t>
         </is>
       </c>
       <c r="AF45" t="inlineStr">
         <is>
-          <t>Acordo Judicial do Rio Doce - ANEXO 12 - 9456605 - Fortalecimento da política pública de gestão do manejo da fauna silvestre, de acordo com mapeamento de necessidades a ser detalhado, a partir de ações como da estruturação e custeio dos serviços prestados porelos Cetras que atendam à bacia hidrográfica do rio Doce; contratação de serviços veterinários especializados; construção de viveiros em áreas de parceiros para a reabilitação e conservação da faun</t>
+          <t>Acordo Judicial do Rio Doce - ANEXO 12 - 9456605 - Fortalecimento da política pública de gestão do manejo da fauna silvestre, de acordo com mapeamento de necessidades a ser detalhado, a partir de ações como da estruturação e custeio dos serviços prestados porelos Cetras que atendam à bacia hidrográfica do rio Doce; contratação de serviços veterinários especializados; construção de viveiros em áreas de parceiros para a reabilitação e conservação da faunA</t>
         </is>
       </c>
     </row>
@@ -6189,7 +6190,7 @@
       </c>
       <c r="AD50" t="inlineStr">
         <is>
-          <t>A SER CRIADO</t>
+          <t>INSTRUMENTO A SER CRIADO</t>
         </is>
       </c>
       <c r="AE50" t="inlineStr">
@@ -6199,7 +6200,7 @@
       </c>
       <c r="AF50" t="inlineStr">
         <is>
-          <t>Acordo Judicial do Rio Doce - ANEXO 12 - A SER CRIADO - Ampliação, modernização e equipagem da rede meteorológica, rede hidrológica e Sala de Situação para eventos hidrológicos críticos, de forma a aprimorar a capacidade do Sistema Estadual de Meio Ambiente (SISEMA) de acompanhar a recuperação da Bacia Hidrográfica do Rio Doce vis-à-vis riscos decorrentes de eventos climáticos extremos.</t>
+          <t>Acordo Judicial do Rio Doce - ANEXO 12 - INSTRUMENTO A SER CRIADO - Ampliação, modernização e equipagem da rede meteorológica, rede hidrológica e Sala de Situação para eventos hidrológicos críticos, de forma a aprimorar a capacidade do Sistema Estadual de Meio Ambiente (SISEMA) de acompanhar a recuperação da Bacia Hidrográfica do Rio Doce vis-à-vis riscos decorrentes de eventos climáticos extremos.</t>
         </is>
       </c>
     </row>
@@ -6305,7 +6306,7 @@
       </c>
       <c r="AD51" t="inlineStr">
         <is>
-          <t>A SER CRIADO</t>
+          <t>INSTRUMENTO A SER CRIADO</t>
         </is>
       </c>
       <c r="AE51" t="inlineStr">
@@ -6315,7 +6316,7 @@
       </c>
       <c r="AF51" t="inlineStr">
         <is>
-          <t>Acordo Judicial do Rio Doce - ANEXO 12 - A SER CRIADO - Ampliação, modernização e equipagem da rede meteorológica, rede hidrológica e Sala de Situação para eventos hidrológicos críticos, de forma a aprimorar a capacidade do Sistema Estadual de Meio Ambiente (SISEMA) de acompanhar a recuperação da Bacia Hidrográfica do Rio Doce vis-à-vis riscos decorrentes de eventos climáticos extremos.</t>
+          <t>Acordo Judicial do Rio Doce - ANEXO 12 - INSTRUMENTO A SER CRIADO - Ampliação, modernização e equipagem da rede meteorológica, rede hidrológica e Sala de Situação para eventos hidrológicos críticos, de forma a aprimorar a capacidade do Sistema Estadual de Meio Ambiente (SISEMA) de acompanhar a recuperação da Bacia Hidrográfica do Rio Doce vis-à-vis riscos decorrentes de eventos climáticos extremos.</t>
         </is>
       </c>
     </row>
@@ -6421,7 +6422,7 @@
       </c>
       <c r="AD52" t="inlineStr">
         <is>
-          <t>A SER CRIADO</t>
+          <t>INSTRUMENTO A SER CRIADO</t>
         </is>
       </c>
       <c r="AE52" t="inlineStr">
@@ -6431,7 +6432,7 @@
       </c>
       <c r="AF52" t="inlineStr">
         <is>
-          <t>Acordo Judicial do Rio Doce - ANEXO 12 - A SER CRIADO - Ampliação, modernização e equipagem da rede meteorológica, rede hidrológica e Sala de Situação para eventos hidrológicos críticos, de forma a aprimorar a capacidade do Sistema Estadual de Meio Ambiente (SISEMA) de acompanhar a recuperação da Bacia Hidrográfica do Rio Doce vis-à-vis riscos decorrentes de eventos climáticos extremos.</t>
+          <t>Acordo Judicial do Rio Doce - ANEXO 12 - INSTRUMENTO A SER CRIADO - Ampliação, modernização e equipagem da rede meteorológica, rede hidrológica e Sala de Situação para eventos hidrológicos críticos, de forma a aprimorar a capacidade do Sistema Estadual de Meio Ambiente (SISEMA) de acompanhar a recuperação da Bacia Hidrográfica do Rio Doce vis-à-vis riscos decorrentes de eventos climáticos extremos.</t>
         </is>
       </c>
     </row>
@@ -6537,7 +6538,7 @@
       </c>
       <c r="AD53" t="inlineStr">
         <is>
-          <t>A SER CRIADO</t>
+          <t>INSTRUMENTO A SER CRIADO</t>
         </is>
       </c>
       <c r="AE53" t="inlineStr">
@@ -6547,7 +6548,7 @@
       </c>
       <c r="AF53" t="inlineStr">
         <is>
-          <t>Acordo Judicial do Rio Doce - ANEXO 12 - A SER CRIADO - Ampliação, modernização e equipagem da rede meteorológica, rede hidrológica e Sala de Situação para eventos hidrológicos críticos, de forma a aprimorar a capacidade do Sistema Estadual de Meio Ambiente (SISEMA) de acompanhar a recuperação da Bacia Hidrográfica do Rio Doce vis-à-vis riscos decorrentes de eventos climáticos extremos.</t>
+          <t>Acordo Judicial do Rio Doce - ANEXO 12 - INSTRUMENTO A SER CRIADO - Ampliação, modernização e equipagem da rede meteorológica, rede hidrológica e Sala de Situação para eventos hidrológicos críticos, de forma a aprimorar a capacidade do Sistema Estadual de Meio Ambiente (SISEMA) de acompanhar a recuperação da Bacia Hidrográfica do Rio Doce vis-à-vis riscos decorrentes de eventos climáticos extremos.</t>
         </is>
       </c>
     </row>
@@ -6653,7 +6654,7 @@
       </c>
       <c r="AD54" t="inlineStr">
         <is>
-          <t>A SER CRIADO</t>
+          <t>INSTRUMENTO A SER CRIADO</t>
         </is>
       </c>
       <c r="AE54" t="inlineStr">
@@ -6663,7 +6664,7 @@
       </c>
       <c r="AF54" t="inlineStr">
         <is>
-          <t>Acordo Judicial do Rio Doce - ANEXO 12 - A SER CRIADO - Melhoria na capacidade estadual fiscalizatória de barragens nas estruturas localizadas na extensão territorial da Bacia Hidrográfica do Rio Doce: aquisição de equipamentos físicos e tecnológicos, contratação de serviços de consultoria</t>
+          <t>Acordo Judicial do Rio Doce - ANEXO 12 - INSTRUMENTO A SER CRIADO - Melhoria na capacidade estadual fiscalizatória de barragens nas estruturas localizadas na extensão territorial da Bacia Hidrográfica do Rio Doce: aquisição de equipamentos físicos e tecnológicos, contratação de serviços de consultoria</t>
         </is>
       </c>
     </row>
@@ -7000,12 +7001,12 @@
       </c>
       <c r="AE57" t="inlineStr">
         <is>
-          <t>Oferta de cursos de qualificação profissional a partir de estudo de demandas do mercado de trabalho - SEDESE</t>
+          <t>Oferta de cursos de qualificação profissional a partir de estudo de demandas do mercado de trabalho</t>
         </is>
       </c>
       <c r="AF57" t="inlineStr">
         <is>
-          <t>Acordo Judicial do Rio Doce - ANEXO 12 - 9456621 - Oferta de cursos de qualificação profissional a partir de estudo de demandas do mercado de trabalho - SEDESE</t>
+          <t>Acordo Judicial do Rio Doce - ANEXO 12 - 9456621 - Oferta de cursos de qualificação profissional a partir de estudo de demandas do mercado de trabalho</t>
         </is>
       </c>
     </row>
@@ -7114,12 +7115,12 @@
       </c>
       <c r="AE58" t="inlineStr">
         <is>
-          <t>Oferta de cursos de qualificação profissional a partir de estudo de demandas do mercado de trabalho - SEDESE</t>
+          <t>Oferta de cursos de qualificação profissional a partir de estudo de demandas do mercado de trabalho</t>
         </is>
       </c>
       <c r="AF58" t="inlineStr">
         <is>
-          <t>Acordo Judicial do Rio Doce - ANEXO 12 - 9456621 - Oferta de cursos de qualificação profissional a partir de estudo de demandas do mercado de trabalho - SEDESE</t>
+          <t>Acordo Judicial do Rio Doce - ANEXO 12 - 9456621 - Oferta de cursos de qualificação profissional a partir de estudo de demandas do mercado de trabalho</t>
         </is>
       </c>
     </row>
@@ -7456,12 +7457,12 @@
       </c>
       <c r="AE61" t="inlineStr">
         <is>
-          <t>Repasse ao Fundo Estadual de Assistência Social (FEAS) do ESTADO DE MINAS GERAIS  (pendente criação de inciativas)</t>
+          <t>Fortalecimento do Sistema Único de Assistência Social (SUAS)</t>
         </is>
       </c>
       <c r="AF61" t="inlineStr">
         <is>
-          <t>Acordo Judicial do Rio Doce - ANEXO 07 - 9445684 - Repasse ao Fundo Estadual de Assistência Social (FEAS) do ESTADO DE MINAS GERAIS  (pendente criação de inciativas)</t>
+          <t>Acordo Judicial do Rio Doce - ANEXO 07 - 9445684 - Fortalecimento do Sistema Único de Assistência Social (SUAS)</t>
         </is>
       </c>
     </row>
@@ -7570,12 +7571,12 @@
       </c>
       <c r="AE62" t="inlineStr">
         <is>
-          <t>Suporte gerencial, administrativo, tecnológico e de comunicação social à implementação das iniciativas</t>
+          <t>Suporte gerencial, administrativo, tecnológico e de comunicação social à implementação das iniciativas Lista 3</t>
         </is>
       </c>
       <c r="AF62" t="inlineStr">
         <is>
-          <t>Acordo Judicial do Rio Doce - ANEXO 12 - 9468055 - Suporte gerencial, administrativo, tecnológico e de comunicação social à implementação das iniciativas</t>
+          <t>Acordo Judicial do Rio Doce - ANEXO 12 - 9468055 - Suporte gerencial, administrativo, tecnológico e de comunicação social à implementação das iniciativas Lista 3</t>
         </is>
       </c>
     </row>
@@ -7684,12 +7685,12 @@
       </c>
       <c r="AE63" t="inlineStr">
         <is>
-          <t>Suporte gerencial, administrativo, tecnológico e de comunicação social à implementação das iniciativas</t>
+          <t>Suporte gerencial, administrativo, tecnológico e de comunicação social à implementação das iniciativas Lista 3</t>
         </is>
       </c>
       <c r="AF63" t="inlineStr">
         <is>
-          <t>Acordo Judicial do Rio Doce - ANEXO 12 - 9468055 - Suporte gerencial, administrativo, tecnológico e de comunicação social à implementação das iniciativas</t>
+          <t>Acordo Judicial do Rio Doce - ANEXO 12 - 9468055 - Suporte gerencial, administrativo, tecnológico e de comunicação social à implementação das iniciativas Lista 3</t>
         </is>
       </c>
     </row>
@@ -7798,12 +7799,12 @@
       </c>
       <c r="AE64" t="inlineStr">
         <is>
-          <t>Suporte gerencial, administrativo, tecnológico e de comunicação social à implementação das iniciativas</t>
+          <t>Suporte gerencial, administrativo, tecnológico e de comunicação social à implementação das iniciativas Lista 3</t>
         </is>
       </c>
       <c r="AF64" t="inlineStr">
         <is>
-          <t>Acordo Judicial do Rio Doce - ANEXO 12 - 9468055 - Suporte gerencial, administrativo, tecnológico e de comunicação social à implementação das iniciativas</t>
+          <t>Acordo Judicial do Rio Doce - ANEXO 12 - 9468055 - Suporte gerencial, administrativo, tecnológico e de comunicação social à implementação das iniciativas Lista 3</t>
         </is>
       </c>
     </row>
@@ -7912,12 +7913,12 @@
       </c>
       <c r="AE65" t="inlineStr">
         <is>
-          <t>Suporte gerencial, administrativo, tecnológico e de comunicação social à implementação das iniciativas</t>
+          <t>Suporte gerencial, administrativo, tecnológico e de comunicação social à implementação das iniciativas Lista 3</t>
         </is>
       </c>
       <c r="AF65" t="inlineStr">
         <is>
-          <t>Acordo Judicial do Rio Doce - ANEXO 12 - 9468055 - Suporte gerencial, administrativo, tecnológico e de comunicação social à implementação das iniciativas</t>
+          <t>Acordo Judicial do Rio Doce - ANEXO 12 - 9468055 - Suporte gerencial, administrativo, tecnológico e de comunicação social à implementação das iniciativas Lista 3</t>
         </is>
       </c>
     </row>
@@ -8026,12 +8027,12 @@
       </c>
       <c r="AE66" t="inlineStr">
         <is>
-          <t>Suporte gerencial, administrativo, tecnológico e de comunicação social à implementação das iniciativas</t>
+          <t>Suporte gerencial, administrativo, tecnológico e de comunicação social à implementação das iniciativas Lista 3</t>
         </is>
       </c>
       <c r="AF66" t="inlineStr">
         <is>
-          <t>Acordo Judicial do Rio Doce - ANEXO 12 - 9468055 - Suporte gerencial, administrativo, tecnológico e de comunicação social à implementação das iniciativas</t>
+          <t>Acordo Judicial do Rio Doce - ANEXO 12 - 9468055 - Suporte gerencial, administrativo, tecnológico e de comunicação social à implementação das iniciativas Lista 3</t>
         </is>
       </c>
     </row>
@@ -8140,12 +8141,12 @@
       </c>
       <c r="AE67" t="inlineStr">
         <is>
-          <t>Suporte gerencial, administrativo, tecnológico e de comunicação social à implementação das iniciativas</t>
+          <t>Suporte gerencial, administrativo, tecnológico e de comunicação social à implementação das iniciativas Lista 3</t>
         </is>
       </c>
       <c r="AF67" t="inlineStr">
         <is>
-          <t>Acordo Judicial do Rio Doce - ANEXO 12 - 9468055 - Suporte gerencial, administrativo, tecnológico e de comunicação social à implementação das iniciativas</t>
+          <t>Acordo Judicial do Rio Doce - ANEXO 12 - 9468055 - Suporte gerencial, administrativo, tecnológico e de comunicação social à implementação das iniciativas Lista 3</t>
         </is>
       </c>
     </row>
